--- a/football_odds/results/2026-09-14_predictions.xlsx
+++ b/football_odds/results/2026-09-14_predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CO12"/>
+  <dimension ref="A1:CS12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -844,40 +844,60 @@
       </c>
       <c r="CH1" t="inlineStr">
         <is>
+          <t>ht_h</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>ht_d</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>ht_a</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>n_ht</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
           <t>tol_probs_1pct</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>tol_probs_2pct</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>tol_probs_3pct</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>tol_probs_5pct</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>tol_odds_1pct</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>tol_odds_2pct</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>tol_odds_3pct</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>tol_odds_5pct</t>
         </is>
@@ -1164,27 +1184,39 @@
         <v>98.896</v>
       </c>
       <c r="CH2" t="n">
+        <v>62</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>30</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>8</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL2" t="n">
         <v>349</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CM2" t="n">
         <v>1229</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CN2" t="n">
         <v>2084</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CO2" t="n">
         <v>3459</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CP2" t="n">
         <v>3</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CQ2" t="n">
         <v>13</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CR2" t="n">
         <v>38</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CS2" t="n">
         <v>128</v>
       </c>
     </row>
@@ -1469,27 +1501,39 @@
         <v>98.786</v>
       </c>
       <c r="CH3" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>499</v>
+      </c>
+      <c r="CL3" t="n">
         <v>265</v>
       </c>
-      <c r="CI3" t="n">
+      <c r="CM3" t="n">
         <v>969</v>
       </c>
-      <c r="CJ3" t="n">
+      <c r="CN3" t="n">
         <v>1674</v>
       </c>
-      <c r="CK3" t="n">
+      <c r="CO3" t="n">
         <v>3021</v>
       </c>
-      <c r="CL3" t="n">
+      <c r="CP3" t="n">
         <v>5</v>
       </c>
-      <c r="CM3" t="n">
+      <c r="CQ3" t="n">
         <v>32</v>
       </c>
-      <c r="CN3" t="n">
+      <c r="CR3" t="n">
         <v>98</v>
       </c>
-      <c r="CO3" t="n">
+      <c r="CS3" t="n">
         <v>299</v>
       </c>
     </row>
@@ -1774,27 +1818,39 @@
         <v>98.372</v>
       </c>
       <c r="CH4" t="n">
+        <v>15.462</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>39.558</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>498</v>
+      </c>
+      <c r="CL4" t="n">
         <v>280</v>
       </c>
-      <c r="CI4" t="n">
+      <c r="CM4" t="n">
         <v>944</v>
       </c>
-      <c r="CJ4" t="n">
+      <c r="CN4" t="n">
         <v>1702</v>
       </c>
-      <c r="CK4" t="n">
+      <c r="CO4" t="n">
         <v>3104</v>
       </c>
-      <c r="CL4" t="n">
+      <c r="CP4" t="n">
         <v>0</v>
       </c>
-      <c r="CM4" t="n">
+      <c r="CQ4" t="n">
         <v>6</v>
       </c>
-      <c r="CN4" t="n">
+      <c r="CR4" t="n">
         <v>15</v>
       </c>
-      <c r="CO4" t="n">
+      <c r="CS4" t="n">
         <v>143</v>
       </c>
     </row>
@@ -2079,27 +2135,39 @@
         <v>99.384</v>
       </c>
       <c r="CH5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL5" t="n">
         <v>1126</v>
       </c>
-      <c r="CI5" t="n">
+      <c r="CM5" t="n">
         <v>3873</v>
       </c>
-      <c r="CJ5" t="n">
+      <c r="CN5" t="n">
         <v>7536</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CO5" t="n">
         <v>15240</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CP5" t="n">
         <v>3</v>
       </c>
-      <c r="CM5" t="n">
+      <c r="CQ5" t="n">
         <v>64</v>
       </c>
-      <c r="CN5" t="n">
+      <c r="CR5" t="n">
         <v>336</v>
       </c>
-      <c r="CO5" t="n">
+      <c r="CS5" t="n">
         <v>1482</v>
       </c>
     </row>
@@ -2384,27 +2452,39 @@
         <v>98.961</v>
       </c>
       <c r="CH6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>35</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL6" t="n">
         <v>544</v>
       </c>
-      <c r="CI6" t="n">
+      <c r="CM6" t="n">
         <v>2123</v>
       </c>
-      <c r="CJ6" t="n">
+      <c r="CN6" t="n">
         <v>4431</v>
       </c>
-      <c r="CK6" t="n">
+      <c r="CO6" t="n">
         <v>9576</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CP6" t="n">
         <v>6</v>
       </c>
-      <c r="CM6" t="n">
+      <c r="CQ6" t="n">
         <v>41</v>
       </c>
-      <c r="CN6" t="n">
+      <c r="CR6" t="n">
         <v>125</v>
       </c>
-      <c r="CO6" t="n">
+      <c r="CS6" t="n">
         <v>597</v>
       </c>
     </row>
@@ -2689,27 +2769,39 @@
         <v>98.82899999999999</v>
       </c>
       <c r="CH7" t="n">
+        <v>27</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>44</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>29</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL7" t="n">
         <v>1102</v>
       </c>
-      <c r="CI7" t="n">
+      <c r="CM7" t="n">
         <v>3925</v>
       </c>
-      <c r="CJ7" t="n">
+      <c r="CN7" t="n">
         <v>8026</v>
       </c>
-      <c r="CK7" t="n">
+      <c r="CO7" t="n">
         <v>17168</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CP7" t="n">
         <v>2</v>
       </c>
-      <c r="CM7" t="n">
+      <c r="CQ7" t="n">
         <v>50</v>
       </c>
-      <c r="CN7" t="n">
+      <c r="CR7" t="n">
         <v>172</v>
       </c>
-      <c r="CO7" t="n">
+      <c r="CS7" t="n">
         <v>1039</v>
       </c>
     </row>
@@ -2994,27 +3086,39 @@
         <v>99.148</v>
       </c>
       <c r="CH8" t="n">
+        <v>57.715</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>32.265</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>499</v>
+      </c>
+      <c r="CL8" t="n">
         <v>545</v>
       </c>
-      <c r="CI8" t="n">
+      <c r="CM8" t="n">
         <v>1403</v>
       </c>
-      <c r="CJ8" t="n">
+      <c r="CN8" t="n">
         <v>2173</v>
       </c>
-      <c r="CK8" t="n">
+      <c r="CO8" t="n">
         <v>3774</v>
       </c>
-      <c r="CL8" t="n">
+      <c r="CP8" t="n">
         <v>5</v>
       </c>
-      <c r="CM8" t="n">
+      <c r="CQ8" t="n">
         <v>27</v>
       </c>
-      <c r="CN8" t="n">
+      <c r="CR8" t="n">
         <v>89</v>
       </c>
-      <c r="CO8" t="n">
+      <c r="CS8" t="n">
         <v>274</v>
       </c>
     </row>
@@ -3299,27 +3403,39 @@
         <v>99.199</v>
       </c>
       <c r="CH9" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL9" t="n">
         <v>717</v>
       </c>
-      <c r="CI9" t="n">
+      <c r="CM9" t="n">
         <v>3424</v>
       </c>
-      <c r="CJ9" t="n">
+      <c r="CN9" t="n">
         <v>7530</v>
       </c>
-      <c r="CK9" t="n">
+      <c r="CO9" t="n">
         <v>18467</v>
       </c>
-      <c r="CL9" t="n">
+      <c r="CP9" t="n">
         <v>26</v>
       </c>
-      <c r="CM9" t="n">
+      <c r="CQ9" t="n">
         <v>149</v>
       </c>
-      <c r="CN9" t="n">
+      <c r="CR9" t="n">
         <v>486</v>
       </c>
-      <c r="CO9" t="n">
+      <c r="CS9" t="n">
         <v>1780</v>
       </c>
     </row>
@@ -3604,27 +3720,39 @@
         <v>98.66500000000001</v>
       </c>
       <c r="CH10" t="n">
+        <v>44</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL10" t="n">
         <v>234</v>
       </c>
-      <c r="CI10" t="n">
+      <c r="CM10" t="n">
         <v>1239</v>
       </c>
-      <c r="CJ10" t="n">
+      <c r="CN10" t="n">
         <v>3798</v>
       </c>
-      <c r="CK10" t="n">
+      <c r="CO10" t="n">
         <v>14083</v>
       </c>
-      <c r="CL10" t="n">
+      <c r="CP10" t="n">
         <v>0</v>
       </c>
-      <c r="CM10" t="n">
+      <c r="CQ10" t="n">
         <v>21</v>
       </c>
-      <c r="CN10" t="n">
+      <c r="CR10" t="n">
         <v>87</v>
       </c>
-      <c r="CO10" t="n">
+      <c r="CS10" t="n">
         <v>468</v>
       </c>
     </row>
@@ -3909,27 +4037,39 @@
         <v>99.518</v>
       </c>
       <c r="CH11" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>25</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL11" t="n">
         <v>1849</v>
       </c>
-      <c r="CI11" t="n">
+      <c r="CM11" t="n">
         <v>6327</v>
       </c>
-      <c r="CJ11" t="n">
+      <c r="CN11" t="n">
         <v>11451</v>
       </c>
-      <c r="CK11" t="n">
+      <c r="CO11" t="n">
         <v>21181</v>
       </c>
-      <c r="CL11" t="n">
+      <c r="CP11" t="n">
         <v>19</v>
       </c>
-      <c r="CM11" t="n">
+      <c r="CQ11" t="n">
         <v>175</v>
       </c>
-      <c r="CN11" t="n">
+      <c r="CR11" t="n">
         <v>680</v>
       </c>
-      <c r="CO11" t="n">
+      <c r="CS11" t="n">
         <v>2741</v>
       </c>
     </row>
@@ -4214,27 +4354,39 @@
         <v>99.036</v>
       </c>
       <c r="CH12" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>500</v>
+      </c>
+      <c r="CL12" t="n">
         <v>623</v>
       </c>
-      <c r="CI12" t="n">
+      <c r="CM12" t="n">
         <v>2181</v>
       </c>
-      <c r="CJ12" t="n">
+      <c r="CN12" t="n">
         <v>3864</v>
       </c>
-      <c r="CK12" t="n">
+      <c r="CO12" t="n">
         <v>6943</v>
       </c>
-      <c r="CL12" t="n">
+      <c r="CP12" t="n">
         <v>4</v>
       </c>
-      <c r="CM12" t="n">
+      <c r="CQ12" t="n">
         <v>19</v>
       </c>
-      <c r="CN12" t="n">
+      <c r="CR12" t="n">
         <v>104</v>
       </c>
-      <c r="CO12" t="n">
+      <c r="CS12" t="n">
         <v>545</v>
       </c>
     </row>

--- a/football_odds/results/2026-09-14_predictions.xlsx
+++ b/football_odds/results/2026-09-14_predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS12"/>
+  <dimension ref="A1:CS28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -804,102 +804,102 @@
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
+          <t>ht_h</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>ht_d</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>ht_a</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>n_ht</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>tol_probs_1pct</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>tol_probs_2pct</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>tol_probs_3pct</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>tol_probs_5pct</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>tol_odds_1pct</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>tol_odds_2pct</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>tol_odds_3pct</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>tol_odds_5pct</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
           <t>similar_leagues_n</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>similar_leagues_hist_h</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>similar_leagues_hist_d</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>similar_leagues_hist_a</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>similar_leagues_adj_h</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>similar_leagues_adj_d</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>similar_leagues_adj_a</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>similar_leagues_avg_sim</t>
-        </is>
-      </c>
-      <c r="CH1" t="inlineStr">
-        <is>
-          <t>ht_h</t>
-        </is>
-      </c>
-      <c r="CI1" t="inlineStr">
-        <is>
-          <t>ht_d</t>
-        </is>
-      </c>
-      <c r="CJ1" t="inlineStr">
-        <is>
-          <t>ht_a</t>
-        </is>
-      </c>
-      <c r="CK1" t="inlineStr">
-        <is>
-          <t>n_ht</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>tol_probs_1pct</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>tol_probs_2pct</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>tol_probs_3pct</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>tol_probs_5pct</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>tol_odds_1pct</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>tol_odds_2pct</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>tol_odds_3pct</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>tol_odds_5pct</t>
         </is>
       </c>
     </row>
@@ -911,83 +911,83 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Huracan</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>2.58</v>
       </c>
       <c r="G2" t="n">
-        <v>5.86</v>
+        <v>2.77</v>
       </c>
       <c r="H2" t="n">
-        <v>13.15</v>
+        <v>2.98</v>
       </c>
       <c r="I2" t="n">
-        <v>76.866</v>
+        <v>35.75</v>
       </c>
       <c r="J2" t="n">
-        <v>16.003</v>
+        <v>33.298</v>
       </c>
       <c r="K2" t="n">
-        <v>7.131</v>
+        <v>30.952</v>
       </c>
       <c r="L2" t="n">
         <v>500</v>
       </c>
       <c r="M2" t="n">
-        <v>82.40000000000001</v>
+        <v>36</v>
       </c>
       <c r="N2" t="n">
-        <v>12.4</v>
+        <v>33.6</v>
       </c>
       <c r="O2" t="n">
-        <v>5.2</v>
+        <v>30.4</v>
       </c>
       <c r="P2" t="n">
-        <v>80.819</v>
+        <v>35.929</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.429</v>
+        <v>33.514</v>
       </c>
       <c r="R2" t="n">
-        <v>5.752</v>
+        <v>30.558</v>
       </c>
       <c r="S2" t="n">
-        <v>3.953</v>
+        <v>0.178</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.573</v>
+        <v>0.216</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.379</v>
+        <v>-0.394</v>
       </c>
       <c r="V2" t="n">
-        <v>57.8</v>
+        <v>34.4</v>
       </c>
       <c r="W2" t="n">
-        <v>42.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>41.2</v>
+        <v>46</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.992</v>
+        <v>2.096</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -996,95 +996,93 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>MODERATE HISTORICAL DEVIATION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>99.18300000000001</v>
+        <v>99.122</v>
       </c>
       <c r="AC2" t="n">
-        <v>99.15900000000001</v>
+        <v>99.074</v>
       </c>
       <c r="AD2" t="n">
-        <v>98.575</v>
+        <v>98.682</v>
       </c>
       <c r="AE2" t="n">
         <v>500</v>
       </c>
       <c r="AF2" t="n">
-        <v>78.819</v>
+        <v>31.914</v>
       </c>
       <c r="AG2" t="n">
-        <v>85.48699999999999</v>
+        <v>40.299</v>
       </c>
       <c r="AH2" t="n">
-        <v>9.795</v>
+        <v>29.599</v>
       </c>
       <c r="AI2" t="n">
-        <v>15.579</v>
+        <v>37.851</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.573</v>
+        <v>26.53</v>
       </c>
       <c r="AK2" t="n">
-        <v>7.51</v>
+        <v>34.569</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.237</v>
+        <v>2.783</v>
       </c>
       <c r="AM2" t="n">
-        <v>7.446</v>
+        <v>2.984</v>
       </c>
       <c r="AN2" t="n">
-        <v>17.386</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>55.789</v>
-      </c>
+        <v>3.273</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>largest deviation HOME +4.0 pp; n_eff=500; market outside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY -0.4 pp; n_eff=500; market inside 95% CI; avg similarity 99.1%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>db6e1ad90e9cfdb4</t>
+          <t>3eff8ca8a0b088ec</t>
         </is>
       </c>
       <c r="AS2" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.534</v>
+        <v>0.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>-3.603</v>
+        <v>0.302</v>
       </c>
       <c r="AV2" t="n">
-        <v>-1.931</v>
+        <v>-0.552</v>
       </c>
       <c r="AW2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.412</v>
+        <v>1.076</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.58</v>
+        <v>1.02</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.935</v>
+        <v>0.117</v>
       </c>
       <c r="BA2" t="n">
-        <v>-2.197</v>
+        <v>0.143</v>
       </c>
       <c r="BB2" t="n">
-        <v>-1.678</v>
+        <v>-0.267</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -1109,116 +1107,100 @@
         <v>200</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.003</v>
+        <v>0.79</v>
       </c>
       <c r="BJ2" t="n">
         <v>500</v>
       </c>
       <c r="BK2" t="n">
-        <v>82.40000000000001</v>
+        <v>36</v>
       </c>
       <c r="BL2" t="n">
-        <v>12.4</v>
+        <v>33.6</v>
       </c>
       <c r="BM2" t="n">
-        <v>5.2</v>
+        <v>30.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>80.819</v>
+        <v>35.929</v>
       </c>
       <c r="BO2" t="n">
-        <v>13.429</v>
+        <v>33.514</v>
       </c>
       <c r="BP2" t="n">
-        <v>5.752</v>
+        <v>30.558</v>
       </c>
       <c r="BQ2" t="n">
-        <v>99.18300000000001</v>
+        <v>99.122</v>
       </c>
       <c r="BR2" t="n">
-        <v>238</v>
+        <v>500</v>
       </c>
       <c r="BS2" t="n">
-        <v>79.83199999999999</v>
+        <v>33.2</v>
       </c>
       <c r="BT2" t="n">
-        <v>12.605</v>
+        <v>34</v>
       </c>
       <c r="BU2" t="n">
-        <v>7.563</v>
+        <v>32.8</v>
       </c>
       <c r="BV2" t="n">
-        <v>78.47799999999999</v>
+        <v>33.929</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.157</v>
+        <v>33.799</v>
       </c>
       <c r="BX2" t="n">
-        <v>7.366</v>
+        <v>32.272</v>
       </c>
       <c r="BY2" t="n">
-        <v>98.355</v>
+        <v>98.328</v>
       </c>
       <c r="BZ2" t="n">
-        <v>500</v>
+        <v>25.591</v>
       </c>
       <c r="CA2" t="n">
-        <v>79</v>
+        <v>50.787</v>
       </c>
       <c r="CB2" t="n">
-        <v>15.4</v>
+        <v>23.622</v>
       </c>
       <c r="CC2" t="n">
-        <v>5.6</v>
+        <v>254</v>
       </c>
       <c r="CD2" t="n">
-        <v>78.39</v>
+        <v>291</v>
       </c>
       <c r="CE2" t="n">
-        <v>15.572</v>
+        <v>1721</v>
       </c>
       <c r="CF2" t="n">
-        <v>6.038</v>
+        <v>5272</v>
       </c>
       <c r="CG2" t="n">
-        <v>98.896</v>
+        <v>23576</v>
       </c>
       <c r="CH2" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="CI2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="CJ2" t="n">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="CK2" t="n">
-        <v>500</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>349</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>1229</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>2084</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>3459</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>3</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>38</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>128</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1228,83 +1210,83 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>I1</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Santos Laguna</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Juarez</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5.71</v>
+        <v>1.94</v>
       </c>
       <c r="G3" t="n">
-        <v>3.98</v>
+        <v>3.66</v>
       </c>
       <c r="H3" t="n">
-        <v>1.56</v>
+        <v>3.28</v>
       </c>
       <c r="I3" t="n">
-        <v>16.407</v>
+        <v>47.136</v>
       </c>
       <c r="J3" t="n">
-        <v>23.539</v>
+        <v>24.985</v>
       </c>
       <c r="K3" t="n">
-        <v>60.054</v>
+        <v>27.879</v>
       </c>
       <c r="L3" t="n">
         <v>500</v>
       </c>
       <c r="M3" t="n">
-        <v>15.8</v>
+        <v>48.6</v>
       </c>
       <c r="N3" t="n">
-        <v>20.4</v>
+        <v>24.2</v>
       </c>
       <c r="O3" t="n">
-        <v>63.8</v>
+        <v>27.2</v>
       </c>
       <c r="P3" t="n">
-        <v>15.973</v>
+        <v>48.182</v>
       </c>
       <c r="Q3" t="n">
-        <v>21.297</v>
+        <v>24.424</v>
       </c>
       <c r="R3" t="n">
-        <v>62.73</v>
+        <v>27.394</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.434</v>
+        <v>1.046</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.242</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>2.676</v>
+        <v>-0.485</v>
       </c>
       <c r="V3" t="n">
-        <v>57.2</v>
+        <v>58.8</v>
       </c>
       <c r="W3" t="n">
-        <v>42.8</v>
+        <v>41.2</v>
       </c>
       <c r="X3" t="n">
-        <v>52.6</v>
+        <v>60.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.848</v>
+        <v>2.996</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
@@ -1317,91 +1299,89 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>99.074</v>
+        <v>99.396</v>
       </c>
       <c r="AC3" t="n">
-        <v>99.026</v>
+        <v>99.34699999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>98.456</v>
+        <v>99.044</v>
       </c>
       <c r="AE3" t="n">
         <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.865</v>
+        <v>44.246</v>
       </c>
       <c r="AG3" t="n">
-        <v>19.256</v>
+        <v>52.975</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.1</v>
+        <v>20.652</v>
       </c>
       <c r="AI3" t="n">
-        <v>24.152</v>
+        <v>28.142</v>
       </c>
       <c r="AJ3" t="n">
-        <v>59.497</v>
+        <v>23.484</v>
       </c>
       <c r="AK3" t="n">
-        <v>67.892</v>
+        <v>31.263</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.26</v>
+        <v>2.075</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.696</v>
+        <v>4.094</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.594</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>52.674</v>
-      </c>
+        <v>3.65</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +2.7 pp; n_eff=500; market inside 95% CI; avg similarity 99.1%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +1.0 pp; n_eff=500; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>f23324910d61ac31</t>
+          <t>2d4160582c274248</t>
         </is>
       </c>
       <c r="AS3" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.607</v>
+        <v>1.464</v>
       </c>
       <c r="AU3" t="n">
-        <v>-3.139</v>
+        <v>-0.785</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.746</v>
+        <v>-0.679</v>
       </c>
       <c r="AW3" t="n">
         <v>3</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.914</v>
+        <v>1.746</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.934</v>
+        <v>1.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.367</v>
+        <v>0.656</v>
       </c>
       <c r="BA3" t="n">
-        <v>-1.654</v>
+        <v>-0.405</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.71</v>
+        <v>-0.339</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
@@ -1426,116 +1406,100 @@
         <v>200</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.512</v>
       </c>
       <c r="BJ3" t="n">
         <v>500</v>
       </c>
       <c r="BK3" t="n">
-        <v>15.8</v>
+        <v>48.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>20.4</v>
+        <v>24.2</v>
       </c>
       <c r="BM3" t="n">
-        <v>63.8</v>
+        <v>27.2</v>
       </c>
       <c r="BN3" t="n">
-        <v>15.973</v>
+        <v>48.182</v>
       </c>
       <c r="BO3" t="n">
-        <v>21.297</v>
+        <v>24.424</v>
       </c>
       <c r="BP3" t="n">
-        <v>62.73</v>
+        <v>27.394</v>
       </c>
       <c r="BQ3" t="n">
-        <v>99.074</v>
+        <v>99.396</v>
       </c>
       <c r="BR3" t="n">
-        <v>232</v>
+        <v>309</v>
       </c>
       <c r="BS3" t="n">
-        <v>12.5</v>
+        <v>52.104</v>
       </c>
       <c r="BT3" t="n">
-        <v>20.69</v>
+        <v>30.097</v>
       </c>
       <c r="BU3" t="n">
-        <v>66.81</v>
+        <v>17.799</v>
       </c>
       <c r="BV3" t="n">
-        <v>14.309</v>
+        <v>50.152</v>
       </c>
       <c r="BW3" t="n">
-        <v>22.009</v>
+        <v>28.088</v>
       </c>
       <c r="BX3" t="n">
-        <v>63.682</v>
+        <v>21.76</v>
       </c>
       <c r="BY3" t="n">
-        <v>98.19199999999999</v>
+        <v>97.791</v>
       </c>
       <c r="BZ3" t="n">
-        <v>500</v>
+        <v>38.202</v>
       </c>
       <c r="CA3" t="n">
-        <v>16</v>
+        <v>38.577</v>
       </c>
       <c r="CB3" t="n">
-        <v>22</v>
+        <v>23.221</v>
       </c>
       <c r="CC3" t="n">
-        <v>62</v>
+        <v>267</v>
       </c>
       <c r="CD3" t="n">
-        <v>16.116</v>
+        <v>651</v>
       </c>
       <c r="CE3" t="n">
-        <v>22.44</v>
+        <v>3492</v>
       </c>
       <c r="CF3" t="n">
-        <v>61.444</v>
+        <v>10762</v>
       </c>
       <c r="CG3" t="n">
-        <v>98.786</v>
+        <v>34195</v>
       </c>
       <c r="CH3" t="n">
-        <v>14.83</v>
+        <v>3</v>
       </c>
       <c r="CI3" t="n">
-        <v>40.08</v>
+        <v>38</v>
       </c>
       <c r="CJ3" t="n">
-        <v>45.09</v>
+        <v>119</v>
       </c>
       <c r="CK3" t="n">
-        <v>499</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>265</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>969</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>1674</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>3021</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>5</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>32</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>98</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>299</v>
-      </c>
+        <v>856</v>
+      </c>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1545,83 +1509,83 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gaziantep</t>
+          <t>San Diego FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Fenerbahce</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.29</v>
+        <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.98</v>
+        <v>3.67</v>
       </c>
       <c r="H4" t="n">
-        <v>1.53</v>
+        <v>2.43</v>
       </c>
       <c r="I4" t="n">
-        <v>17.281</v>
+        <v>37.277</v>
       </c>
       <c r="J4" t="n">
-        <v>22.969</v>
+        <v>24.987</v>
       </c>
       <c r="K4" t="n">
-        <v>59.75</v>
+        <v>37.737</v>
       </c>
       <c r="L4" t="n">
         <v>500</v>
       </c>
       <c r="M4" t="n">
-        <v>16.8</v>
+        <v>38</v>
       </c>
       <c r="N4" t="n">
         <v>22.8</v>
       </c>
       <c r="O4" t="n">
-        <v>60.4</v>
+        <v>39.2</v>
       </c>
       <c r="P4" t="n">
-        <v>16.937</v>
+        <v>37.793</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.848</v>
+        <v>23.425</v>
       </c>
       <c r="R4" t="n">
-        <v>60.214</v>
+        <v>38.782</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.344</v>
+        <v>0.517</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.121</v>
+        <v>-1.562</v>
       </c>
       <c r="U4" t="n">
-        <v>0.464</v>
+        <v>1.045</v>
       </c>
       <c r="V4" t="n">
-        <v>58</v>
+        <v>61.6</v>
       </c>
       <c r="W4" t="n">
-        <v>42</v>
+        <v>38.4</v>
       </c>
       <c r="X4" t="n">
-        <v>53.6</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.902</v>
+        <v>3.254</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -1634,22 +1598,22 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>99.095</v>
+        <v>98.917</v>
       </c>
       <c r="AC4" t="n">
-        <v>99.057</v>
+        <v>98.83199999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>98.508</v>
+        <v>98.396</v>
       </c>
       <c r="AE4" t="n">
         <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.779</v>
+        <v>33.852</v>
       </c>
       <c r="AG4" t="n">
-        <v>20.328</v>
+        <v>42.331</v>
       </c>
       <c r="AH4" t="n">
         <v>19.338</v>
@@ -1658,67 +1622,65 @@
         <v>26.677</v>
       </c>
       <c r="AJ4" t="n">
-        <v>56.05</v>
+        <v>35.019</v>
       </c>
       <c r="AK4" t="n">
-        <v>64.592</v>
+        <v>43.546</v>
       </c>
       <c r="AL4" t="n">
-        <v>5.904</v>
+        <v>2.646</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.377</v>
+        <v>4.269</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.661</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>54.545</v>
-      </c>
+        <v>2.579</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +0.5 pp; n_eff=500; market inside 95% CI; avg similarity 99.1%; backtest: no significant improvement over market</t>
+          <t>largest deviation DRAW -1.6 pp; n_eff=500; market inside 95% CI; avg similarity 98.9%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1abf57910ccbf973</t>
+          <t>f1b4fe896a3dd4bc</t>
         </is>
       </c>
       <c r="AS4" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.481</v>
+        <v>0.723</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.169</v>
+        <v>-2.187</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.65</v>
+        <v>1.463</v>
       </c>
       <c r="AW4" t="n">
         <v>3</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.954</v>
+        <v>1.592</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.948</v>
+        <v>1.662</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.285</v>
+        <v>0.335</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.09</v>
+        <v>-1.129</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.296</v>
+        <v>0.675</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
@@ -1743,116 +1705,100 @@
         <v>200</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.767</v>
+        <v>0.259</v>
       </c>
       <c r="BJ4" t="n">
         <v>500</v>
       </c>
       <c r="BK4" t="n">
-        <v>16.8</v>
+        <v>38</v>
       </c>
       <c r="BL4" t="n">
         <v>22.8</v>
       </c>
       <c r="BM4" t="n">
-        <v>60.4</v>
+        <v>39.2</v>
       </c>
       <c r="BN4" t="n">
-        <v>16.937</v>
+        <v>37.793</v>
       </c>
       <c r="BO4" t="n">
-        <v>22.848</v>
+        <v>23.425</v>
       </c>
       <c r="BP4" t="n">
-        <v>60.214</v>
+        <v>38.782</v>
       </c>
       <c r="BQ4" t="n">
-        <v>99.095</v>
+        <v>98.917</v>
       </c>
       <c r="BR4" t="n">
-        <v>114</v>
+        <v>322</v>
       </c>
       <c r="BS4" t="n">
-        <v>14.035</v>
+        <v>40.373</v>
       </c>
       <c r="BT4" t="n">
-        <v>17.544</v>
+        <v>21.739</v>
       </c>
       <c r="BU4" t="n">
-        <v>68.42100000000001</v>
+        <v>37.888</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.103</v>
+        <v>39.186</v>
       </c>
       <c r="BW4" t="n">
-        <v>20.999</v>
+        <v>22.983</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.898</v>
+        <v>37.83</v>
       </c>
       <c r="BY4" t="n">
-        <v>98.136</v>
+        <v>97.986</v>
       </c>
       <c r="BZ4" t="n">
-        <v>500</v>
+        <v>34.328</v>
       </c>
       <c r="CA4" t="n">
-        <v>16</v>
+        <v>34.701</v>
       </c>
       <c r="CB4" t="n">
-        <v>20.4</v>
+        <v>30.97</v>
       </c>
       <c r="CC4" t="n">
-        <v>63.6</v>
+        <v>268</v>
       </c>
       <c r="CD4" t="n">
-        <v>16.366</v>
+        <v>165</v>
       </c>
       <c r="CE4" t="n">
-        <v>21.134</v>
+        <v>1143</v>
       </c>
       <c r="CF4" t="n">
-        <v>62.5</v>
+        <v>4105</v>
       </c>
       <c r="CG4" t="n">
-        <v>98.372</v>
+        <v>21416</v>
       </c>
       <c r="CH4" t="n">
-        <v>15.462</v>
+        <v>3</v>
       </c>
       <c r="CI4" t="n">
-        <v>39.558</v>
+        <v>15</v>
       </c>
       <c r="CJ4" t="n">
-        <v>44.98</v>
+        <v>56</v>
       </c>
       <c r="CK4" t="n">
-        <v>498</v>
-      </c>
-      <c r="CL4" t="n">
-        <v>280</v>
-      </c>
-      <c r="CM4" t="n">
-        <v>944</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>1702</v>
-      </c>
-      <c r="CO4" t="n">
-        <v>3104</v>
-      </c>
-      <c r="CP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>15</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>143</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1862,83 +1808,83 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>02:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Guadalajara Chivas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Estrela</t>
+          <t>UNAM Pumas</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>1.43</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>4.19</v>
       </c>
       <c r="H5" t="n">
-        <v>2.48</v>
+        <v>6.13</v>
       </c>
       <c r="I5" t="n">
-        <v>34.101</v>
+        <v>63.509</v>
       </c>
       <c r="J5" t="n">
-        <v>28.773</v>
+        <v>21.675</v>
       </c>
       <c r="K5" t="n">
-        <v>37.126</v>
+        <v>14.815</v>
       </c>
       <c r="L5" t="n">
         <v>500</v>
       </c>
       <c r="M5" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="N5" t="n">
-        <v>29.6</v>
+        <v>24.8</v>
       </c>
       <c r="O5" t="n">
-        <v>36.4</v>
+        <v>14.2</v>
       </c>
       <c r="P5" t="n">
-        <v>34.029</v>
+        <v>61.717</v>
       </c>
       <c r="Q5" t="n">
-        <v>29.364</v>
+        <v>23.907</v>
       </c>
       <c r="R5" t="n">
-        <v>36.607</v>
+        <v>14.376</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.07199999999999999</v>
+        <v>-1.792</v>
       </c>
       <c r="T5" t="n">
-        <v>0.591</v>
+        <v>2.232</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.519</v>
+        <v>-0.44</v>
       </c>
       <c r="V5" t="n">
-        <v>48.2</v>
+        <v>55.4</v>
       </c>
       <c r="W5" t="n">
-        <v>51.8</v>
+        <v>44.6</v>
       </c>
       <c r="X5" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
@@ -1951,47 +1897,45 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>99.55200000000001</v>
+        <v>99.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>99.51900000000001</v>
+        <v>99.601</v>
       </c>
       <c r="AD5" t="n">
-        <v>99.315</v>
+        <v>99.348</v>
       </c>
       <c r="AE5" t="n">
         <v>500</v>
       </c>
       <c r="AF5" t="n">
-        <v>29.984</v>
+        <v>56.656</v>
       </c>
       <c r="AG5" t="n">
-        <v>38.26</v>
+        <v>65.176</v>
       </c>
       <c r="AH5" t="n">
-        <v>25.766</v>
+        <v>21.216</v>
       </c>
       <c r="AI5" t="n">
-        <v>33.745</v>
+        <v>28.768</v>
       </c>
       <c r="AJ5" t="n">
-        <v>32.301</v>
+        <v>11.413</v>
       </c>
       <c r="AK5" t="n">
-        <v>40.706</v>
+        <v>17.533</v>
       </c>
       <c r="AL5" t="n">
-        <v>2.939</v>
+        <v>1.62</v>
       </c>
       <c r="AM5" t="n">
-        <v>3.406</v>
+        <v>4.183</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.732</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>45.722</v>
-      </c>
+        <v>6.956</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
           <t>draw</t>
@@ -1999,43 +1943,43 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>largest deviation DRAW +0.6 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation DRAW +2.2 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1ff929e515a2b577</t>
+          <t>f794fffe562384e4</t>
         </is>
       </c>
       <c r="AS5" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.101</v>
+        <v>-2.509</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.827</v>
+        <v>3.125</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.726</v>
+        <v>-0.615</v>
       </c>
       <c r="AW5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.242</v>
+        <v>1.996</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.298</v>
+        <v>0.904</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.048</v>
+        <v>-1.166</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.409</v>
+        <v>1.696</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.336</v>
+        <v>-0.387</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
@@ -2060,116 +2004,100 @@
         <v>200</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="BJ5" t="n">
         <v>500</v>
       </c>
       <c r="BK5" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="BL5" t="n">
-        <v>29.6</v>
+        <v>24.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>36.4</v>
+        <v>14.2</v>
       </c>
       <c r="BN5" t="n">
-        <v>34.029</v>
+        <v>61.717</v>
       </c>
       <c r="BO5" t="n">
-        <v>29.364</v>
+        <v>23.907</v>
       </c>
       <c r="BP5" t="n">
-        <v>36.607</v>
+        <v>14.376</v>
       </c>
       <c r="BQ5" t="n">
-        <v>99.55200000000001</v>
+        <v>99.62</v>
       </c>
       <c r="BR5" t="n">
-        <v>351</v>
+        <v>304</v>
       </c>
       <c r="BS5" t="n">
-        <v>30.769</v>
+        <v>64.474</v>
       </c>
       <c r="BT5" t="n">
-        <v>31.054</v>
+        <v>22.368</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.177</v>
+        <v>13.158</v>
       </c>
       <c r="BV5" t="n">
-        <v>31.979</v>
+        <v>64.09099999999999</v>
       </c>
       <c r="BW5" t="n">
-        <v>30.226</v>
+        <v>22.093</v>
       </c>
       <c r="BX5" t="n">
-        <v>37.795</v>
+        <v>13.816</v>
       </c>
       <c r="BY5" t="n">
-        <v>98.06100000000001</v>
+        <v>98.244</v>
       </c>
       <c r="BZ5" t="n">
-        <v>500</v>
+        <v>43.73</v>
       </c>
       <c r="CA5" t="n">
-        <v>33.6</v>
+        <v>36.656</v>
       </c>
       <c r="CB5" t="n">
-        <v>29.6</v>
+        <v>19.614</v>
       </c>
       <c r="CC5" t="n">
-        <v>36.8</v>
+        <v>311</v>
       </c>
       <c r="CD5" t="n">
-        <v>33.743</v>
+        <v>1470</v>
       </c>
       <c r="CE5" t="n">
-        <v>29.364</v>
+        <v>5048</v>
       </c>
       <c r="CF5" t="n">
-        <v>36.893</v>
+        <v>9032</v>
       </c>
       <c r="CG5" t="n">
-        <v>99.384</v>
+        <v>16586</v>
       </c>
       <c r="CH5" t="n">
-        <v>25.8</v>
+        <v>2</v>
       </c>
       <c r="CI5" t="n">
-        <v>46.4</v>
+        <v>16</v>
       </c>
       <c r="CJ5" t="n">
-        <v>27.8</v>
+        <v>105</v>
       </c>
       <c r="CK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>1126</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>3873</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>7536</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>15240</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>64</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>336</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>1482</v>
-      </c>
+        <v>910</v>
+      </c>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2179,83 +2107,83 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SP2</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Celta B</t>
+          <t>Inter Turku</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.22</v>
+        <v>1.69</v>
       </c>
       <c r="G6" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>28.442</v>
+        <v>53.809</v>
       </c>
       <c r="J6" t="n">
-        <v>29.929</v>
+        <v>25.982</v>
       </c>
       <c r="K6" t="n">
-        <v>41.629</v>
+        <v>20.208</v>
       </c>
       <c r="L6" t="n">
         <v>500</v>
       </c>
       <c r="M6" t="n">
-        <v>27.6</v>
+        <v>52.6</v>
       </c>
       <c r="N6" t="n">
-        <v>27.8</v>
+        <v>25.6</v>
       </c>
       <c r="O6" t="n">
-        <v>44.6</v>
+        <v>21.8</v>
       </c>
       <c r="P6" t="n">
-        <v>27.841</v>
+        <v>52.946</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.408</v>
+        <v>25.709</v>
       </c>
       <c r="R6" t="n">
-        <v>43.751</v>
+        <v>21.345</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.601</v>
+        <v>-0.864</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.521</v>
+        <v>-0.273</v>
       </c>
       <c r="U6" t="n">
-        <v>2.122</v>
+        <v>1.137</v>
       </c>
       <c r="V6" t="n">
-        <v>42.2</v>
+        <v>46.6</v>
       </c>
       <c r="W6" t="n">
-        <v>57.8</v>
+        <v>53.4</v>
       </c>
       <c r="X6" t="n">
-        <v>50.2</v>
+        <v>47.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.384</v>
+        <v>2.524</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -2268,47 +2196,45 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>99.371</v>
+        <v>99.733</v>
       </c>
       <c r="AC6" t="n">
-        <v>99.346</v>
+        <v>99.724</v>
       </c>
       <c r="AD6" t="n">
-        <v>99.005</v>
+        <v>99.563</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>23.864</v>
+        <v>48.22</v>
       </c>
       <c r="AG6" t="n">
-        <v>31.678</v>
+        <v>56.94</v>
       </c>
       <c r="AH6" t="n">
-        <v>24.054</v>
+        <v>21.971</v>
       </c>
       <c r="AI6" t="n">
-        <v>31.885</v>
+        <v>29.601</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40.301</v>
+        <v>18.403</v>
       </c>
       <c r="AK6" t="n">
-        <v>48.982</v>
+        <v>25.627</v>
       </c>
       <c r="AL6" t="n">
-        <v>3.592</v>
+        <v>1.889</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.52</v>
+        <v>3.89</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.286</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>44.297</v>
-      </c>
+        <v>4.685</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
         <is>
           <t>away</t>
@@ -2316,43 +2242,43 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +2.1 pp; n_eff=500; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY +1.1 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>27608b27528b27c8</t>
+          <t>e72f50832c795c9b</t>
         </is>
       </c>
       <c r="AS6" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.842</v>
+        <v>-1.209</v>
       </c>
       <c r="AU6" t="n">
-        <v>-2.129</v>
+        <v>-0.382</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.971</v>
+        <v>1.592</v>
       </c>
       <c r="AW6" t="n">
         <v>2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.02</v>
+        <v>1.602</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.364</v>
+        <v>0.922</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.417</v>
+        <v>-0.542</v>
       </c>
       <c r="BA6" t="n">
-        <v>-1.04</v>
+        <v>-0.195</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.348</v>
+        <v>0.886</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
@@ -2377,116 +2303,100 @@
         <v>200</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.178</v>
+        <v>0.375</v>
       </c>
       <c r="BJ6" t="n">
         <v>500</v>
       </c>
       <c r="BK6" t="n">
-        <v>27.6</v>
+        <v>52.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>27.8</v>
+        <v>25.6</v>
       </c>
       <c r="BM6" t="n">
-        <v>44.6</v>
+        <v>21.8</v>
       </c>
       <c r="BN6" t="n">
-        <v>27.841</v>
+        <v>52.946</v>
       </c>
       <c r="BO6" t="n">
-        <v>28.408</v>
+        <v>25.709</v>
       </c>
       <c r="BP6" t="n">
-        <v>43.751</v>
+        <v>21.345</v>
       </c>
       <c r="BQ6" t="n">
-        <v>99.371</v>
+        <v>99.733</v>
       </c>
       <c r="BR6" t="n">
-        <v>304</v>
+        <v>241</v>
       </c>
       <c r="BS6" t="n">
-        <v>27.303</v>
+        <v>55.187</v>
       </c>
       <c r="BT6" t="n">
-        <v>29.934</v>
+        <v>25.311</v>
       </c>
       <c r="BU6" t="n">
-        <v>42.763</v>
+        <v>19.502</v>
       </c>
       <c r="BV6" t="n">
-        <v>27.755</v>
+        <v>54.562</v>
       </c>
       <c r="BW6" t="n">
-        <v>29.932</v>
+        <v>25.616</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.313</v>
+        <v>19.822</v>
       </c>
       <c r="BY6" t="n">
-        <v>98.18600000000001</v>
+        <v>98.229</v>
       </c>
       <c r="BZ6" t="n">
-        <v>500</v>
+        <v>35.484</v>
       </c>
       <c r="CA6" t="n">
-        <v>30</v>
+        <v>43.695</v>
       </c>
       <c r="CB6" t="n">
-        <v>25.6</v>
+        <v>20.821</v>
       </c>
       <c r="CC6" t="n">
-        <v>44.4</v>
+        <v>341</v>
       </c>
       <c r="CD6" t="n">
-        <v>29.555</v>
+        <v>2955</v>
       </c>
       <c r="CE6" t="n">
-        <v>26.837</v>
+        <v>9737</v>
       </c>
       <c r="CF6" t="n">
-        <v>43.608</v>
+        <v>17450</v>
       </c>
       <c r="CG6" t="n">
-        <v>98.961</v>
+        <v>31912</v>
       </c>
       <c r="CH6" t="n">
-        <v>21.6</v>
+        <v>4</v>
       </c>
       <c r="CI6" t="n">
-        <v>43.4</v>
+        <v>80</v>
       </c>
       <c r="CJ6" t="n">
-        <v>35</v>
+        <v>394</v>
       </c>
       <c r="CK6" t="n">
-        <v>500</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>544</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2123</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>4431</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>9576</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>6</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>41</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>125</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>597</v>
-      </c>
+        <v>2378</v>
+      </c>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2496,83 +2406,83 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>U. Cluj</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Otelul</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>1.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="H7" t="n">
-        <v>2.56</v>
+        <v>4.23</v>
       </c>
       <c r="I7" t="n">
-        <v>35.778</v>
+        <v>53.359</v>
       </c>
       <c r="J7" t="n">
-        <v>28.444</v>
+        <v>25.197</v>
       </c>
       <c r="K7" t="n">
-        <v>35.778</v>
+        <v>21.444</v>
       </c>
       <c r="L7" t="n">
         <v>500</v>
       </c>
       <c r="M7" t="n">
-        <v>33.6</v>
+        <v>55.8</v>
       </c>
       <c r="N7" t="n">
-        <v>30.4</v>
+        <v>26.2</v>
       </c>
       <c r="O7" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="P7" t="n">
-        <v>34.222</v>
+        <v>55.102</v>
       </c>
       <c r="Q7" t="n">
-        <v>29.841</v>
+        <v>25.913</v>
       </c>
       <c r="R7" t="n">
-        <v>35.937</v>
+        <v>18.984</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.556</v>
+        <v>1.744</v>
       </c>
       <c r="T7" t="n">
-        <v>1.397</v>
+        <v>0.716</v>
       </c>
       <c r="U7" t="n">
-        <v>0.159</v>
+        <v>-2.46</v>
       </c>
       <c r="V7" t="n">
-        <v>49.2</v>
+        <v>48.2</v>
       </c>
       <c r="W7" t="n">
-        <v>50.8</v>
+        <v>51.8</v>
       </c>
       <c r="X7" t="n">
-        <v>53.8</v>
+        <v>52</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.624</v>
+        <v>2.776</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -2585,91 +2495,89 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>99.565</v>
+        <v>99.68600000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>99.544</v>
+        <v>99.673</v>
       </c>
       <c r="AD7" t="n">
-        <v>99.312</v>
+        <v>99.505</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>29.599</v>
+        <v>51.419</v>
       </c>
       <c r="AG7" t="n">
-        <v>37.851</v>
+        <v>60.092</v>
       </c>
       <c r="AH7" t="n">
-        <v>26.53</v>
+        <v>22.538</v>
       </c>
       <c r="AI7" t="n">
-        <v>34.569</v>
+        <v>30.225</v>
       </c>
       <c r="AJ7" t="n">
-        <v>31.914</v>
+        <v>14.88</v>
       </c>
       <c r="AK7" t="n">
-        <v>40.299</v>
+        <v>21.608</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.922</v>
+        <v>1.815</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.351</v>
+        <v>3.859</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.783</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>48.925</v>
-      </c>
+        <v>5.268</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>largest deviation HOME -1.6 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY -2.5 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>3457cab3a4a3d38b</t>
+          <t>977e15f6d52581d6</t>
         </is>
       </c>
       <c r="AS7" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT7" t="n">
-        <v>-2.178</v>
+        <v>2.441</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.956</v>
+        <v>1.003</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.222</v>
+        <v>-3.444</v>
       </c>
       <c r="AW7" t="n">
         <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.29</v>
+        <v>1.792</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.334</v>
+        <v>0.984</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-1.016</v>
+        <v>1.094</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.969</v>
+        <v>0.517</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.104</v>
+        <v>-1.876</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
@@ -2694,116 +2602,100 @@
         <v>200</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.31</v>
+        <v>0.061</v>
       </c>
       <c r="BJ7" t="n">
         <v>500</v>
       </c>
       <c r="BK7" t="n">
-        <v>33.6</v>
+        <v>55.8</v>
       </c>
       <c r="BL7" t="n">
-        <v>30.4</v>
+        <v>26.2</v>
       </c>
       <c r="BM7" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="BN7" t="n">
-        <v>34.222</v>
+        <v>55.102</v>
       </c>
       <c r="BO7" t="n">
-        <v>29.841</v>
+        <v>25.913</v>
       </c>
       <c r="BP7" t="n">
-        <v>35.937</v>
+        <v>18.984</v>
       </c>
       <c r="BQ7" t="n">
-        <v>99.565</v>
+        <v>99.68600000000001</v>
       </c>
       <c r="BR7" t="n">
-        <v>403</v>
+        <v>312</v>
       </c>
       <c r="BS7" t="n">
-        <v>32.754</v>
+        <v>51.282</v>
       </c>
       <c r="BT7" t="n">
-        <v>32.754</v>
+        <v>27.885</v>
       </c>
       <c r="BU7" t="n">
-        <v>34.491</v>
+        <v>20.833</v>
       </c>
       <c r="BV7" t="n">
-        <v>33.757</v>
+        <v>52.093</v>
       </c>
       <c r="BW7" t="n">
-        <v>31.325</v>
+        <v>26.835</v>
       </c>
       <c r="BX7" t="n">
-        <v>34.918</v>
+        <v>21.072</v>
       </c>
       <c r="BY7" t="n">
-        <v>97.81699999999999</v>
+        <v>97.95</v>
       </c>
       <c r="BZ7" t="n">
-        <v>500</v>
+        <v>41.64</v>
       </c>
       <c r="CA7" t="n">
-        <v>36.2</v>
+        <v>40.379</v>
       </c>
       <c r="CB7" t="n">
-        <v>29.6</v>
+        <v>17.981</v>
       </c>
       <c r="CC7" t="n">
-        <v>34.2</v>
+        <v>317</v>
       </c>
       <c r="CD7" t="n">
-        <v>36.079</v>
+        <v>2444</v>
       </c>
       <c r="CE7" t="n">
-        <v>29.27</v>
+        <v>8720</v>
       </c>
       <c r="CF7" t="n">
-        <v>34.651</v>
+        <v>16709</v>
       </c>
       <c r="CG7" t="n">
-        <v>98.82899999999999</v>
+        <v>32526</v>
       </c>
       <c r="CH7" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="CI7" t="n">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="CJ7" t="n">
-        <v>29</v>
+        <v>262</v>
       </c>
       <c r="CK7" t="n">
-        <v>500</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1102</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>3925</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>8026</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>17168</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>50</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>172</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>1039</v>
-      </c>
+        <v>1739</v>
+      </c>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2813,7 +2705,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2823,31 +2715,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G8" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="H8" t="n">
-        <v>11.15</v>
+        <v>13.15</v>
       </c>
       <c r="I8" t="n">
-        <v>75.42700000000001</v>
+        <v>76.866</v>
       </c>
       <c r="J8" t="n">
-        <v>16.117</v>
+        <v>16.003</v>
       </c>
       <c r="K8" t="n">
-        <v>8.456</v>
+        <v>7.131</v>
       </c>
       <c r="L8" t="n">
         <v>500</v>
@@ -2862,34 +2754,34 @@
         <v>5.4</v>
       </c>
       <c r="P8" t="n">
-        <v>79.265</v>
+        <v>79.676</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.462</v>
+        <v>14.429</v>
       </c>
       <c r="R8" t="n">
-        <v>6.273</v>
+        <v>5.895</v>
       </c>
       <c r="S8" t="n">
-        <v>3.838</v>
+        <v>2.81</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.655</v>
+        <v>-1.573</v>
       </c>
       <c r="U8" t="n">
-        <v>-2.183</v>
+        <v>-1.237</v>
       </c>
       <c r="V8" t="n">
-        <v>64.40000000000001</v>
+        <v>55.2</v>
       </c>
       <c r="W8" t="n">
-        <v>35.6</v>
+        <v>44.8</v>
       </c>
       <c r="X8" t="n">
-        <v>48.4</v>
+        <v>39.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.202</v>
+        <v>2.916</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
@@ -2898,17 +2790,17 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>MODERATE HISTORICAL DEVIATION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>99.375</v>
+        <v>99.321</v>
       </c>
       <c r="AC8" t="n">
-        <v>99.349</v>
+        <v>99.288</v>
       </c>
       <c r="AD8" t="n">
-        <v>98.90000000000001</v>
+        <v>98.80200000000001</v>
       </c>
       <c r="AE8" t="n">
         <v>500</v>
@@ -2932,16 +2824,16 @@
         <v>7.743</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.262</v>
+        <v>1.255</v>
       </c>
       <c r="AM8" t="n">
-        <v>6.915</v>
+        <v>6.93</v>
       </c>
       <c r="AN8" t="n">
-        <v>15.941</v>
+        <v>16.965</v>
       </c>
       <c r="AO8" t="n">
-        <v>61.266</v>
+        <v>55.789</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -2950,43 +2842,43 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>largest deviation HOME +3.8 pp; n_eff=500; market outside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +2.8 pp; n_eff=500; market outside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>5872458712f110b9</t>
+          <t>db6e1ad90e9cfdb4</t>
         </is>
       </c>
       <c r="AS8" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.373</v>
+        <v>3.934</v>
       </c>
       <c r="AU8" t="n">
-        <v>-2.317</v>
+        <v>-2.203</v>
       </c>
       <c r="AV8" t="n">
-        <v>-3.056</v>
+        <v>-1.731</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.518</v>
+        <v>2.356</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.791</v>
+        <v>2.086</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.409</v>
+        <v>-1.343</v>
       </c>
       <c r="BB8" t="n">
-        <v>-2.456</v>
+        <v>-1.504</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
@@ -3011,7 +2903,7 @@
         <v>200</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.005</v>
+        <v>0.037</v>
       </c>
       <c r="BJ8" t="n">
         <v>500</v>
@@ -3026,100 +2918,100 @@
         <v>5.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>79.265</v>
+        <v>79.676</v>
       </c>
       <c r="BO8" t="n">
-        <v>14.462</v>
+        <v>14.429</v>
       </c>
       <c r="BP8" t="n">
-        <v>6.273</v>
+        <v>5.895</v>
       </c>
       <c r="BQ8" t="n">
-        <v>99.375</v>
+        <v>99.321</v>
       </c>
       <c r="BR8" t="n">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="BS8" t="n">
-        <v>78.626</v>
+        <v>79.83199999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>13.74</v>
+        <v>12.605</v>
       </c>
       <c r="BU8" t="n">
-        <v>7.634</v>
+        <v>7.563</v>
       </c>
       <c r="BV8" t="n">
-        <v>77.241</v>
+        <v>78.47799999999999</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.769</v>
+        <v>14.157</v>
       </c>
       <c r="BX8" t="n">
-        <v>7.99</v>
+        <v>7.366</v>
       </c>
       <c r="BY8" t="n">
-        <v>98.422</v>
+        <v>98.355</v>
       </c>
       <c r="BZ8" t="n">
-        <v>500</v>
+        <v>60.784</v>
       </c>
       <c r="CA8" t="n">
-        <v>79.40000000000001</v>
+        <v>30.252</v>
       </c>
       <c r="CB8" t="n">
-        <v>13.4</v>
+        <v>8.964</v>
       </c>
       <c r="CC8" t="n">
-        <v>7.2</v>
+        <v>357</v>
       </c>
       <c r="CD8" t="n">
-        <v>78.265</v>
+        <v>515</v>
       </c>
       <c r="CE8" t="n">
-        <v>14.176</v>
+        <v>1872</v>
       </c>
       <c r="CF8" t="n">
-        <v>7.559</v>
+        <v>3247</v>
       </c>
       <c r="CG8" t="n">
-        <v>99.148</v>
+        <v>5482</v>
       </c>
       <c r="CH8" t="n">
-        <v>57.715</v>
+        <v>6</v>
       </c>
       <c r="CI8" t="n">
-        <v>32.265</v>
+        <v>26</v>
       </c>
       <c r="CJ8" t="n">
-        <v>10.02</v>
+        <v>60</v>
       </c>
       <c r="CK8" t="n">
-        <v>499</v>
+        <v>189</v>
       </c>
       <c r="CL8" t="n">
-        <v>545</v>
+        <v>500</v>
       </c>
       <c r="CM8" t="n">
-        <v>1403</v>
+        <v>79</v>
       </c>
       <c r="CN8" t="n">
-        <v>2173</v>
+        <v>15.4</v>
       </c>
       <c r="CO8" t="n">
-        <v>3774</v>
+        <v>5.6</v>
       </c>
       <c r="CP8" t="n">
-        <v>5</v>
+        <v>78.39</v>
       </c>
       <c r="CQ8" t="n">
-        <v>27</v>
+        <v>15.572</v>
       </c>
       <c r="CR8" t="n">
-        <v>89</v>
+        <v>6.038</v>
       </c>
       <c r="CS8" t="n">
-        <v>274</v>
+        <v>98.896</v>
       </c>
     </row>
     <row r="9">
@@ -3130,83 +3022,83 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>E0</t>
+          <t>I1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Leeds</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.38</v>
+        <v>5.71</v>
       </c>
       <c r="G9" t="n">
-        <v>3.45</v>
+        <v>3.98</v>
       </c>
       <c r="H9" t="n">
-        <v>2.81</v>
+        <v>1.56</v>
       </c>
       <c r="I9" t="n">
-        <v>39.419</v>
+        <v>16.407</v>
       </c>
       <c r="J9" t="n">
-        <v>27.194</v>
+        <v>23.539</v>
       </c>
       <c r="K9" t="n">
-        <v>33.387</v>
+        <v>60.054</v>
       </c>
       <c r="L9" t="n">
         <v>500</v>
       </c>
       <c r="M9" t="n">
-        <v>35.4</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>30.2</v>
+        <v>22.4</v>
       </c>
       <c r="O9" t="n">
-        <v>34.4</v>
+        <v>63.6</v>
       </c>
       <c r="P9" t="n">
-        <v>36.548</v>
+        <v>14.688</v>
       </c>
       <c r="Q9" t="n">
-        <v>29.341</v>
+        <v>22.725</v>
       </c>
       <c r="R9" t="n">
-        <v>34.111</v>
+        <v>62.587</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.871</v>
+        <v>-1.719</v>
       </c>
       <c r="T9" t="n">
-        <v>2.147</v>
+        <v>-0.8129999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.723</v>
+        <v>2.533</v>
       </c>
       <c r="V9" t="n">
-        <v>54</v>
+        <v>56.6</v>
       </c>
       <c r="W9" t="n">
-        <v>46</v>
+        <v>43.4</v>
       </c>
       <c r="X9" t="n">
-        <v>60</v>
+        <v>52.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.896</v>
+        <v>2.812</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -3219,91 +3111,91 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>99.441</v>
+        <v>99.349</v>
       </c>
       <c r="AC9" t="n">
-        <v>99.41</v>
+        <v>99.312</v>
       </c>
       <c r="AD9" t="n">
-        <v>99.129</v>
+        <v>98.89700000000001</v>
       </c>
       <c r="AE9" t="n">
         <v>500</v>
       </c>
       <c r="AF9" t="n">
-        <v>31.334</v>
+        <v>11.232</v>
       </c>
       <c r="AG9" t="n">
-        <v>39.688</v>
+        <v>17.317</v>
       </c>
       <c r="AH9" t="n">
-        <v>26.339</v>
+        <v>18.964</v>
       </c>
       <c r="AI9" t="n">
-        <v>34.363</v>
+        <v>26.257</v>
       </c>
       <c r="AJ9" t="n">
-        <v>30.369</v>
+        <v>59.294</v>
       </c>
       <c r="AK9" t="n">
-        <v>38.669</v>
+        <v>67.699</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.736</v>
+        <v>6.808</v>
       </c>
       <c r="AM9" t="n">
-        <v>3.408</v>
+        <v>4.4</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.932</v>
+        <v>1.598</v>
       </c>
       <c r="AO9" t="n">
-        <v>53.333</v>
+        <v>52.674</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>largest deviation HOME -2.9 pp; n_eff=500; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY +2.5 pp; n_eff=500; market inside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6f9127235505df86</t>
+          <t>f23324910d61ac31</t>
         </is>
       </c>
       <c r="AS9" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT9" t="n">
-        <v>-4.019</v>
+        <v>-2.407</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.006</v>
+        <v>-1.139</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.013</v>
+        <v>3.546</v>
       </c>
       <c r="AW9" t="n">
         <v>3</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.482</v>
+        <v>0.86</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.414</v>
+        <v>1.952</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.839</v>
+        <v>-1.453</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.511</v>
+        <v>-0.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.48</v>
+        <v>1.619</v>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
@@ -3328,115 +3220,115 @@
         <v>200</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.066</v>
+        <v>0.105</v>
       </c>
       <c r="BJ9" t="n">
         <v>500</v>
       </c>
       <c r="BK9" t="n">
-        <v>35.4</v>
+        <v>14</v>
       </c>
       <c r="BL9" t="n">
-        <v>30.2</v>
+        <v>22.4</v>
       </c>
       <c r="BM9" t="n">
-        <v>34.4</v>
+        <v>63.6</v>
       </c>
       <c r="BN9" t="n">
-        <v>36.548</v>
+        <v>14.688</v>
       </c>
       <c r="BO9" t="n">
-        <v>29.341</v>
+        <v>22.725</v>
       </c>
       <c r="BP9" t="n">
-        <v>34.111</v>
+        <v>62.587</v>
       </c>
       <c r="BQ9" t="n">
-        <v>99.441</v>
+        <v>99.349</v>
       </c>
       <c r="BR9" t="n">
-        <v>500</v>
+        <v>232</v>
       </c>
       <c r="BS9" t="n">
-        <v>37.8</v>
+        <v>12.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>32.6</v>
+        <v>20.69</v>
       </c>
       <c r="BU9" t="n">
-        <v>29.6</v>
+        <v>66.81</v>
       </c>
       <c r="BV9" t="n">
-        <v>38.263</v>
+        <v>14.309</v>
       </c>
       <c r="BW9" t="n">
-        <v>31.055</v>
+        <v>22.009</v>
       </c>
       <c r="BX9" t="n">
-        <v>30.682</v>
+        <v>63.682</v>
       </c>
       <c r="BY9" t="n">
-        <v>98.08499999999999</v>
+        <v>98.19199999999999</v>
       </c>
       <c r="BZ9" t="n">
-        <v>500</v>
+        <v>16.562</v>
       </c>
       <c r="CA9" t="n">
-        <v>36.6</v>
+        <v>37.812</v>
       </c>
       <c r="CB9" t="n">
-        <v>28.6</v>
+        <v>45.625</v>
       </c>
       <c r="CC9" t="n">
-        <v>34.8</v>
+        <v>320</v>
       </c>
       <c r="CD9" t="n">
-        <v>37.406</v>
+        <v>521</v>
       </c>
       <c r="CE9" t="n">
-        <v>28.198</v>
+        <v>1790</v>
       </c>
       <c r="CF9" t="n">
-        <v>34.396</v>
+        <v>3078</v>
       </c>
       <c r="CG9" t="n">
-        <v>99.199</v>
+        <v>5615</v>
       </c>
       <c r="CH9" t="n">
-        <v>32.6</v>
+        <v>13</v>
       </c>
       <c r="CI9" t="n">
-        <v>43.8</v>
+        <v>72</v>
       </c>
       <c r="CJ9" t="n">
-        <v>23.6</v>
+        <v>209</v>
       </c>
       <c r="CK9" t="n">
-        <v>500</v>
+        <v>604</v>
       </c>
       <c r="CL9" t="n">
-        <v>717</v>
+        <v>500</v>
       </c>
       <c r="CM9" t="n">
-        <v>3424</v>
+        <v>16</v>
       </c>
       <c r="CN9" t="n">
-        <v>7530</v>
+        <v>22</v>
       </c>
       <c r="CO9" t="n">
-        <v>18467</v>
+        <v>62</v>
       </c>
       <c r="CP9" t="n">
-        <v>26</v>
+        <v>16.116</v>
       </c>
       <c r="CQ9" t="n">
-        <v>149</v>
+        <v>22.44</v>
       </c>
       <c r="CR9" t="n">
-        <v>486</v>
+        <v>61.444</v>
       </c>
       <c r="CS9" t="n">
-        <v>1780</v>
+        <v>98.786</v>
       </c>
     </row>
     <row r="10">
@@ -3447,83 +3339,83 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SP1</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Brondby</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>3.79</v>
+        <v>3.63</v>
       </c>
       <c r="H10" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="I10" t="n">
-        <v>49.618</v>
+        <v>49.422</v>
       </c>
       <c r="J10" t="n">
-        <v>24.613</v>
+        <v>25.324</v>
       </c>
       <c r="K10" t="n">
-        <v>25.769</v>
+        <v>25.254</v>
       </c>
       <c r="L10" t="n">
         <v>500</v>
       </c>
       <c r="M10" t="n">
-        <v>54.6</v>
+        <v>50.2</v>
       </c>
       <c r="N10" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="O10" t="n">
-        <v>19.8</v>
+        <v>24.6</v>
       </c>
       <c r="P10" t="n">
-        <v>53.177</v>
+        <v>49.978</v>
       </c>
       <c r="Q10" t="n">
-        <v>25.318</v>
+        <v>25.235</v>
       </c>
       <c r="R10" t="n">
-        <v>21.505</v>
+        <v>24.787</v>
       </c>
       <c r="S10" t="n">
-        <v>3.558</v>
+        <v>0.556</v>
       </c>
       <c r="T10" t="n">
-        <v>0.705</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-4.263</v>
+        <v>-0.467</v>
       </c>
       <c r="V10" t="n">
-        <v>56.6</v>
+        <v>53.8</v>
       </c>
       <c r="W10" t="n">
-        <v>43.4</v>
+        <v>46.2</v>
       </c>
       <c r="X10" t="n">
-        <v>60.4</v>
+        <v>58</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.006</v>
+        <v>2.884</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -3532,95 +3424,93 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>MODERATE HISTORICAL DEVIATION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>99.032</v>
+        <v>99.599</v>
       </c>
       <c r="AC10" t="n">
-        <v>98.97499999999999</v>
+        <v>99.57599999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>98.524</v>
+        <v>99.369</v>
       </c>
       <c r="AE10" t="n">
         <v>500</v>
       </c>
       <c r="AF10" t="n">
-        <v>50.217</v>
+        <v>45.833</v>
       </c>
       <c r="AG10" t="n">
-        <v>58.913</v>
+        <v>54.564</v>
       </c>
       <c r="AH10" t="n">
-        <v>21.971</v>
+        <v>21.593</v>
       </c>
       <c r="AI10" t="n">
-        <v>29.601</v>
+        <v>29.185</v>
       </c>
       <c r="AJ10" t="n">
-        <v>16.543</v>
+        <v>21.028</v>
       </c>
       <c r="AK10" t="n">
-        <v>23.517</v>
+        <v>28.559</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.881</v>
+        <v>2.001</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.95</v>
+        <v>3.963</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>60.513</v>
-      </c>
+        <v>4.034</v>
+      </c>
+      <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>largest deviation AWAY -4.3 pp; n_eff=500; market outside 95% CI; avg similarity 99.0%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +0.6 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>ec8992136f5ba2ef</t>
+          <t>a67def971a901c71</t>
         </is>
       </c>
       <c r="AS10" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.982</v>
+        <v>0.778</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.987</v>
+        <v>-0.124</v>
       </c>
       <c r="AV10" t="n">
-        <v>-5.969</v>
+        <v>-0.654</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.858</v>
+        <v>1.714</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.148</v>
+        <v>1.17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.228</v>
+        <v>0.348</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.512</v>
+        <v>-0.064</v>
       </c>
       <c r="BB10" t="n">
-        <v>-3.052</v>
+        <v>-0.337</v>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
@@ -3645,116 +3535,100 @@
         <v>200</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.002</v>
+        <v>0.728</v>
       </c>
       <c r="BJ10" t="n">
         <v>500</v>
       </c>
       <c r="BK10" t="n">
-        <v>54.6</v>
+        <v>50.2</v>
       </c>
       <c r="BL10" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="BM10" t="n">
-        <v>19.8</v>
+        <v>24.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>53.177</v>
+        <v>49.978</v>
       </c>
       <c r="BO10" t="n">
-        <v>25.318</v>
+        <v>25.235</v>
       </c>
       <c r="BP10" t="n">
-        <v>21.505</v>
+        <v>24.787</v>
       </c>
       <c r="BQ10" t="n">
-        <v>99.032</v>
+        <v>99.599</v>
       </c>
       <c r="BR10" t="n">
-        <v>187</v>
+        <v>307</v>
       </c>
       <c r="BS10" t="n">
-        <v>52.941</v>
+        <v>53.094</v>
       </c>
       <c r="BT10" t="n">
-        <v>24.064</v>
+        <v>26.71</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.995</v>
+        <v>20.195</v>
       </c>
       <c r="BV10" t="n">
-        <v>51.224</v>
+        <v>51.646</v>
       </c>
       <c r="BW10" t="n">
-        <v>24.348</v>
+        <v>26.163</v>
       </c>
       <c r="BX10" t="n">
-        <v>24.428</v>
+        <v>22.191</v>
       </c>
       <c r="BY10" t="n">
-        <v>97.721</v>
+        <v>98.03700000000001</v>
       </c>
       <c r="BZ10" t="n">
-        <v>500</v>
+        <v>39.085</v>
       </c>
       <c r="CA10" t="n">
-        <v>50.2</v>
+        <v>40.493</v>
       </c>
       <c r="CB10" t="n">
-        <v>25.8</v>
+        <v>20.423</v>
       </c>
       <c r="CC10" t="n">
-        <v>24</v>
+        <v>284</v>
       </c>
       <c r="CD10" t="n">
-        <v>50.034</v>
+        <v>1417</v>
       </c>
       <c r="CE10" t="n">
-        <v>25.461</v>
+        <v>6247</v>
       </c>
       <c r="CF10" t="n">
-        <v>24.505</v>
+        <v>15064</v>
       </c>
       <c r="CG10" t="n">
-        <v>98.66500000000001</v>
+        <v>36467</v>
       </c>
       <c r="CH10" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="CI10" t="n">
-        <v>36.2</v>
+        <v>127</v>
       </c>
       <c r="CJ10" t="n">
-        <v>19.8</v>
+        <v>405</v>
       </c>
       <c r="CK10" t="n">
-        <v>500</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>234</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>1239</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>3798</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>14083</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>21</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>87</v>
-      </c>
-      <c r="CS10" t="n">
-        <v>468</v>
-      </c>
+        <v>2245</v>
+      </c>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3764,83 +3638,83 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Moreirense</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Maritimo</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>1.16</v>
       </c>
       <c r="G11" t="n">
-        <v>3.12</v>
+        <v>7.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.88</v>
+        <v>12.15</v>
       </c>
       <c r="I11" t="n">
-        <v>38.424</v>
+        <v>79.581</v>
       </c>
       <c r="J11" t="n">
-        <v>29.557</v>
+        <v>12.821</v>
       </c>
       <c r="K11" t="n">
-        <v>32.02</v>
+        <v>7.598</v>
       </c>
       <c r="L11" t="n">
         <v>500</v>
       </c>
       <c r="M11" t="n">
-        <v>41</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>30.4</v>
+        <v>11.2</v>
       </c>
       <c r="O11" t="n">
-        <v>28.6</v>
+        <v>5.4</v>
       </c>
       <c r="P11" t="n">
-        <v>40.264</v>
+        <v>82.309</v>
       </c>
       <c r="Q11" t="n">
-        <v>30.159</v>
+        <v>11.663</v>
       </c>
       <c r="R11" t="n">
-        <v>29.577</v>
+        <v>6.028</v>
       </c>
       <c r="S11" t="n">
-        <v>1.84</v>
+        <v>2.728</v>
       </c>
       <c r="T11" t="n">
-        <v>0.602</v>
+        <v>-1.158</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.443</v>
+        <v>-1.57</v>
       </c>
       <c r="V11" t="n">
-        <v>43</v>
+        <v>71.2</v>
       </c>
       <c r="W11" t="n">
-        <v>57</v>
+        <v>28.8</v>
       </c>
       <c r="X11" t="n">
-        <v>49</v>
+        <v>53.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.362</v>
+        <v>3.642</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
@@ -3853,91 +3727,89 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>99.64700000000001</v>
+        <v>99.16500000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>99.616</v>
+        <v>99.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>99.45099999999999</v>
+        <v>98.49299999999999</v>
       </c>
       <c r="AE11" t="n">
         <v>500</v>
       </c>
       <c r="AF11" t="n">
-        <v>36.773</v>
+        <v>79.886</v>
       </c>
       <c r="AG11" t="n">
-        <v>45.364</v>
+        <v>86.404</v>
       </c>
       <c r="AH11" t="n">
-        <v>26.53</v>
+        <v>8.726000000000001</v>
       </c>
       <c r="AI11" t="n">
-        <v>34.569</v>
+        <v>14.265</v>
       </c>
       <c r="AJ11" t="n">
-        <v>24.814</v>
+        <v>3.737</v>
       </c>
       <c r="AK11" t="n">
-        <v>32.712</v>
+        <v>7.743</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.484</v>
+        <v>1.215</v>
       </c>
       <c r="AM11" t="n">
-        <v>3.316</v>
+        <v>8.574</v>
       </c>
       <c r="AN11" t="n">
-        <v>3.381</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>41.995</v>
-      </c>
+        <v>16.589</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>largest deviation AWAY -2.4 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +2.7 pp; n_eff=500; market outside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>ea486369b4abba95</t>
+          <t>0b6c938375e07bc5</t>
         </is>
       </c>
       <c r="AS11" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.576</v>
+        <v>3.819</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.843</v>
+        <v>-1.621</v>
       </c>
       <c r="AV11" t="n">
-        <v>-3.42</v>
+        <v>-2.198</v>
       </c>
       <c r="AW11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.3</v>
+        <v>2.874</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.062</v>
+        <v>0.768</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.184</v>
+        <v>2.119</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.413</v>
+        <v>-1.084</v>
       </c>
       <c r="BB11" t="n">
-        <v>-1.639</v>
+        <v>-1.855</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
@@ -3962,116 +3834,100 @@
         <v>200</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.101</v>
+        <v>0.034</v>
       </c>
       <c r="BJ11" t="n">
         <v>500</v>
       </c>
       <c r="BK11" t="n">
-        <v>41</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>30.4</v>
+        <v>11.2</v>
       </c>
       <c r="BM11" t="n">
-        <v>28.6</v>
+        <v>5.4</v>
       </c>
       <c r="BN11" t="n">
-        <v>40.264</v>
+        <v>82.309</v>
       </c>
       <c r="BO11" t="n">
-        <v>30.159</v>
+        <v>11.663</v>
       </c>
       <c r="BP11" t="n">
-        <v>29.577</v>
+        <v>6.028</v>
       </c>
       <c r="BQ11" t="n">
-        <v>99.64700000000001</v>
+        <v>99.16500000000001</v>
       </c>
       <c r="BR11" t="n">
-        <v>500</v>
+        <v>60</v>
       </c>
       <c r="BS11" t="n">
-        <v>38.4</v>
+        <v>78.333</v>
       </c>
       <c r="BT11" t="n">
-        <v>29.4</v>
+        <v>15</v>
       </c>
       <c r="BU11" t="n">
-        <v>32.2</v>
+        <v>6.667</v>
       </c>
       <c r="BV11" t="n">
-        <v>38.407</v>
+        <v>79.29300000000001</v>
       </c>
       <c r="BW11" t="n">
-        <v>29.445</v>
+        <v>13.324</v>
       </c>
       <c r="BX11" t="n">
-        <v>32.148</v>
+        <v>7.383</v>
       </c>
       <c r="BY11" t="n">
-        <v>98.669</v>
+        <v>98.303</v>
       </c>
       <c r="BZ11" t="n">
-        <v>500</v>
+        <v>61.081</v>
       </c>
       <c r="CA11" t="n">
-        <v>40.4</v>
+        <v>28.919</v>
       </c>
       <c r="CB11" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="CC11" t="n">
-        <v>29.6</v>
+        <v>370</v>
       </c>
       <c r="CD11" t="n">
-        <v>39.835</v>
+        <v>342</v>
       </c>
       <c r="CE11" t="n">
-        <v>29.873</v>
+        <v>1469</v>
       </c>
       <c r="CF11" t="n">
-        <v>30.291</v>
+        <v>2534</v>
       </c>
       <c r="CG11" t="n">
-        <v>99.518</v>
+        <v>4324</v>
       </c>
       <c r="CH11" t="n">
-        <v>32.8</v>
+        <v>0</v>
       </c>
       <c r="CI11" t="n">
-        <v>42.2</v>
+        <v>4</v>
       </c>
       <c r="CJ11" t="n">
         <v>25</v>
       </c>
       <c r="CK11" t="n">
-        <v>500</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>1849</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>6327</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>11451</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>21181</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>19</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>175</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>680</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>2741</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4081,83 +3937,83 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sp Braga</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.44</v>
+        <v>2.27</v>
       </c>
       <c r="G12" t="n">
-        <v>4.3</v>
+        <v>3.47</v>
       </c>
       <c r="H12" t="n">
-        <v>6.41</v>
+        <v>2.73</v>
       </c>
       <c r="I12" t="n">
-        <v>64.122</v>
+        <v>40.23</v>
       </c>
       <c r="J12" t="n">
-        <v>21.473</v>
+        <v>26.318</v>
       </c>
       <c r="K12" t="n">
-        <v>14.405</v>
+        <v>33.452</v>
       </c>
       <c r="L12" t="n">
         <v>500</v>
       </c>
       <c r="M12" t="n">
-        <v>63.8</v>
+        <v>35</v>
       </c>
       <c r="N12" t="n">
-        <v>24.2</v>
+        <v>28.6</v>
       </c>
       <c r="O12" t="n">
-        <v>12</v>
+        <v>36.4</v>
       </c>
       <c r="P12" t="n">
-        <v>63.892</v>
+        <v>36.494</v>
       </c>
       <c r="Q12" t="n">
-        <v>23.421</v>
+        <v>27.948</v>
       </c>
       <c r="R12" t="n">
-        <v>12.687</v>
+        <v>35.558</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.23</v>
+        <v>-3.736</v>
       </c>
       <c r="T12" t="n">
-        <v>1.948</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.718</v>
+        <v>2.106</v>
       </c>
       <c r="V12" t="n">
-        <v>53.4</v>
+        <v>57.4</v>
       </c>
       <c r="W12" t="n">
-        <v>46.6</v>
+        <v>42.6</v>
       </c>
       <c r="X12" t="n">
-        <v>51.8</v>
+        <v>59</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.92</v>
+        <v>2.932</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -4166,95 +4022,93 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>MODERATE HISTORICAL DEVIATION</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>99.411</v>
+        <v>99.553</v>
       </c>
       <c r="AC12" t="n">
-        <v>99.383</v>
+        <v>99.52</v>
       </c>
       <c r="AD12" t="n">
-        <v>98.971</v>
+        <v>99.313</v>
       </c>
       <c r="AE12" t="n">
         <v>500</v>
       </c>
       <c r="AF12" t="n">
-        <v>59.497</v>
+        <v>30.948</v>
       </c>
       <c r="AG12" t="n">
-        <v>67.892</v>
+        <v>39.281</v>
       </c>
       <c r="AH12" t="n">
-        <v>20.652</v>
+        <v>24.814</v>
       </c>
       <c r="AI12" t="n">
-        <v>28.142</v>
+        <v>32.712</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9.436999999999999</v>
+        <v>32.301</v>
       </c>
       <c r="AK12" t="n">
-        <v>15.142</v>
+        <v>40.706</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.565</v>
+        <v>2.74</v>
       </c>
       <c r="AM12" t="n">
-        <v>4.27</v>
+        <v>3.578</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.882</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>55.585</v>
-      </c>
+        <v>2.812</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>largest deviation DRAW +1.9 pp; n_eff=500; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME -3.7 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>984031c9c9d7c31d</t>
+          <t>7cbefd862b05884b</t>
         </is>
       </c>
       <c r="AS12" t="n">
-        <v>83984</v>
+        <v>179331</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0.322</v>
+        <v>-5.23</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.727</v>
+        <v>2.282</v>
       </c>
       <c r="AV12" t="n">
-        <v>-2.405</v>
+        <v>2.948</v>
       </c>
       <c r="AW12" t="n">
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.09</v>
+        <v>1.464</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.83</v>
+        <v>1.468</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.15</v>
+        <v>-2.385</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.485</v>
+        <v>1.159</v>
       </c>
       <c r="BB12" t="n">
-        <v>-1.531</v>
+        <v>1.397</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
@@ -4279,116 +4133,5046 @@
         <v>200</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.126</v>
+        <v>0.017</v>
       </c>
       <c r="BJ12" t="n">
         <v>500</v>
       </c>
       <c r="BK12" t="n">
-        <v>63.8</v>
+        <v>35</v>
       </c>
       <c r="BL12" t="n">
-        <v>24.2</v>
+        <v>28.6</v>
       </c>
       <c r="BM12" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>36.494</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>27.948</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>35.558</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>99.553</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>307</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>40.391</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>30.293</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>29.316</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>40.328</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>28.725</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>30.947</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>97.744</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>28.889</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>40.952</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>30.159</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>315</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>1121</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>5189</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>13975</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>37026</v>
+      </c>
+      <c r="CH12" t="n">
         <v>12</v>
       </c>
-      <c r="BN12" t="n">
-        <v>63.892</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>23.421</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>12.687</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>99.411</v>
-      </c>
-      <c r="BR12" t="n">
+      <c r="CI12" t="n">
+        <v>94</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>310</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1515</v>
+      </c>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Djurgarden</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GAIS</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="I13" t="n">
+        <v>58.845</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="K13" t="n">
+        <v>18.545</v>
+      </c>
+      <c r="L13" t="n">
+        <v>500</v>
+      </c>
+      <c r="M13" t="n">
+        <v>65</v>
+      </c>
+      <c r="N13" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>63.241</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>19.889</v>
+      </c>
+      <c r="R13" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.397</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-2.722</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-1.675</v>
+      </c>
+      <c r="V13" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="X13" t="n">
+        <v>57</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>3.084</v>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>MODERATE HISTORICAL DEVIATION</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>99.57599999999999</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>99.55</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>99.313</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>60.719</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>69.05200000000001</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>15.618</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>22.458</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>19.685</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>5.028</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>5.928</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>largest deviation HOME +4.4 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>3a153314a8745a5e</t>
+        </is>
+      </c>
+      <c r="AS13" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.155</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>-2.345</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.797</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-2.037</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-1.349</v>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF13" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>65</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>63.241</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>19.889</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>99.57599999999999</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>310</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>62.258</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>16.452</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>60.919</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>21.808</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>17.273</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>98.017</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>51.724</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>32.759</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>15.517</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>290</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>1201</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>4815</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>10704</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>23025</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>12</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>59</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>216</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1198</v>
+      </c>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SWE</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="I14" t="n">
+        <v>65.919</v>
+      </c>
+      <c r="J14" t="n">
+        <v>19.962</v>
+      </c>
+      <c r="K14" t="n">
+        <v>14.118</v>
+      </c>
+      <c r="L14" t="n">
+        <v>500</v>
+      </c>
+      <c r="M14" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>18</v>
+      </c>
+      <c r="O14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>69.691</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>18.561</v>
+      </c>
+      <c r="R14" t="n">
+        <v>11.748</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.772</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-1.402</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="V14" t="n">
+        <v>64</v>
+      </c>
+      <c r="W14" t="n">
+        <v>36</v>
+      </c>
+      <c r="X14" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>3.244</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>MODERATE HISTORICAL DEVIATION</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>99.527</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>99.504</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>99.199</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>67.081</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>74.996</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>21.608</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>8.372</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>13.826</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>5.388</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>8.512</v>
+      </c>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>largest deviation HOME +3.8 pp; n_eff=500; market outside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>45f884ffde8307c7</t>
+        </is>
+      </c>
+      <c r="AS14" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.281</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>-1.962</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-3.318</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>2.358</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.491</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>-1.098</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>-2.131</v>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF14" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>69.691</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>18.561</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>11.748</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>99.527</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>258</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>63.566</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>22.481</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>13.953</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>64.59399999999999</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>21.381</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>14.025</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>98.122</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>51.815</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>36.634</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>11.551</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>303</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>961</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>3602</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>7068</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>13553</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>8</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>30</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>142</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>666</v>
+      </c>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Gaziantep</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I15" t="n">
+        <v>17.281</v>
+      </c>
+      <c r="J15" t="n">
+        <v>22.969</v>
+      </c>
+      <c r="K15" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>500</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>22</v>
+      </c>
+      <c r="O15" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>16.795</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>22.277</v>
+      </c>
+      <c r="R15" t="n">
+        <v>60.929</v>
+      </c>
+      <c r="S15" t="n">
+        <v>-0.487</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-0.6919999999999999</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="V15" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="W15" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.834</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>99.291</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>98.923</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13.596</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>20.114</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>25.837</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>57.061</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>65.565</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>5.954</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>4.489</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>54.545</v>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>largest deviation AWAY +1.2 pp; n_eff=500; market inside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>1abf57910ccbf973</t>
+        </is>
+      </c>
+      <c r="AS15" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.681</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>-0.969</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0.403</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>-0.515</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF15" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>16.795</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>22.277</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>60.929</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>114</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>14.035</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>17.544</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>68.42100000000001</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>16.103</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>20.999</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>62.898</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>98.136</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>14.545</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>39.394</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>46.061</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>330</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>542</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>1796</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>3187</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>5817</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>2</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>24</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>74</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>411</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>16</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>16.366</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>21.134</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>98.372</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Rio Ave</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Estrela</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I16" t="n">
+        <v>34.101</v>
+      </c>
+      <c r="J16" t="n">
+        <v>28.773</v>
+      </c>
+      <c r="K16" t="n">
+        <v>37.126</v>
+      </c>
+      <c r="L16" t="n">
+        <v>500</v>
+      </c>
+      <c r="M16" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="O16" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>35.029</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>26.649</v>
+      </c>
+      <c r="R16" t="n">
+        <v>38.322</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.928</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-2.123</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.196</v>
+      </c>
+      <c r="V16" t="n">
+        <v>48</v>
+      </c>
+      <c r="W16" t="n">
+        <v>52</v>
+      </c>
+      <c r="X16" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.578</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>99.744</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>99.729</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>99.59699999999999</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>31.334</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>39.688</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>29.809</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>43.141</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.855</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>3.752</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.609</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>45.722</v>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>largest deviation DRAW -2.1 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>1ff929e515a2b577</t>
+        </is>
+      </c>
+      <c r="AS16" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1.299</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>-2.973</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.674</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>-1.468</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF16" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>35.029</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>26.649</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>38.322</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>99.744</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>351</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>30.769</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>31.054</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>38.177</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>31.979</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>30.226</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>37.795</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>98.06100000000001</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>24.501</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>44.444</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>31.054</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>351</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>2940</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>9608</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>17920</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>35265</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>46</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>380</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1349</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>4783</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>33.743</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>29.364</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>36.893</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>99.384</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ROU</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Petrolul</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>63.402</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21.587</v>
+      </c>
+      <c r="K17" t="n">
+        <v>15.011</v>
+      </c>
+      <c r="L17" t="n">
+        <v>500</v>
+      </c>
+      <c r="M17" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>62.115</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>24.168</v>
+      </c>
+      <c r="R17" t="n">
+        <v>13.717</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-1.287</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.581</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-1.293</v>
+      </c>
+      <c r="V17" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.004</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>99.611</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>99.595</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>99.34</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>57.264</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>65.759</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21.593</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>29.185</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>10.512</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>4.138</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>largest deviation DRAW +2.6 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>faa4003141757259</t>
+        </is>
+      </c>
+      <c r="AS17" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>-1.802</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.613</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-1.811</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>-0.837</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>-1.134</v>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF17" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>62.115</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>24.168</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>13.717</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>99.611</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>249</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>64.25700000000001</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>13.253</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>63.876</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>22.088</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>14.036</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>97.998</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>45.283</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>35.535</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>19.182</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>318</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>1428</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>4947</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>9022</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>16679</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>14</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>97</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>819</v>
+      </c>
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SP2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Celta B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>28.442</v>
+      </c>
+      <c r="J18" t="n">
+        <v>29.929</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41.629</v>
+      </c>
+      <c r="L18" t="n">
+        <v>500</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="N18" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>29.698</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>28.837</v>
+      </c>
+      <c r="R18" t="n">
+        <v>41.465</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.256</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-1.092</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-0.163</v>
+      </c>
+      <c r="V18" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.412</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>99.548</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>99.53100000000001</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>99.297</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>26.339</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>34.363</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24.624</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>32.506</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>37.164</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>45.767</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>3.367</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>3.468</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.412</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>44.297</v>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>largest deviation HOME +1.3 pp; n_eff=500; market inside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>27608b27528b27c8</t>
+        </is>
+      </c>
+      <c r="AS18" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1.758</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-1.529</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-0.229</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0.747</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>-0.104</v>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF18" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>29.698</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>28.837</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>41.465</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>99.548</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>304</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>27.303</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>29.934</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>42.763</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>27.755</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>29.932</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>42.313</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>98.18600000000001</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>26.263</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>42.088</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>297</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>1091</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>4668</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>10196</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>22390</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>7</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>69</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>279</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>1475</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>30</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>29.555</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>26.837</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>43.608</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>98.961</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Red Star</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Metz</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I19" t="n">
+        <v>35.778</v>
+      </c>
+      <c r="J19" t="n">
+        <v>28.444</v>
+      </c>
+      <c r="K19" t="n">
+        <v>35.778</v>
+      </c>
+      <c r="L19" t="n">
+        <v>500</v>
+      </c>
+      <c r="M19" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="N19" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P19" t="n">
+        <v>35.508</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>26.556</v>
+      </c>
+      <c r="R19" t="n">
+        <v>37.937</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-1.889</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.159</v>
+      </c>
+      <c r="V19" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="W19" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.604</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>99.736</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>99.605</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>31.334</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>39.688</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>22.16</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>29.809</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>34.63</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>43.141</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.816</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>3.766</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.636</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>48.925</v>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>largest deviation AWAY +2.2 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>3457cab3a4a3d38b</t>
+        </is>
+      </c>
+      <c r="AS19" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>-0.378</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>-2.644</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.022</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.324</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>-0.176</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>-1.311</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF19" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>35.508</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>26.556</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>37.937</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>403</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>32.754</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>32.754</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>34.491</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>33.757</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>31.325</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>34.918</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>97.81699999999999</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>25.137</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>43.443</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>31.421</v>
+      </c>
+      <c r="CC19" t="n">
+        <v>366</v>
+      </c>
+      <c r="CD19" t="n">
+        <v>3008</v>
+      </c>
+      <c r="CE19" t="n">
+        <v>10049</v>
+      </c>
+      <c r="CF19" t="n">
+        <v>19196</v>
+      </c>
+      <c r="CG19" t="n">
+        <v>38782</v>
+      </c>
+      <c r="CH19" t="n">
+        <v>29</v>
+      </c>
+      <c r="CI19" t="n">
+        <v>318</v>
+      </c>
+      <c r="CJ19" t="n">
+        <v>881</v>
+      </c>
+      <c r="CK19" t="n">
+        <v>3889</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="CN19" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="CO19" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="CP19" t="n">
+        <v>36.079</v>
+      </c>
+      <c r="CQ19" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="CR19" t="n">
+        <v>34.651</v>
+      </c>
+      <c r="CS19" t="n">
+        <v>98.82899999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G20" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="H20" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="I20" t="n">
+        <v>75.42700000000001</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.117</v>
+      </c>
+      <c r="K20" t="n">
+        <v>8.456</v>
+      </c>
+      <c r="L20" t="n">
+        <v>500</v>
+      </c>
+      <c r="M20" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P20" t="n">
+        <v>80.693</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>13.605</v>
+      </c>
+      <c r="R20" t="n">
+        <v>5.702</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.266</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-2.512</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-2.754</v>
+      </c>
+      <c r="V20" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="W20" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="X20" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.228</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>MODERATE HISTORICAL DEVIATION</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>99.508</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>99.497</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>99.122</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>79.245</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>85.855</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>9.973000000000001</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>15.797</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>3.084</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>6.808</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.539</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>61.266</v>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>largest deviation HOME +5.3 pp; n_eff=500; market outside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market; downgraded to MODERATE (backtest or similarity gate)</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>5872458712f110b9</t>
+        </is>
+      </c>
+      <c r="AS20" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7.373</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>-3.517</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-3.856</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>3.829</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>-2.139</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>-3.099</v>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF20" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>80.693</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>13.605</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>5.702</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>99.508</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>262</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>78.626</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="BU20" t="n">
+        <v>7.634</v>
+      </c>
+      <c r="BV20" t="n">
+        <v>77.241</v>
+      </c>
+      <c r="BW20" t="n">
+        <v>14.769</v>
+      </c>
+      <c r="BX20" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="BY20" t="n">
+        <v>98.422</v>
+      </c>
+      <c r="BZ20" t="n">
+        <v>56.125</v>
+      </c>
+      <c r="CA20" t="n">
+        <v>34.188</v>
+      </c>
+      <c r="CB20" t="n">
+        <v>9.686999999999999</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>351</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>864</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>2281</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>3600</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>6311</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>5</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>42</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>137</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>434</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="CP20" t="n">
+        <v>78.265</v>
+      </c>
+      <c r="CQ20" t="n">
+        <v>14.176</v>
+      </c>
+      <c r="CR20" t="n">
+        <v>7.559</v>
+      </c>
+      <c r="CS20" t="n">
+        <v>99.148</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>E0</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="I21" t="n">
+        <v>39.419</v>
+      </c>
+      <c r="J21" t="n">
+        <v>27.194</v>
+      </c>
+      <c r="K21" t="n">
+        <v>33.387</v>
+      </c>
+      <c r="L21" t="n">
+        <v>500</v>
+      </c>
+      <c r="M21" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>38.263</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>26.627</v>
+      </c>
+      <c r="R21" t="n">
+        <v>35.111</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-1.157</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.5669999999999999</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.723</v>
+      </c>
+      <c r="V21" t="n">
+        <v>54</v>
+      </c>
+      <c r="W21" t="n">
+        <v>46</v>
+      </c>
+      <c r="X21" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.862</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>99.658</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>99.637</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>99.471</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>33.658</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>42.128</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22.727</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>30.433</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>31.721</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>40.096</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.614</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>3.756</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.848</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>53.333</v>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>largest deviation AWAY +1.7 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>6f9127235505df86</t>
+        </is>
+      </c>
+      <c r="AS21" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>-1.619</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>-0.794</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.413</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.346</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>-0.741</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-0.399</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.144</v>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF21" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>38.263</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>26.627</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>35.111</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>99.658</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>500</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="BU21" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="BV21" t="n">
+        <v>38.263</v>
+      </c>
+      <c r="BW21" t="n">
+        <v>31.055</v>
+      </c>
+      <c r="BX21" t="n">
+        <v>30.682</v>
+      </c>
+      <c r="BY21" t="n">
+        <v>98.08499999999999</v>
+      </c>
+      <c r="BZ21" t="n">
+        <v>31.624</v>
+      </c>
+      <c r="CA21" t="n">
+        <v>41.311</v>
+      </c>
+      <c r="CB21" t="n">
+        <v>27.066</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>351</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>2005</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>8952</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>18575</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>41421</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>64</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>349</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>1213</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>4652</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="CN21" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="CO21" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="CP21" t="n">
+        <v>37.406</v>
+      </c>
+      <c r="CQ21" t="n">
+        <v>28.198</v>
+      </c>
+      <c r="CR21" t="n">
+        <v>34.396</v>
+      </c>
+      <c r="CS21" t="n">
+        <v>99.199</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SP1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="I22" t="n">
+        <v>49.618</v>
+      </c>
+      <c r="J22" t="n">
+        <v>24.613</v>
+      </c>
+      <c r="K22" t="n">
+        <v>25.769</v>
+      </c>
+      <c r="L22" t="n">
+        <v>500</v>
+      </c>
+      <c r="M22" t="n">
+        <v>55</v>
+      </c>
+      <c r="N22" t="n">
+        <v>26</v>
+      </c>
+      <c r="O22" t="n">
+        <v>19</v>
+      </c>
+      <c r="P22" t="n">
+        <v>53.462</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>25.604</v>
+      </c>
+      <c r="R22" t="n">
+        <v>20.934</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.991</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-4.835</v>
+      </c>
+      <c r="V22" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="W22" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="X22" t="n">
+        <v>63</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.092</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>MODERATE HISTORICAL DEVIATION</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>99.413</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>99.369</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>99.089</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>50.618</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>59.306</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>22.349</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>30.017</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>15.803</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>3.906</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>60.513</v>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>largest deviation AWAY -4.8 pp; n_eff=500; market outside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>ec8992136f5ba2ef</t>
+        </is>
+      </c>
+      <c r="AS22" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.382</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-6.769</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.934</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.407</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-3.461</v>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF22" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>55</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>26</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>53.462</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>25.604</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>20.934</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>99.413</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>187</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>52.941</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>24.064</v>
+      </c>
+      <c r="BU22" t="n">
+        <v>22.995</v>
+      </c>
+      <c r="BV22" t="n">
+        <v>51.224</v>
+      </c>
+      <c r="BW22" t="n">
+        <v>24.348</v>
+      </c>
+      <c r="BX22" t="n">
+        <v>24.428</v>
+      </c>
+      <c r="BY22" t="n">
+        <v>97.721</v>
+      </c>
+      <c r="BZ22" t="n">
+        <v>47.222</v>
+      </c>
+      <c r="CA22" t="n">
+        <v>32.54</v>
+      </c>
+      <c r="CB22" t="n">
+        <v>20.238</v>
+      </c>
+      <c r="CC22" t="n">
+        <v>252</v>
+      </c>
+      <c r="CD22" t="n">
+        <v>750</v>
+      </c>
+      <c r="CE22" t="n">
+        <v>3641</v>
+      </c>
+      <c r="CF22" t="n">
+        <v>10591</v>
+      </c>
+      <c r="CG22" t="n">
+        <v>32590</v>
+      </c>
+      <c r="CH22" t="n">
+        <v>4</v>
+      </c>
+      <c r="CI22" t="n">
+        <v>87</v>
+      </c>
+      <c r="CJ22" t="n">
+        <v>321</v>
+      </c>
+      <c r="CK22" t="n">
+        <v>1415</v>
+      </c>
+      <c r="CL22" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="CN22" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="CO22" t="n">
+        <v>24</v>
+      </c>
+      <c r="CP22" t="n">
+        <v>50.034</v>
+      </c>
+      <c r="CQ22" t="n">
+        <v>25.461</v>
+      </c>
+      <c r="CR22" t="n">
+        <v>24.505</v>
+      </c>
+      <c r="CS22" t="n">
+        <v>98.66500000000001</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Moreirense</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Maritimo</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I23" t="n">
+        <v>38.424</v>
+      </c>
+      <c r="J23" t="n">
+        <v>29.557</v>
+      </c>
+      <c r="K23" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="L23" t="n">
+        <v>500</v>
+      </c>
+      <c r="M23" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>39.407</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>29.016</v>
+      </c>
+      <c r="R23" t="n">
+        <v>31.577</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.983</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.443</v>
+      </c>
+      <c r="V23" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="X23" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>99.742</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>99.736</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>99.586</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>35.603</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>44.153</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>25.004</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>32.919</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>27.487</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>35.597</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.538</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>3.446</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>41.995</v>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>largest deviation HOME +1.0 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>ea486369b4abba95</t>
+        </is>
+      </c>
+      <c r="AS23" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>-0.757</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.294</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.086</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>-0.371</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>-0.297</v>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF23" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>39.407</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>29.016</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>31.577</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>99.742</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>500</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="BU23" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="BV23" t="n">
+        <v>38.407</v>
+      </c>
+      <c r="BW23" t="n">
+        <v>29.445</v>
+      </c>
+      <c r="BX23" t="n">
+        <v>32.148</v>
+      </c>
+      <c r="BY23" t="n">
+        <v>98.669</v>
+      </c>
+      <c r="BZ23" t="n">
+        <v>30.211</v>
+      </c>
+      <c r="CA23" t="n">
+        <v>46.828</v>
+      </c>
+      <c r="CB23" t="n">
+        <v>22.961</v>
+      </c>
+      <c r="CC23" t="n">
+        <v>331</v>
+      </c>
+      <c r="CD23" t="n">
+        <v>3572</v>
+      </c>
+      <c r="CE23" t="n">
+        <v>12739</v>
+      </c>
+      <c r="CF23" t="n">
+        <v>23767</v>
+      </c>
+      <c r="CG23" t="n">
+        <v>45114</v>
+      </c>
+      <c r="CH23" t="n">
+        <v>49</v>
+      </c>
+      <c r="CI23" t="n">
+        <v>404</v>
+      </c>
+      <c r="CJ23" t="n">
+        <v>1604</v>
+      </c>
+      <c r="CK23" t="n">
+        <v>6291</v>
+      </c>
+      <c r="CL23" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="CN23" t="n">
+        <v>30</v>
+      </c>
+      <c r="CO23" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="CP23" t="n">
+        <v>39.835</v>
+      </c>
+      <c r="CQ23" t="n">
+        <v>29.873</v>
+      </c>
+      <c r="CR23" t="n">
+        <v>30.291</v>
+      </c>
+      <c r="CS23" t="n">
+        <v>99.518</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sp Braga</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="I24" t="n">
+        <v>64.122</v>
+      </c>
+      <c r="J24" t="n">
+        <v>21.473</v>
+      </c>
+      <c r="K24" t="n">
+        <v>14.405</v>
+      </c>
+      <c r="L24" t="n">
+        <v>500</v>
+      </c>
+      <c r="M24" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="N24" t="n">
+        <v>22</v>
+      </c>
+      <c r="O24" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="P24" t="n">
+        <v>64.60599999999999</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="R24" t="n">
+        <v>13.544</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.861</v>
+      </c>
+      <c r="V24" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="X24" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.982</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB24" t="n">
+        <v>99.617</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>99.602</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>99.36799999999999</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>60.515</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>68.85899999999999</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>25.837</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>10.512</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>4.577</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>7.383</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>55.585</v>
+      </c>
+      <c r="AP24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>largest deviation AWAY -0.9 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>984031c9c9d7c31d</t>
+        </is>
+      </c>
+      <c r="AS24" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-1.205</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2.086</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>-0.767</v>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF24" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG24" t="inlineStr"/>
+      <c r="BH24" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>22</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>64.60599999999999</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>13.544</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>99.617</v>
+      </c>
+      <c r="BR24" t="n">
         <v>149</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="BS24" t="n">
         <v>61.074</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="BT24" t="n">
         <v>26.846</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="BU24" t="n">
         <v>12.081</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="BV24" t="n">
         <v>62.82</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="BW24" t="n">
         <v>23.767</v>
       </c>
-      <c r="BX12" t="n">
+      <c r="BX24" t="n">
         <v>13.413</v>
       </c>
-      <c r="BY12" t="n">
+      <c r="BY24" t="n">
         <v>98.098</v>
       </c>
-      <c r="BZ12" t="n">
-        <v>500</v>
-      </c>
-      <c r="CA12" t="n">
+      <c r="BZ24" t="n">
+        <v>49.375</v>
+      </c>
+      <c r="CA24" t="n">
+        <v>31.562</v>
+      </c>
+      <c r="CB24" t="n">
+        <v>19.062</v>
+      </c>
+      <c r="CC24" t="n">
+        <v>320</v>
+      </c>
+      <c r="CD24" t="n">
+        <v>1469</v>
+      </c>
+      <c r="CE24" t="n">
+        <v>4979</v>
+      </c>
+      <c r="CF24" t="n">
+        <v>8706</v>
+      </c>
+      <c r="CG24" t="n">
+        <v>15761</v>
+      </c>
+      <c r="CH24" t="n">
+        <v>15</v>
+      </c>
+      <c r="CI24" t="n">
+        <v>77</v>
+      </c>
+      <c r="CJ24" t="n">
+        <v>368</v>
+      </c>
+      <c r="CK24" t="n">
+        <v>1451</v>
+      </c>
+      <c r="CL24" t="n">
+        <v>500</v>
+      </c>
+      <c r="CM24" t="n">
         <v>65.8</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CN24" t="n">
         <v>22.6</v>
       </c>
-      <c r="CC12" t="n">
+      <c r="CO24" t="n">
         <v>11.6</v>
       </c>
-      <c r="CD12" t="n">
+      <c r="CP24" t="n">
         <v>65.321</v>
       </c>
-      <c r="CE12" t="n">
+      <c r="CQ24" t="n">
         <v>22.278</v>
       </c>
-      <c r="CF12" t="n">
+      <c r="CR24" t="n">
         <v>12.401</v>
       </c>
-      <c r="CG12" t="n">
+      <c r="CS24" t="n">
         <v>99.036</v>
       </c>
-      <c r="CH12" t="n">
-        <v>46.4</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>500</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>623</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>2181</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>3864</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>6943</v>
-      </c>
-      <c r="CP12" t="n">
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Barracas Central</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>39.729</v>
+      </c>
+      <c r="J25" t="n">
+        <v>32.341</v>
+      </c>
+      <c r="K25" t="n">
+        <v>27.931</v>
+      </c>
+      <c r="L25" t="n">
+        <v>500</v>
+      </c>
+      <c r="M25" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="N25" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="O25" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>32.669</v>
+      </c>
+      <c r="R25" t="n">
+        <v>25.552</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.051</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-2.379</v>
+      </c>
+      <c r="V25" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="W25" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="X25" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB25" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>99.366</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>99.086</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>38.338</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>46.975</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>37.033</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>21.028</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>28.559</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.394</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>3.061</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>3.914</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>largest deviation AWAY -2.4 pp; n_eff=500; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>39f3f049b5c9361b</t>
+        </is>
+      </c>
+      <c r="AS25" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.871</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>-3.331</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.156</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF25" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG25" t="inlineStr"/>
+      <c r="BH25" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>41.78</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>32.669</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>25.552</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>500</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>40.494</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>31.097</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>28.409</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>98.742</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>31.095</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>44.876</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>24.028</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>283</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>693</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>3306</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>8971</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>32565</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>9</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>74</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>261</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>1435</v>
+      </c>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Dep. Riestra</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I26" t="n">
+        <v>31.655</v>
+      </c>
+      <c r="J26" t="n">
+        <v>34.362</v>
+      </c>
+      <c r="K26" t="n">
+        <v>33.983</v>
+      </c>
+      <c r="L26" t="n">
+        <v>500</v>
+      </c>
+      <c r="M26" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>31.044</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>37.246</v>
+      </c>
+      <c r="R26" t="n">
+        <v>31.709</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.611</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.884</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-2.273</v>
+      </c>
+      <c r="V26" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="W26" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="X26" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.036</v>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB26" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>98.462</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>97.873</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>26.913</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>34.241</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>42.736</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>26.913</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>34.98</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3.221</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>2.685</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>3.154</v>
+      </c>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr">
+        <is>
+          <t>draw</t>
+        </is>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>largest deviation DRAW +2.9 pp; n_eff=500; market inside 95% CI; avg similarity 98.6%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>4ea83631bacb14d7</t>
+        </is>
+      </c>
+      <c r="AS26" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>-0.855</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.038</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>-3.183</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>-0.411</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.901</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>-1.503</v>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF26" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>31.044</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>37.246</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>31.709</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>98.58</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>411</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>33.577</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>35.523</v>
+      </c>
+      <c r="BU26" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>32.948</v>
+      </c>
+      <c r="BW26" t="n">
+        <v>35.143</v>
+      </c>
+      <c r="BX26" t="n">
+        <v>31.909</v>
+      </c>
+      <c r="BY26" t="n">
+        <v>97.857</v>
+      </c>
+      <c r="BZ26" t="n">
+        <v>29.63</v>
+      </c>
+      <c r="CA26" t="n">
+        <v>49.537</v>
+      </c>
+      <c r="CB26" t="n">
+        <v>20.833</v>
+      </c>
+      <c r="CC26" t="n">
+        <v>216</v>
+      </c>
+      <c r="CD26" t="n">
+        <v>105</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>482</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>1802</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>10558</v>
+      </c>
+      <c r="CH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>16</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>52</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>218</v>
+      </c>
+      <c r="CL26" t="inlineStr"/>
+      <c r="CM26" t="inlineStr"/>
+      <c r="CN26" t="inlineStr"/>
+      <c r="CO26" t="inlineStr"/>
+      <c r="CP26" t="inlineStr"/>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Remo</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="H27" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="I27" t="n">
+        <v>65.542</v>
+      </c>
+      <c r="J27" t="n">
+        <v>20.582</v>
+      </c>
+      <c r="K27" t="n">
+        <v>13.876</v>
+      </c>
+      <c r="L27" t="n">
+        <v>500</v>
+      </c>
+      <c r="M27" t="n">
+        <v>71</v>
+      </c>
+      <c r="N27" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="P27" t="n">
+        <v>69.441</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>19.309</v>
+      </c>
+      <c r="R27" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.899</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-1.273</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-2.626</v>
+      </c>
+      <c r="V27" t="n">
+        <v>61</v>
+      </c>
+      <c r="W27" t="n">
+        <v>39</v>
+      </c>
+      <c r="X27" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>MODERATE HISTORICAL DEVIATION</t>
+        </is>
+      </c>
+      <c r="AB27" t="n">
+        <v>99.587</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>99.565</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>99.303</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>66.874</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>74.80500000000001</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>15.618</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>22.458</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>7.843</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>13.164</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>5.179</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>8.888999999999999</v>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>largest deviation HOME +3.9 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>ecaa0347800574e5</t>
+        </is>
+      </c>
+      <c r="AS27" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.458</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>-1.782</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-3.676</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>2.286</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>2.568</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>-0.986</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-2.378</v>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF27" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG27" t="inlineStr"/>
+      <c r="BH27" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>71</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>69.441</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>19.309</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>99.587</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>362</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>67.68000000000001</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>18.508</v>
+      </c>
+      <c r="BU27" t="n">
+        <v>13.812</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>66.919</v>
+      </c>
+      <c r="BW27" t="n">
+        <v>19.246</v>
+      </c>
+      <c r="BX27" t="n">
+        <v>13.835</v>
+      </c>
+      <c r="BY27" t="n">
+        <v>97.947</v>
+      </c>
+      <c r="BZ27" t="n">
+        <v>49.53</v>
+      </c>
+      <c r="CA27" t="n">
+        <v>37.304</v>
+      </c>
+      <c r="CB27" t="n">
+        <v>13.166</v>
+      </c>
+      <c r="CC27" t="n">
+        <v>319</v>
+      </c>
+      <c r="CD27" t="n">
+        <v>1295</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>4346</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>7782</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>14041</v>
+      </c>
+      <c r="CH27" t="n">
+        <v>11</v>
+      </c>
+      <c r="CI27" t="n">
+        <v>82</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>325</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>1207</v>
+      </c>
+      <c r="CL27" t="inlineStr"/>
+      <c r="CM27" t="inlineStr"/>
+      <c r="CN27" t="inlineStr"/>
+      <c r="CO27" t="inlineStr"/>
+      <c r="CP27" t="inlineStr"/>
+      <c r="CQ27" t="inlineStr"/>
+      <c r="CR27" t="inlineStr"/>
+      <c r="CS27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Instituto</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>65.904</v>
+      </c>
+      <c r="J28" t="n">
+        <v>23.241</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10.855</v>
+      </c>
+      <c r="L28" t="n">
+        <v>500</v>
+      </c>
+      <c r="M28" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="N28" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="O28" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="P28" t="n">
+        <v>67.258</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>22.069</v>
+      </c>
+      <c r="R28" t="n">
+        <v>10.673</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.354</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-1.172</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.182</v>
+      </c>
+      <c r="V28" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="X28" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="AB28" t="n">
+        <v>98.884</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>98.797</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>98.29900000000001</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>500</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>63.582</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>71.746</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>18.217</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>25.416</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>8.196</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>13.605</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.487</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>4.531</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>largest deviation HOME +1.4 pp; n_eff=500; market inside 95% CI; avg similarity 98.9%; backtest: no significant improvement over market</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>8d90d4bfa5c68fa8</t>
+        </is>
+      </c>
+      <c r="AS28" t="n">
+        <v>179331</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.896</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>-1.641</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>-0.255</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.854</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0.694</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>-0.869</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1x2</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr">
+        <is>
+          <t>cosine</t>
+        </is>
+      </c>
+      <c r="BF28" t="n">
+        <v>500</v>
+      </c>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="n">
+        <v>200</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>500</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>67.258</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>22.069</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>10.673</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>98.884</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>167</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>64.67100000000001</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>20.359</v>
+      </c>
+      <c r="BU28" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>65.343</v>
+      </c>
+      <c r="BW28" t="n">
+        <v>21.93</v>
+      </c>
+      <c r="BX28" t="n">
+        <v>12.727</v>
+      </c>
+      <c r="BY28" t="n">
+        <v>98.127</v>
+      </c>
+      <c r="BZ28" t="n">
+        <v>47.143</v>
+      </c>
+      <c r="CA28" t="n">
+        <v>40.714</v>
+      </c>
+      <c r="CB28" t="n">
+        <v>12.143</v>
+      </c>
+      <c r="CC28" t="n">
+        <v>280</v>
+      </c>
+      <c r="CD28" t="n">
+        <v>168</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>1266</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>3918</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>11703</v>
+      </c>
+      <c r="CH28" t="n">
         <v>4</v>
       </c>
-      <c r="CQ12" t="n">
-        <v>19</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>104</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>545</v>
-      </c>
+      <c r="CI28" t="n">
+        <v>6</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>26</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>105</v>
+      </c>
+      <c r="CL28" t="inlineStr"/>
+      <c r="CM28" t="inlineStr"/>
+      <c r="CN28" t="inlineStr"/>
+      <c r="CO28" t="inlineStr"/>
+      <c r="CP28" t="inlineStr"/>
+      <c r="CQ28" t="inlineStr"/>
+      <c r="CR28" t="inlineStr"/>
+      <c r="CS28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/football_odds/results/2026-09-14_predictions.xlsx
+++ b/football_odds/results/2026-09-14_predictions.xlsx
@@ -804,102 +804,102 @@
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
+          <t>similar_leagues_n</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>similar_leagues_hist_h</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>similar_leagues_hist_d</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>similar_leagues_hist_a</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>similar_leagues_adj_h</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>similar_leagues_adj_d</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>similar_leagues_adj_a</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>similar_leagues_avg_sim</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
           <t>ht_h</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>ht_d</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>ht_a</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>n_ht</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>tol_probs_1pct</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>tol_probs_2pct</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>tol_probs_3pct</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>tol_probs_5pct</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>tol_odds_1pct</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>tol_odds_2pct</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>tol_odds_3pct</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>tol_odds_5pct</t>
-        </is>
-      </c>
-      <c r="CL1" t="inlineStr">
-        <is>
-          <t>similar_leagues_n</t>
-        </is>
-      </c>
-      <c r="CM1" t="inlineStr">
-        <is>
-          <t>similar_leagues_hist_h</t>
-        </is>
-      </c>
-      <c r="CN1" t="inlineStr">
-        <is>
-          <t>similar_leagues_hist_d</t>
-        </is>
-      </c>
-      <c r="CO1" t="inlineStr">
-        <is>
-          <t>similar_leagues_hist_a</t>
-        </is>
-      </c>
-      <c r="CP1" t="inlineStr">
-        <is>
-          <t>similar_leagues_adj_h</t>
-        </is>
-      </c>
-      <c r="CQ1" t="inlineStr">
-        <is>
-          <t>similar_leagues_adj_d</t>
-        </is>
-      </c>
-      <c r="CR1" t="inlineStr">
-        <is>
-          <t>similar_leagues_adj_a</t>
-        </is>
-      </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>similar_leagues_avg_sim</t>
         </is>
       </c>
     </row>
@@ -948,50 +948,50 @@
         <v>30.952</v>
       </c>
       <c r="L2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>33.6</v>
+        <v>30</v>
       </c>
       <c r="O2" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="P2" t="n">
-        <v>35.929</v>
+        <v>37.167</v>
       </c>
       <c r="Q2" t="n">
-        <v>33.514</v>
+        <v>32.199</v>
       </c>
       <c r="R2" t="n">
-        <v>30.558</v>
+        <v>30.634</v>
       </c>
       <c r="S2" t="n">
-        <v>0.178</v>
+        <v>1.417</v>
       </c>
       <c r="T2" t="n">
-        <v>0.216</v>
+        <v>-1.099</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.394</v>
+        <v>-0.317</v>
       </c>
       <c r="V2" t="n">
-        <v>34.4</v>
+        <v>29</v>
       </c>
       <c r="W2" t="n">
-        <v>65.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="X2" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.096</v>
+        <v>1.94</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1000,53 +1000,53 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>99.122</v>
+        <v>99.379</v>
       </c>
       <c r="AC2" t="n">
-        <v>99.074</v>
+        <v>99.383</v>
       </c>
       <c r="AD2" t="n">
-        <v>98.682</v>
+        <v>98.82299999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>31.914</v>
+        <v>30.94</v>
       </c>
       <c r="AG2" t="n">
-        <v>40.299</v>
+        <v>49.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>29.599</v>
+        <v>21.895</v>
       </c>
       <c r="AI2" t="n">
-        <v>37.851</v>
+        <v>39.585</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.53</v>
+        <v>21.895</v>
       </c>
       <c r="AK2" t="n">
-        <v>34.569</v>
+        <v>39.585</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.783</v>
+        <v>2.691</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.984</v>
+        <v>3.106</v>
       </c>
       <c r="AN2" t="n">
-        <v>3.273</v>
+        <v>3.264</v>
       </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>largest deviation AWAY -0.4 pp; n_eff=500; market inside 95% CI; avg similarity 99.1%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +1.4 pp; n_eff=100; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1058,31 +1058,31 @@
         <v>179331</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.25</v>
+        <v>4.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.302</v>
+        <v>-3.298</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.552</v>
+        <v>-0.952</v>
       </c>
       <c r="AW2" t="n">
         <v>2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.076</v>
+        <v>1.04</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.117</v>
+        <v>0.887</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.143</v>
+        <v>-0.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0.267</v>
+        <v>-0.206</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -1096,111 +1096,127 @@
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="n">
         <v>200</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.79</v>
+        <v>0.375</v>
       </c>
       <c r="BJ2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BL2" t="n">
-        <v>33.6</v>
+        <v>30</v>
       </c>
       <c r="BM2" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="BN2" t="n">
-        <v>35.929</v>
+        <v>37.167</v>
       </c>
       <c r="BO2" t="n">
-        <v>33.514</v>
+        <v>32.199</v>
       </c>
       <c r="BP2" t="n">
-        <v>30.558</v>
+        <v>30.634</v>
       </c>
       <c r="BQ2" t="n">
-        <v>99.122</v>
+        <v>99.379</v>
       </c>
       <c r="BR2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>33.2</v>
+        <v>40</v>
       </c>
       <c r="BT2" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BU2" t="n">
-        <v>32.8</v>
+        <v>31</v>
       </c>
       <c r="BV2" t="n">
-        <v>33.929</v>
+        <v>37.167</v>
       </c>
       <c r="BW2" t="n">
-        <v>33.799</v>
+        <v>31.865</v>
       </c>
       <c r="BX2" t="n">
-        <v>32.272</v>
+        <v>30.968</v>
       </c>
       <c r="BY2" t="n">
-        <v>98.328</v>
+        <v>98.929</v>
       </c>
       <c r="BZ2" t="n">
-        <v>25.591</v>
+        <v>100</v>
       </c>
       <c r="CA2" t="n">
-        <v>50.787</v>
+        <v>37</v>
       </c>
       <c r="CB2" t="n">
-        <v>23.622</v>
+        <v>31</v>
       </c>
       <c r="CC2" t="n">
-        <v>254</v>
+        <v>32</v>
       </c>
       <c r="CD2" t="n">
+        <v>36.167</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>32.532</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>31.301</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>99.349</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>22.917</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>20.833</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>48</v>
+      </c>
+      <c r="CL2" t="n">
         <v>291</v>
       </c>
-      <c r="CE2" t="n">
+      <c r="CM2" t="n">
         <v>1721</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CN2" t="n">
         <v>5272</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CO2" t="n">
         <v>23576</v>
       </c>
-      <c r="CH2" t="n">
+      <c r="CP2" t="n">
         <v>2</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CQ2" t="n">
         <v>33</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CR2" t="n">
         <v>142</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CS2" t="n">
         <v>648</v>
       </c>
-      <c r="CL2" t="inlineStr"/>
-      <c r="CM2" t="inlineStr"/>
-      <c r="CN2" t="inlineStr"/>
-      <c r="CO2" t="inlineStr"/>
-      <c r="CP2" t="inlineStr"/>
-      <c r="CQ2" t="inlineStr"/>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1247,50 +1263,50 @@
         <v>27.879</v>
       </c>
       <c r="L3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>24.2</v>
+        <v>27</v>
       </c>
       <c r="O3" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="P3" t="n">
-        <v>48.182</v>
+        <v>47.424</v>
       </c>
       <c r="Q3" t="n">
-        <v>24.424</v>
+        <v>25.656</v>
       </c>
       <c r="R3" t="n">
-        <v>27.394</v>
+        <v>26.92</v>
       </c>
       <c r="S3" t="n">
-        <v>1.046</v>
+        <v>0.288</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.672</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.485</v>
+        <v>-0.96</v>
       </c>
       <c r="V3" t="n">
-        <v>58.8</v>
+        <v>50</v>
       </c>
       <c r="W3" t="n">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="X3" t="n">
-        <v>60.4</v>
+        <v>58</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.996</v>
+        <v>2.85</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1299,53 +1315,53 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>99.396</v>
+        <v>99.627</v>
       </c>
       <c r="AC3" t="n">
-        <v>99.34699999999999</v>
+        <v>99.648</v>
       </c>
       <c r="AD3" t="n">
-        <v>99.044</v>
+        <v>99.196</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF3" t="n">
-        <v>44.246</v>
+        <v>38.464</v>
       </c>
       <c r="AG3" t="n">
-        <v>52.975</v>
+        <v>57.684</v>
       </c>
       <c r="AH3" t="n">
-        <v>20.652</v>
+        <v>19.269</v>
       </c>
       <c r="AI3" t="n">
-        <v>28.142</v>
+        <v>36.432</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23.484</v>
+        <v>17.545</v>
       </c>
       <c r="AK3" t="n">
-        <v>31.263</v>
+        <v>34.305</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.075</v>
+        <v>2.109</v>
       </c>
       <c r="AM3" t="n">
-        <v>4.094</v>
+        <v>3.898</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.65</v>
+        <v>3.715</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>largest deviation HOME +1.0 pp; n_eff=500; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY -1.0 pp; n_eff=100; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1357,31 +1373,31 @@
         <v>179331</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.464</v>
+        <v>0.864</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.785</v>
+        <v>2.015</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.679</v>
+        <v>-2.879</v>
       </c>
       <c r="AW3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.746</v>
+        <v>1.69</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.656</v>
+        <v>0.173</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.405</v>
+        <v>0.466</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.339</v>
+        <v>-0.642</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
@@ -1395,111 +1411,127 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="n">
         <v>200</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.512</v>
+        <v>0.521</v>
       </c>
       <c r="BJ3" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK3" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="BL3" t="n">
-        <v>24.2</v>
+        <v>27</v>
       </c>
       <c r="BM3" t="n">
-        <v>27.2</v>
+        <v>25</v>
       </c>
       <c r="BN3" t="n">
-        <v>48.182</v>
+        <v>47.424</v>
       </c>
       <c r="BO3" t="n">
-        <v>24.424</v>
+        <v>25.656</v>
       </c>
       <c r="BP3" t="n">
-        <v>27.394</v>
+        <v>26.92</v>
       </c>
       <c r="BQ3" t="n">
-        <v>99.396</v>
+        <v>99.627</v>
       </c>
       <c r="BR3" t="n">
-        <v>309</v>
+        <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>52.104</v>
+        <v>58</v>
       </c>
       <c r="BT3" t="n">
-        <v>30.097</v>
+        <v>22</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.799</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>50.152</v>
+        <v>50.757</v>
       </c>
       <c r="BW3" t="n">
-        <v>28.088</v>
+        <v>23.99</v>
       </c>
       <c r="BX3" t="n">
-        <v>21.76</v>
+        <v>25.253</v>
       </c>
       <c r="BY3" t="n">
-        <v>97.791</v>
+        <v>97.837</v>
       </c>
       <c r="BZ3" t="n">
-        <v>38.202</v>
+        <v>100</v>
       </c>
       <c r="CA3" t="n">
-        <v>38.577</v>
+        <v>45</v>
       </c>
       <c r="CB3" t="n">
-        <v>23.221</v>
+        <v>26</v>
       </c>
       <c r="CC3" t="n">
-        <v>267</v>
+        <v>29</v>
       </c>
       <c r="CD3" t="n">
+        <v>46.424</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>25.323</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>28.253</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>99.559</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>34.545</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>49.091</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>16.364</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>55</v>
+      </c>
+      <c r="CL3" t="n">
         <v>651</v>
       </c>
-      <c r="CE3" t="n">
+      <c r="CM3" t="n">
         <v>3492</v>
       </c>
-      <c r="CF3" t="n">
+      <c r="CN3" t="n">
         <v>10762</v>
       </c>
-      <c r="CG3" t="n">
+      <c r="CO3" t="n">
         <v>34195</v>
       </c>
-      <c r="CH3" t="n">
+      <c r="CP3" t="n">
         <v>3</v>
       </c>
-      <c r="CI3" t="n">
+      <c r="CQ3" t="n">
         <v>38</v>
       </c>
-      <c r="CJ3" t="n">
+      <c r="CR3" t="n">
         <v>119</v>
       </c>
-      <c r="CK3" t="n">
+      <c r="CS3" t="n">
         <v>856</v>
       </c>
-      <c r="CL3" t="inlineStr"/>
-      <c r="CM3" t="inlineStr"/>
-      <c r="CN3" t="inlineStr"/>
-      <c r="CO3" t="inlineStr"/>
-      <c r="CP3" t="inlineStr"/>
-      <c r="CQ3" t="inlineStr"/>
-      <c r="CR3" t="inlineStr"/>
-      <c r="CS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1546,50 +1578,50 @@
         <v>37.737</v>
       </c>
       <c r="L4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M4" t="n">
+        <v>39</v>
+      </c>
+      <c r="N4" t="n">
+        <v>23</v>
+      </c>
+      <c r="O4" t="n">
         <v>38</v>
       </c>
-      <c r="N4" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O4" t="n">
-        <v>39.2</v>
-      </c>
       <c r="P4" t="n">
-        <v>37.793</v>
+        <v>37.851</v>
       </c>
       <c r="Q4" t="n">
-        <v>23.425</v>
+        <v>24.324</v>
       </c>
       <c r="R4" t="n">
-        <v>38.782</v>
+        <v>37.825</v>
       </c>
       <c r="S4" t="n">
-        <v>0.517</v>
+        <v>0.574</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.562</v>
+        <v>-0.662</v>
       </c>
       <c r="U4" t="n">
-        <v>1.045</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>61.6</v>
+        <v>66</v>
       </c>
       <c r="W4" t="n">
-        <v>38.4</v>
+        <v>34</v>
       </c>
       <c r="X4" t="n">
-        <v>64.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.254</v>
+        <v>3.52</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1598,43 +1630,43 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>98.917</v>
+        <v>99.26600000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>98.83199999999999</v>
+        <v>99.28700000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>98.396</v>
+        <v>98.435</v>
       </c>
       <c r="AE4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
-        <v>33.852</v>
+        <v>30.017</v>
       </c>
       <c r="AG4" t="n">
-        <v>42.331</v>
+        <v>48.797</v>
       </c>
       <c r="AH4" t="n">
-        <v>19.338</v>
+        <v>15.843</v>
       </c>
       <c r="AI4" t="n">
-        <v>26.677</v>
+        <v>32.155</v>
       </c>
       <c r="AJ4" t="n">
-        <v>35.019</v>
+        <v>29.097</v>
       </c>
       <c r="AK4" t="n">
-        <v>43.546</v>
+        <v>47.79</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.646</v>
+        <v>2.642</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.269</v>
+        <v>4.111</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.579</v>
+        <v>2.644</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr">
@@ -1644,7 +1676,7 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>largest deviation DRAW -1.6 pp; n_eff=500; market inside 95% CI; avg similarity 98.9%; backtest: no significant improvement over market</t>
+          <t>largest deviation DRAW -0.7 pp; n_eff=100; market inside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1656,31 +1688,31 @@
         <v>179331</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.723</v>
+        <v>1.723</v>
       </c>
       <c r="AU4" t="n">
-        <v>-2.187</v>
+        <v>-1.987</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.463</v>
+        <v>0.263</v>
       </c>
       <c r="AW4" t="n">
         <v>3</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.592</v>
+        <v>1.73</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.662</v>
+        <v>1.79</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.335</v>
+        <v>0.356</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1.129</v>
+        <v>-0.459</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.675</v>
+        <v>0.054</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
@@ -1694,111 +1726,127 @@
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
         <v>200</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.259</v>
+        <v>0.646</v>
       </c>
       <c r="BJ4" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK4" t="n">
+        <v>39</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>23</v>
+      </c>
+      <c r="BM4" t="n">
         <v>38</v>
       </c>
-      <c r="BL4" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>39.2</v>
-      </c>
       <c r="BN4" t="n">
-        <v>37.793</v>
+        <v>37.851</v>
       </c>
       <c r="BO4" t="n">
-        <v>23.425</v>
+        <v>24.324</v>
       </c>
       <c r="BP4" t="n">
-        <v>38.782</v>
+        <v>37.825</v>
       </c>
       <c r="BQ4" t="n">
-        <v>98.917</v>
+        <v>99.26600000000001</v>
       </c>
       <c r="BR4" t="n">
-        <v>322</v>
+        <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>40.373</v>
+        <v>39</v>
       </c>
       <c r="BT4" t="n">
-        <v>21.739</v>
+        <v>22</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.888</v>
+        <v>39</v>
       </c>
       <c r="BV4" t="n">
-        <v>39.186</v>
+        <v>37.851</v>
       </c>
       <c r="BW4" t="n">
-        <v>22.983</v>
+        <v>23.991</v>
       </c>
       <c r="BX4" t="n">
-        <v>37.83</v>
+        <v>38.158</v>
       </c>
       <c r="BY4" t="n">
-        <v>97.986</v>
+        <v>98.327</v>
       </c>
       <c r="BZ4" t="n">
-        <v>34.328</v>
+        <v>100</v>
       </c>
       <c r="CA4" t="n">
-        <v>34.701</v>
+        <v>43</v>
       </c>
       <c r="CB4" t="n">
-        <v>30.97</v>
+        <v>21</v>
       </c>
       <c r="CC4" t="n">
-        <v>268</v>
+        <v>36</v>
       </c>
       <c r="CD4" t="n">
+        <v>39.184</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>23.658</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>37.158</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>99.148</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>43.478</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>30.435</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>26.087</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>46</v>
+      </c>
+      <c r="CL4" t="n">
         <v>165</v>
       </c>
-      <c r="CE4" t="n">
+      <c r="CM4" t="n">
         <v>1143</v>
       </c>
-      <c r="CF4" t="n">
+      <c r="CN4" t="n">
         <v>4105</v>
       </c>
-      <c r="CG4" t="n">
+      <c r="CO4" t="n">
         <v>21416</v>
       </c>
-      <c r="CH4" t="n">
+      <c r="CP4" t="n">
         <v>3</v>
       </c>
-      <c r="CI4" t="n">
+      <c r="CQ4" t="n">
         <v>15</v>
       </c>
-      <c r="CJ4" t="n">
+      <c r="CR4" t="n">
         <v>56</v>
       </c>
-      <c r="CK4" t="n">
+      <c r="CS4" t="n">
         <v>292</v>
       </c>
-      <c r="CL4" t="inlineStr"/>
-      <c r="CM4" t="inlineStr"/>
-      <c r="CN4" t="inlineStr"/>
-      <c r="CO4" t="inlineStr"/>
-      <c r="CP4" t="inlineStr"/>
-      <c r="CQ4" t="inlineStr"/>
-      <c r="CR4" t="inlineStr"/>
-      <c r="CS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1845,50 +1893,50 @@
         <v>14.815</v>
       </c>
       <c r="L5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N5" t="n">
-        <v>24.8</v>
+        <v>22</v>
       </c>
       <c r="O5" t="n">
-        <v>14.2</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>61.717</v>
+        <v>65.673</v>
       </c>
       <c r="Q5" t="n">
-        <v>23.907</v>
+        <v>21.783</v>
       </c>
       <c r="R5" t="n">
-        <v>14.376</v>
+        <v>12.544</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.792</v>
+        <v>2.164</v>
       </c>
       <c r="T5" t="n">
-        <v>2.232</v>
+        <v>0.108</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.44</v>
+        <v>-2.272</v>
       </c>
       <c r="V5" t="n">
-        <v>55.4</v>
+        <v>56</v>
       </c>
       <c r="W5" t="n">
-        <v>44.6</v>
+        <v>44</v>
       </c>
       <c r="X5" t="n">
-        <v>53.2</v>
+        <v>51</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1897,53 +1945,53 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>99.62</v>
+        <v>99.78400000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>99.601</v>
+        <v>99.795</v>
       </c>
       <c r="AD5" t="n">
-        <v>99.348</v>
+        <v>99.51300000000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF5" t="n">
-        <v>56.656</v>
+        <v>60.415</v>
       </c>
       <c r="AG5" t="n">
-        <v>65.176</v>
+        <v>78.105</v>
       </c>
       <c r="AH5" t="n">
-        <v>21.216</v>
+        <v>15.001</v>
       </c>
       <c r="AI5" t="n">
-        <v>28.768</v>
+        <v>31.071</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11.413</v>
+        <v>4.109</v>
       </c>
       <c r="AK5" t="n">
-        <v>17.533</v>
+        <v>14.998</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.62</v>
+        <v>1.523</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.183</v>
+        <v>4.591</v>
       </c>
       <c r="AN5" t="n">
-        <v>6.956</v>
+        <v>7.972</v>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>largest deviation DRAW +2.2 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY -2.3 pp; n_eff=100; market inside 95% CI; avg similarity 99.8%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -1955,31 +2003,31 @@
         <v>179331</v>
       </c>
       <c r="AT5" t="n">
-        <v>-2.509</v>
+        <v>6.491</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.125</v>
+        <v>0.325</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.615</v>
+        <v>-6.815</v>
       </c>
       <c r="AW5" t="n">
         <v>3</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.996</v>
+        <v>2.08</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.904</v>
+        <v>0.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-1.166</v>
+        <v>1.348</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.696</v>
+        <v>0.079</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.387</v>
+        <v>-1.918</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
@@ -1993,111 +2041,127 @@
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
         <v>200</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.09</v>
+        <v>0.055</v>
       </c>
       <c r="BJ5" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK5" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="BL5" t="n">
-        <v>24.8</v>
+        <v>22</v>
       </c>
       <c r="BM5" t="n">
-        <v>14.2</v>
+        <v>8</v>
       </c>
       <c r="BN5" t="n">
-        <v>61.717</v>
+        <v>65.673</v>
       </c>
       <c r="BO5" t="n">
-        <v>23.907</v>
+        <v>21.783</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.376</v>
+        <v>12.544</v>
       </c>
       <c r="BQ5" t="n">
-        <v>99.62</v>
+        <v>99.78400000000001</v>
       </c>
       <c r="BR5" t="n">
-        <v>304</v>
+        <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>64.474</v>
+        <v>67</v>
       </c>
       <c r="BT5" t="n">
-        <v>22.368</v>
+        <v>22</v>
       </c>
       <c r="BU5" t="n">
-        <v>13.158</v>
+        <v>11</v>
       </c>
       <c r="BV5" t="n">
-        <v>64.09099999999999</v>
+        <v>64.673</v>
       </c>
       <c r="BW5" t="n">
-        <v>22.093</v>
+        <v>21.783</v>
       </c>
       <c r="BX5" t="n">
-        <v>13.816</v>
+        <v>13.544</v>
       </c>
       <c r="BY5" t="n">
-        <v>98.244</v>
+        <v>98.764</v>
       </c>
       <c r="BZ5" t="n">
-        <v>43.73</v>
+        <v>100</v>
       </c>
       <c r="CA5" t="n">
-        <v>36.656</v>
+        <v>69</v>
       </c>
       <c r="CB5" t="n">
-        <v>19.614</v>
+        <v>24</v>
       </c>
       <c r="CC5" t="n">
-        <v>311</v>
+        <v>7</v>
       </c>
       <c r="CD5" t="n">
+        <v>65.34</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>22.45</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>99.718</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>54.237</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>28.814</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>16.949</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>59</v>
+      </c>
+      <c r="CL5" t="n">
         <v>1470</v>
       </c>
-      <c r="CE5" t="n">
+      <c r="CM5" t="n">
         <v>5048</v>
       </c>
-      <c r="CF5" t="n">
+      <c r="CN5" t="n">
         <v>9032</v>
       </c>
-      <c r="CG5" t="n">
+      <c r="CO5" t="n">
         <v>16586</v>
       </c>
-      <c r="CH5" t="n">
+      <c r="CP5" t="n">
         <v>2</v>
       </c>
-      <c r="CI5" t="n">
+      <c r="CQ5" t="n">
         <v>16</v>
       </c>
-      <c r="CJ5" t="n">
+      <c r="CR5" t="n">
         <v>105</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CS5" t="n">
         <v>910</v>
       </c>
-      <c r="CL5" t="inlineStr"/>
-      <c r="CM5" t="inlineStr"/>
-      <c r="CN5" t="inlineStr"/>
-      <c r="CO5" t="inlineStr"/>
-      <c r="CP5" t="inlineStr"/>
-      <c r="CQ5" t="inlineStr"/>
-      <c r="CR5" t="inlineStr"/>
-      <c r="CS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2144,50 +2208,50 @@
         <v>20.208</v>
       </c>
       <c r="L6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>52.6</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="O6" t="n">
-        <v>21.8</v>
+        <v>27</v>
       </c>
       <c r="P6" t="n">
-        <v>52.946</v>
+        <v>52.206</v>
       </c>
       <c r="Q6" t="n">
-        <v>25.709</v>
+        <v>25.321</v>
       </c>
       <c r="R6" t="n">
-        <v>21.345</v>
+        <v>22.472</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.864</v>
+        <v>-1.603</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.273</v>
+        <v>-0.661</v>
       </c>
       <c r="U6" t="n">
-        <v>1.137</v>
+        <v>2.264</v>
       </c>
       <c r="V6" t="n">
-        <v>46.6</v>
+        <v>44</v>
       </c>
       <c r="W6" t="n">
-        <v>53.4</v>
+        <v>56</v>
       </c>
       <c r="X6" t="n">
-        <v>47.6</v>
+        <v>46</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.524</v>
+        <v>2.39</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -2196,43 +2260,43 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>99.733</v>
+        <v>99.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>99.724</v>
+        <v>99.827</v>
       </c>
       <c r="AD6" t="n">
-        <v>99.563</v>
+        <v>99.673</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF6" t="n">
-        <v>48.22</v>
+        <v>39.422</v>
       </c>
       <c r="AG6" t="n">
-        <v>56.94</v>
+        <v>58.652</v>
       </c>
       <c r="AH6" t="n">
-        <v>21.971</v>
+        <v>16.691</v>
       </c>
       <c r="AI6" t="n">
-        <v>29.601</v>
+        <v>33.233</v>
       </c>
       <c r="AJ6" t="n">
-        <v>18.403</v>
+        <v>19.269</v>
       </c>
       <c r="AK6" t="n">
-        <v>25.627</v>
+        <v>36.432</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.889</v>
+        <v>1.915</v>
       </c>
       <c r="AM6" t="n">
-        <v>3.89</v>
+        <v>3.949</v>
       </c>
       <c r="AN6" t="n">
-        <v>4.685</v>
+        <v>4.45</v>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr">
@@ -2242,7 +2306,7 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +1.1 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY +2.3 pp; n_eff=100; market inside 95% CI; avg similarity 99.8%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2254,31 +2318,31 @@
         <v>179331</v>
       </c>
       <c r="AT6" t="n">
-        <v>-1.209</v>
+        <v>-4.809</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.382</v>
+        <v>-1.982</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.592</v>
+        <v>6.792</v>
       </c>
       <c r="AW6" t="n">
         <v>2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.602</v>
+        <v>1.43</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.922</v>
+        <v>0.96</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.542</v>
+        <v>-0.965</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.195</v>
+        <v>-0.452</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.886</v>
+        <v>1.691</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
@@ -2292,111 +2356,127 @@
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="n">
         <v>200</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.375</v>
+        <v>0.091</v>
       </c>
       <c r="BJ6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK6" t="n">
-        <v>52.6</v>
+        <v>49</v>
       </c>
       <c r="BL6" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="BM6" t="n">
-        <v>21.8</v>
+        <v>27</v>
       </c>
       <c r="BN6" t="n">
-        <v>52.946</v>
+        <v>52.206</v>
       </c>
       <c r="BO6" t="n">
-        <v>25.709</v>
+        <v>25.321</v>
       </c>
       <c r="BP6" t="n">
-        <v>21.345</v>
+        <v>22.472</v>
       </c>
       <c r="BQ6" t="n">
-        <v>99.733</v>
+        <v>99.84</v>
       </c>
       <c r="BR6" t="n">
-        <v>241</v>
+        <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>55.187</v>
+        <v>57</v>
       </c>
       <c r="BT6" t="n">
-        <v>25.311</v>
+        <v>23</v>
       </c>
       <c r="BU6" t="n">
-        <v>19.502</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>54.562</v>
+        <v>54.873</v>
       </c>
       <c r="BW6" t="n">
-        <v>25.616</v>
+        <v>24.988</v>
       </c>
       <c r="BX6" t="n">
-        <v>19.822</v>
+        <v>20.139</v>
       </c>
       <c r="BY6" t="n">
-        <v>98.229</v>
+        <v>98.587</v>
       </c>
       <c r="BZ6" t="n">
-        <v>35.484</v>
+        <v>100</v>
       </c>
       <c r="CA6" t="n">
-        <v>43.695</v>
+        <v>48</v>
       </c>
       <c r="CB6" t="n">
-        <v>20.821</v>
+        <v>31</v>
       </c>
       <c r="CC6" t="n">
-        <v>341</v>
+        <v>21</v>
       </c>
       <c r="CD6" t="n">
+        <v>51.873</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>27.655</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>20.472</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>99.741</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>34.286</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>42.857</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>22.857</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>70</v>
+      </c>
+      <c r="CL6" t="n">
         <v>2955</v>
       </c>
-      <c r="CE6" t="n">
+      <c r="CM6" t="n">
         <v>9737</v>
       </c>
-      <c r="CF6" t="n">
+      <c r="CN6" t="n">
         <v>17450</v>
       </c>
-      <c r="CG6" t="n">
+      <c r="CO6" t="n">
         <v>31912</v>
       </c>
-      <c r="CH6" t="n">
+      <c r="CP6" t="n">
         <v>4</v>
       </c>
-      <c r="CI6" t="n">
+      <c r="CQ6" t="n">
         <v>80</v>
       </c>
-      <c r="CJ6" t="n">
+      <c r="CR6" t="n">
         <v>394</v>
       </c>
-      <c r="CK6" t="n">
+      <c r="CS6" t="n">
         <v>2378</v>
       </c>
-      <c r="CL6" t="inlineStr"/>
-      <c r="CM6" t="inlineStr"/>
-      <c r="CN6" t="inlineStr"/>
-      <c r="CO6" t="inlineStr"/>
-      <c r="CP6" t="inlineStr"/>
-      <c r="CQ6" t="inlineStr"/>
-      <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2443,50 +2523,50 @@
         <v>21.444</v>
       </c>
       <c r="L7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="N7" t="n">
-        <v>26.2</v>
+        <v>23</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P7" t="n">
-        <v>55.102</v>
+        <v>54.239</v>
       </c>
       <c r="Q7" t="n">
-        <v>25.913</v>
+        <v>24.465</v>
       </c>
       <c r="R7" t="n">
-        <v>18.984</v>
+        <v>21.296</v>
       </c>
       <c r="S7" t="n">
-        <v>1.744</v>
+        <v>0.88</v>
       </c>
       <c r="T7" t="n">
-        <v>0.716</v>
+        <v>-0.732</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.46</v>
+        <v>-0.148</v>
       </c>
       <c r="V7" t="n">
-        <v>48.2</v>
+        <v>47</v>
       </c>
       <c r="W7" t="n">
-        <v>51.8</v>
+        <v>53</v>
       </c>
       <c r="X7" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.776</v>
+        <v>2.69</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -2495,53 +2575,53 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>99.68600000000001</v>
+        <v>99.789</v>
       </c>
       <c r="AC7" t="n">
-        <v>99.673</v>
+        <v>99.815</v>
       </c>
       <c r="AD7" t="n">
-        <v>99.505</v>
+        <v>99.57599999999999</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF7" t="n">
-        <v>51.419</v>
+        <v>46.228</v>
       </c>
       <c r="AG7" t="n">
-        <v>60.092</v>
+        <v>65.328</v>
       </c>
       <c r="AH7" t="n">
-        <v>22.538</v>
+        <v>15.843</v>
       </c>
       <c r="AI7" t="n">
-        <v>30.225</v>
+        <v>32.155</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.88</v>
+        <v>14.166</v>
       </c>
       <c r="AK7" t="n">
-        <v>21.608</v>
+        <v>29.98</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.815</v>
+        <v>1.844</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.859</v>
+        <v>4.088</v>
       </c>
       <c r="AN7" t="n">
-        <v>5.268</v>
+        <v>4.696</v>
       </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>largest deviation AWAY -2.5 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +0.9 pp; n_eff=100; market inside 95% CI; avg similarity 99.8%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -2553,31 +2633,31 @@
         <v>179331</v>
       </c>
       <c r="AT7" t="n">
-        <v>2.441</v>
+        <v>2.641</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.003</v>
+        <v>-2.197</v>
       </c>
       <c r="AV7" t="n">
-        <v>-3.444</v>
+        <v>-0.444</v>
       </c>
       <c r="AW7" t="n">
         <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.792</v>
+        <v>1.81</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.984</v>
+        <v>0.88</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.094</v>
+        <v>0.529</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.517</v>
+        <v>-0.506</v>
       </c>
       <c r="BB7" t="n">
-        <v>-1.876</v>
+        <v>-0.108</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
@@ -2591,111 +2671,127 @@
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="n">
         <v>200</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.061</v>
+        <v>0.596</v>
       </c>
       <c r="BJ7" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK7" t="n">
-        <v>55.8</v>
+        <v>56</v>
       </c>
       <c r="BL7" t="n">
-        <v>26.2</v>
+        <v>23</v>
       </c>
       <c r="BM7" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>55.102</v>
+        <v>54.239</v>
       </c>
       <c r="BO7" t="n">
-        <v>25.913</v>
+        <v>24.465</v>
       </c>
       <c r="BP7" t="n">
-        <v>18.984</v>
+        <v>21.296</v>
       </c>
       <c r="BQ7" t="n">
-        <v>99.68600000000001</v>
+        <v>99.789</v>
       </c>
       <c r="BR7" t="n">
-        <v>312</v>
+        <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>51.282</v>
+        <v>45</v>
       </c>
       <c r="BT7" t="n">
-        <v>27.885</v>
+        <v>35</v>
       </c>
       <c r="BU7" t="n">
-        <v>20.833</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
-        <v>52.093</v>
+        <v>50.572</v>
       </c>
       <c r="BW7" t="n">
-        <v>26.835</v>
+        <v>28.465</v>
       </c>
       <c r="BX7" t="n">
-        <v>21.072</v>
+        <v>20.963</v>
       </c>
       <c r="BY7" t="n">
-        <v>97.95</v>
+        <v>98</v>
       </c>
       <c r="BZ7" t="n">
-        <v>41.64</v>
+        <v>100</v>
       </c>
       <c r="CA7" t="n">
-        <v>40.379</v>
+        <v>52</v>
       </c>
       <c r="CB7" t="n">
-        <v>17.981</v>
+        <v>23</v>
       </c>
       <c r="CC7" t="n">
-        <v>317</v>
+        <v>25</v>
       </c>
       <c r="CD7" t="n">
+        <v>52.906</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>24.465</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>99.309</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>43.056</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>33.333</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>23.611</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>72</v>
+      </c>
+      <c r="CL7" t="n">
         <v>2444</v>
       </c>
-      <c r="CE7" t="n">
+      <c r="CM7" t="n">
         <v>8720</v>
       </c>
-      <c r="CF7" t="n">
+      <c r="CN7" t="n">
         <v>16709</v>
       </c>
-      <c r="CG7" t="n">
+      <c r="CO7" t="n">
         <v>32526</v>
       </c>
-      <c r="CH7" t="n">
+      <c r="CP7" t="n">
         <v>4</v>
       </c>
-      <c r="CI7" t="n">
+      <c r="CQ7" t="n">
         <v>64</v>
       </c>
-      <c r="CJ7" t="n">
+      <c r="CR7" t="n">
         <v>262</v>
       </c>
-      <c r="CK7" t="n">
+      <c r="CS7" t="n">
         <v>1739</v>
       </c>
-      <c r="CL7" t="inlineStr"/>
-      <c r="CM7" t="inlineStr"/>
-      <c r="CN7" t="inlineStr"/>
-      <c r="CO7" t="inlineStr"/>
-      <c r="CP7" t="inlineStr"/>
-      <c r="CQ7" t="inlineStr"/>
-      <c r="CR7" t="inlineStr"/>
-      <c r="CS7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2742,50 +2838,50 @@
         <v>7.131</v>
       </c>
       <c r="L8" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>80.8</v>
+        <v>83</v>
       </c>
       <c r="N8" t="n">
-        <v>13.8</v>
+        <v>16</v>
       </c>
       <c r="O8" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>79.676</v>
+        <v>78.911</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.429</v>
+        <v>16.002</v>
       </c>
       <c r="R8" t="n">
-        <v>5.895</v>
+        <v>5.088</v>
       </c>
       <c r="S8" t="n">
-        <v>2.81</v>
+        <v>2.045</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.573</v>
+        <v>-0.001</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.237</v>
+        <v>-2.044</v>
       </c>
       <c r="V8" t="n">
-        <v>55.2</v>
+        <v>53</v>
       </c>
       <c r="W8" t="n">
-        <v>44.8</v>
+        <v>47</v>
       </c>
       <c r="X8" t="n">
-        <v>39.4</v>
+        <v>37</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.916</v>
+        <v>2.83</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -2794,43 +2890,43 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>99.321</v>
+        <v>99.131</v>
       </c>
       <c r="AC8" t="n">
-        <v>99.288</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>98.80200000000001</v>
+        <v>98.25700000000001</v>
       </c>
       <c r="AE8" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF8" t="n">
-        <v>77.11799999999999</v>
+        <v>74.452</v>
       </c>
       <c r="AG8" t="n">
-        <v>84.012</v>
+        <v>89.107</v>
       </c>
       <c r="AH8" t="n">
-        <v>11.052</v>
+        <v>10.095</v>
       </c>
       <c r="AI8" t="n">
-        <v>17.1</v>
+        <v>24.42</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.737</v>
+        <v>0.177</v>
       </c>
       <c r="AK8" t="n">
-        <v>7.743</v>
+        <v>5.449</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.255</v>
+        <v>1.267</v>
       </c>
       <c r="AM8" t="n">
-        <v>6.93</v>
+        <v>6.249</v>
       </c>
       <c r="AN8" t="n">
-        <v>16.965</v>
+        <v>19.656</v>
       </c>
       <c r="AO8" t="n">
         <v>55.789</v>
@@ -2842,7 +2938,7 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>largest deviation HOME +2.8 pp; n_eff=500; market outside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +2.0 pp; n_eff=100; market inside 95% CI; avg similarity 99.1%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -2851,34 +2947,34 @@
         </is>
       </c>
       <c r="AS8" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.934</v>
+        <v>6.134</v>
       </c>
       <c r="AU8" t="n">
-        <v>-2.203</v>
+        <v>-0.003</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.731</v>
+        <v>-6.131</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.356</v>
+        <v>2.38</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.086</v>
+        <v>1.455</v>
       </c>
       <c r="BA8" t="n">
-        <v>-1.343</v>
+        <v>-0.001</v>
       </c>
       <c r="BB8" t="n">
-        <v>-1.504</v>
+        <v>-2.383</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
@@ -2887,131 +2983,131 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="n">
         <v>200</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.037</v>
+        <v>0.017</v>
       </c>
       <c r="BJ8" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK8" t="n">
-        <v>80.8</v>
+        <v>83</v>
       </c>
       <c r="BL8" t="n">
-        <v>13.8</v>
+        <v>16</v>
       </c>
       <c r="BM8" t="n">
-        <v>5.4</v>
+        <v>1</v>
       </c>
       <c r="BN8" t="n">
-        <v>79.676</v>
+        <v>78.911</v>
       </c>
       <c r="BO8" t="n">
-        <v>14.429</v>
+        <v>16.002</v>
       </c>
       <c r="BP8" t="n">
-        <v>5.895</v>
+        <v>5.088</v>
       </c>
       <c r="BQ8" t="n">
-        <v>99.321</v>
+        <v>99.131</v>
       </c>
       <c r="BR8" t="n">
-        <v>238</v>
+        <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>79.83199999999999</v>
+        <v>77</v>
       </c>
       <c r="BT8" t="n">
-        <v>12.605</v>
+        <v>18</v>
       </c>
       <c r="BU8" t="n">
-        <v>7.563</v>
+        <v>5</v>
       </c>
       <c r="BV8" t="n">
-        <v>78.47799999999999</v>
+        <v>76.911</v>
       </c>
       <c r="BW8" t="n">
-        <v>14.157</v>
+        <v>16.669</v>
       </c>
       <c r="BX8" t="n">
-        <v>7.366</v>
+        <v>6.421</v>
       </c>
       <c r="BY8" t="n">
-        <v>98.355</v>
+        <v>97.529</v>
       </c>
       <c r="BZ8" t="n">
-        <v>60.784</v>
+        <v>100</v>
       </c>
       <c r="CA8" t="n">
-        <v>30.252</v>
+        <v>74</v>
       </c>
       <c r="CB8" t="n">
-        <v>8.964</v>
+        <v>21</v>
       </c>
       <c r="CC8" t="n">
-        <v>357</v>
+        <v>5</v>
       </c>
       <c r="CD8" t="n">
-        <v>515</v>
+        <v>75.911</v>
       </c>
       <c r="CE8" t="n">
-        <v>1872</v>
+        <v>17.669</v>
       </c>
       <c r="CF8" t="n">
-        <v>3247</v>
+        <v>6.421</v>
       </c>
       <c r="CG8" t="n">
-        <v>5482</v>
+        <v>98.691</v>
       </c>
       <c r="CH8" t="n">
+        <v>63</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>31</v>
+      </c>
+      <c r="CJ8" t="n">
         <v>6</v>
       </c>
-      <c r="CI8" t="n">
-        <v>26</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>60</v>
-      </c>
       <c r="CK8" t="n">
-        <v>189</v>
+        <v>100</v>
       </c>
       <c r="CL8" t="n">
-        <v>500</v>
+        <v>371</v>
       </c>
       <c r="CM8" t="n">
-        <v>79</v>
+        <v>1326</v>
       </c>
       <c r="CN8" t="n">
-        <v>15.4</v>
+        <v>2265</v>
       </c>
       <c r="CO8" t="n">
-        <v>5.6</v>
+        <v>3777</v>
       </c>
       <c r="CP8" t="n">
-        <v>78.39</v>
+        <v>3</v>
       </c>
       <c r="CQ8" t="n">
-        <v>15.572</v>
+        <v>14</v>
       </c>
       <c r="CR8" t="n">
-        <v>6.038</v>
+        <v>40</v>
       </c>
       <c r="CS8" t="n">
-        <v>98.896</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
@@ -3059,50 +3155,50 @@
         <v>60.054</v>
       </c>
       <c r="L9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N9" t="n">
-        <v>22.4</v>
+        <v>25</v>
       </c>
       <c r="O9" t="n">
-        <v>63.6</v>
+        <v>60</v>
       </c>
       <c r="P9" t="n">
-        <v>14.688</v>
+        <v>15.938</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.725</v>
+        <v>24.026</v>
       </c>
       <c r="R9" t="n">
-        <v>62.587</v>
+        <v>60.036</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.719</v>
+        <v>-0.469</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8129999999999999</v>
+        <v>0.487</v>
       </c>
       <c r="U9" t="n">
-        <v>2.533</v>
+        <v>-0.018</v>
       </c>
       <c r="V9" t="n">
-        <v>56.6</v>
+        <v>60</v>
       </c>
       <c r="W9" t="n">
-        <v>43.4</v>
+        <v>40</v>
       </c>
       <c r="X9" t="n">
-        <v>52.4</v>
+        <v>59</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.812</v>
+        <v>2.96</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -3111,55 +3207,55 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>99.349</v>
+        <v>99.19799999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>99.312</v>
+        <v>99.19199999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>98.89700000000001</v>
+        <v>98.566</v>
       </c>
       <c r="AE9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.232</v>
+        <v>9.305999999999999</v>
       </c>
       <c r="AG9" t="n">
-        <v>17.317</v>
+        <v>23.284</v>
       </c>
       <c r="AH9" t="n">
-        <v>18.964</v>
+        <v>17.545</v>
       </c>
       <c r="AI9" t="n">
-        <v>26.257</v>
+        <v>34.305</v>
       </c>
       <c r="AJ9" t="n">
-        <v>59.294</v>
+        <v>50.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>67.699</v>
+        <v>69.06</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.808</v>
+        <v>6.274</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.4</v>
+        <v>4.162</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.598</v>
+        <v>1.666</v>
       </c>
       <c r="AO9" t="n">
         <v>52.674</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +2.5 pp; n_eff=500; market inside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
+          <t>largest deviation DRAW +0.5 pp; n_eff=100; market inside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -3168,34 +3264,34 @@
         </is>
       </c>
       <c r="AS9" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT9" t="n">
-        <v>-2.407</v>
+        <v>-1.407</v>
       </c>
       <c r="AU9" t="n">
-        <v>-1.139</v>
+        <v>1.461</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.546</v>
+        <v>-0.054</v>
       </c>
       <c r="AW9" t="n">
         <v>3</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.952</v>
+        <v>2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-1.453</v>
+        <v>-0.38</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0.6</v>
+        <v>0.344</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.619</v>
+        <v>-0.011</v>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
@@ -3204,131 +3300,131 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="n">
         <v>200</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.105</v>
+        <v>0.704</v>
       </c>
       <c r="BJ9" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK9" t="n">
+        <v>15</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>25</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>15.938</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>24.026</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>60.036</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>99.19799999999999</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>17</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>23</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>16.605</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>23.359</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>60.036</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>98.197</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>100</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>18</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>26</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>56</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>16.938</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>24.359</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>58.703</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>99.071</v>
+      </c>
+      <c r="CH9" t="n">
         <v>14</v>
       </c>
-      <c r="BL9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>14.688</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>22.725</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>62.587</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>99.349</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>232</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>20.69</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>66.81</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>14.309</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>22.009</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>63.682</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>98.19199999999999</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>16.562</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>37.812</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>45.625</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>320</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>521</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>1790</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>3078</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>5615</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>13</v>
-      </c>
       <c r="CI9" t="n">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="CJ9" t="n">
-        <v>209</v>
+        <v>44</v>
       </c>
       <c r="CK9" t="n">
-        <v>604</v>
+        <v>100</v>
       </c>
       <c r="CL9" t="n">
-        <v>500</v>
+        <v>337</v>
       </c>
       <c r="CM9" t="n">
-        <v>16</v>
+        <v>1196</v>
       </c>
       <c r="CN9" t="n">
-        <v>22</v>
+        <v>2033</v>
       </c>
       <c r="CO9" t="n">
-        <v>62</v>
+        <v>3673</v>
       </c>
       <c r="CP9" t="n">
-        <v>16.116</v>
+        <v>8</v>
       </c>
       <c r="CQ9" t="n">
-        <v>22.44</v>
+        <v>40</v>
       </c>
       <c r="CR9" t="n">
-        <v>61.444</v>
+        <v>126</v>
       </c>
       <c r="CS9" t="n">
-        <v>98.786</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -3376,50 +3472,50 @@
         <v>25.254</v>
       </c>
       <c r="L10" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>50.2</v>
+        <v>54</v>
       </c>
       <c r="N10" t="n">
-        <v>25.2</v>
+        <v>23</v>
       </c>
       <c r="O10" t="n">
-        <v>24.6</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>49.978</v>
+        <v>50.948</v>
       </c>
       <c r="Q10" t="n">
-        <v>25.235</v>
+        <v>24.549</v>
       </c>
       <c r="R10" t="n">
-        <v>24.787</v>
+        <v>24.503</v>
       </c>
       <c r="S10" t="n">
-        <v>0.556</v>
+        <v>1.526</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.775</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.467</v>
+        <v>-0.751</v>
       </c>
       <c r="V10" t="n">
-        <v>53.8</v>
+        <v>55</v>
       </c>
       <c r="W10" t="n">
-        <v>46.2</v>
+        <v>45</v>
       </c>
       <c r="X10" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.884</v>
+        <v>2.84</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -3428,43 +3524,43 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>99.599</v>
+        <v>99.762</v>
       </c>
       <c r="AC10" t="n">
-        <v>99.57599999999999</v>
+        <v>99.77800000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>99.369</v>
+        <v>99.489</v>
       </c>
       <c r="AE10" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF10" t="n">
-        <v>45.833</v>
+        <v>44.265</v>
       </c>
       <c r="AG10" t="n">
-        <v>54.564</v>
+        <v>63.439</v>
       </c>
       <c r="AH10" t="n">
-        <v>21.593</v>
+        <v>15.843</v>
       </c>
       <c r="AI10" t="n">
-        <v>29.185</v>
+        <v>32.155</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21.028</v>
+        <v>15.843</v>
       </c>
       <c r="AK10" t="n">
-        <v>28.559</v>
+        <v>32.155</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.001</v>
+        <v>1.963</v>
       </c>
       <c r="AM10" t="n">
-        <v>3.963</v>
+        <v>4.073</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.034</v>
+        <v>4.081</v>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr">
@@ -3474,7 +3570,7 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>largest deviation HOME +0.6 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +1.5 pp; n_eff=100; market inside 95% CI; avg similarity 99.8%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -3486,31 +3582,31 @@
         <v>179331</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.778</v>
+        <v>4.578</v>
       </c>
       <c r="AU10" t="n">
-        <v>-0.124</v>
+        <v>-2.324</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.654</v>
+        <v>-2.254</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.714</v>
+        <v>1.73</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.348</v>
+        <v>0.916</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0.064</v>
+        <v>-0.534</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.337</v>
+        <v>-0.519</v>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
@@ -3524,111 +3620,127 @@
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="n">
         <v>200</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.728</v>
+        <v>0.36</v>
       </c>
       <c r="BJ10" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK10" t="n">
-        <v>50.2</v>
+        <v>54</v>
       </c>
       <c r="BL10" t="n">
-        <v>25.2</v>
+        <v>23</v>
       </c>
       <c r="BM10" t="n">
-        <v>24.6</v>
+        <v>23</v>
       </c>
       <c r="BN10" t="n">
-        <v>49.978</v>
+        <v>50.948</v>
       </c>
       <c r="BO10" t="n">
-        <v>25.235</v>
+        <v>24.549</v>
       </c>
       <c r="BP10" t="n">
-        <v>24.787</v>
+        <v>24.503</v>
       </c>
       <c r="BQ10" t="n">
-        <v>99.599</v>
+        <v>99.762</v>
       </c>
       <c r="BR10" t="n">
-        <v>307</v>
+        <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>53.094</v>
+        <v>52</v>
       </c>
       <c r="BT10" t="n">
-        <v>26.71</v>
+        <v>34</v>
       </c>
       <c r="BU10" t="n">
-        <v>20.195</v>
+        <v>14</v>
       </c>
       <c r="BV10" t="n">
-        <v>51.646</v>
+        <v>50.281</v>
       </c>
       <c r="BW10" t="n">
-        <v>26.163</v>
+        <v>28.216</v>
       </c>
       <c r="BX10" t="n">
-        <v>22.191</v>
+        <v>21.503</v>
       </c>
       <c r="BY10" t="n">
-        <v>98.03700000000001</v>
+        <v>98.517</v>
       </c>
       <c r="BZ10" t="n">
-        <v>39.085</v>
+        <v>100</v>
       </c>
       <c r="CA10" t="n">
-        <v>40.493</v>
+        <v>58</v>
       </c>
       <c r="CB10" t="n">
-        <v>20.423</v>
+        <v>26</v>
       </c>
       <c r="CC10" t="n">
-        <v>284</v>
+        <v>16</v>
       </c>
       <c r="CD10" t="n">
+        <v>52.281</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>25.549</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>22.169</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>99.706</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>39.655</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>37.931</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>22.414</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>58</v>
+      </c>
+      <c r="CL10" t="n">
         <v>1417</v>
       </c>
-      <c r="CE10" t="n">
+      <c r="CM10" t="n">
         <v>6247</v>
       </c>
-      <c r="CF10" t="n">
+      <c r="CN10" t="n">
         <v>15064</v>
       </c>
-      <c r="CG10" t="n">
+      <c r="CO10" t="n">
         <v>36467</v>
       </c>
-      <c r="CH10" t="n">
+      <c r="CP10" t="n">
         <v>16</v>
       </c>
-      <c r="CI10" t="n">
+      <c r="CQ10" t="n">
         <v>127</v>
       </c>
-      <c r="CJ10" t="n">
+      <c r="CR10" t="n">
         <v>405</v>
       </c>
-      <c r="CK10" t="n">
+      <c r="CS10" t="n">
         <v>2245</v>
       </c>
-      <c r="CL10" t="inlineStr"/>
-      <c r="CM10" t="inlineStr"/>
-      <c r="CN10" t="inlineStr"/>
-      <c r="CO10" t="inlineStr"/>
-      <c r="CP10" t="inlineStr"/>
-      <c r="CQ10" t="inlineStr"/>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3675,50 +3787,50 @@
         <v>7.598</v>
       </c>
       <c r="L11" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M11" t="n">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="N11" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="O11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>82.309</v>
+        <v>80.721</v>
       </c>
       <c r="Q11" t="n">
-        <v>11.663</v>
+        <v>12.214</v>
       </c>
       <c r="R11" t="n">
-        <v>6.028</v>
+        <v>7.065</v>
       </c>
       <c r="S11" t="n">
-        <v>2.728</v>
+        <v>1.14</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.158</v>
+        <v>-0.607</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.57</v>
+        <v>-0.533</v>
       </c>
       <c r="V11" t="n">
-        <v>71.2</v>
+        <v>70</v>
       </c>
       <c r="W11" t="n">
-        <v>28.8</v>
+        <v>30</v>
       </c>
       <c r="X11" t="n">
-        <v>53.8</v>
+        <v>56</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.642</v>
+        <v>3.65</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -3727,43 +3839,43 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>99.16500000000001</v>
+        <v>99.42400000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>99.14</v>
+        <v>99.455</v>
       </c>
       <c r="AD11" t="n">
-        <v>98.49299999999999</v>
+        <v>98.83</v>
       </c>
       <c r="AE11" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF11" t="n">
-        <v>79.886</v>
+        <v>74.452</v>
       </c>
       <c r="AG11" t="n">
-        <v>86.404</v>
+        <v>89.107</v>
       </c>
       <c r="AH11" t="n">
-        <v>8.726000000000001</v>
+        <v>6.254</v>
       </c>
       <c r="AI11" t="n">
-        <v>14.265</v>
+        <v>18.631</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.737</v>
+        <v>2.779</v>
       </c>
       <c r="AK11" t="n">
-        <v>7.743</v>
+        <v>12.477</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.215</v>
+        <v>1.239</v>
       </c>
       <c r="AM11" t="n">
-        <v>8.574</v>
+        <v>8.186999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>16.589</v>
+        <v>14.154</v>
       </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr">
@@ -3773,7 +3885,7 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>largest deviation HOME +2.7 pp; n_eff=500; market outside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +1.1 pp; n_eff=100; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -3785,31 +3897,31 @@
         <v>179331</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.819</v>
+        <v>3.419</v>
       </c>
       <c r="AU11" t="n">
-        <v>-1.621</v>
+        <v>-1.821</v>
       </c>
       <c r="AV11" t="n">
-        <v>-2.198</v>
+        <v>-1.598</v>
       </c>
       <c r="AW11" t="n">
         <v>3</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.874</v>
+        <v>2.89</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.768</v>
+        <v>0.76</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.119</v>
+        <v>0.848</v>
       </c>
       <c r="BA11" t="n">
-        <v>-1.084</v>
+        <v>-0.545</v>
       </c>
       <c r="BB11" t="n">
-        <v>-1.855</v>
+        <v>-0.603</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
@@ -3823,111 +3935,127 @@
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="n">
         <v>200</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.034</v>
+        <v>0.396</v>
       </c>
       <c r="BJ11" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK11" t="n">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="BL11" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="BM11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BN11" t="n">
-        <v>82.309</v>
+        <v>80.721</v>
       </c>
       <c r="BO11" t="n">
-        <v>11.663</v>
+        <v>12.214</v>
       </c>
       <c r="BP11" t="n">
-        <v>6.028</v>
+        <v>7.065</v>
       </c>
       <c r="BQ11" t="n">
-        <v>99.16500000000001</v>
+        <v>99.42400000000001</v>
       </c>
       <c r="BR11" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>78.333</v>
+        <v>82</v>
       </c>
       <c r="BT11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.667</v>
+        <v>4</v>
       </c>
       <c r="BV11" t="n">
-        <v>79.29300000000001</v>
+        <v>80.387</v>
       </c>
       <c r="BW11" t="n">
-        <v>13.324</v>
+        <v>13.214</v>
       </c>
       <c r="BX11" t="n">
-        <v>7.383</v>
+        <v>6.399</v>
       </c>
       <c r="BY11" t="n">
-        <v>98.303</v>
+        <v>97.259</v>
       </c>
       <c r="BZ11" t="n">
-        <v>61.081</v>
+        <v>100</v>
       </c>
       <c r="CA11" t="n">
-        <v>28.919</v>
+        <v>83</v>
       </c>
       <c r="CB11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CC11" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="CD11" t="n">
+        <v>80.721</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>12.214</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>7.065</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>99.408</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>48.387</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>12.903</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>62</v>
+      </c>
+      <c r="CL11" t="n">
         <v>342</v>
       </c>
-      <c r="CE11" t="n">
+      <c r="CM11" t="n">
         <v>1469</v>
       </c>
-      <c r="CF11" t="n">
+      <c r="CN11" t="n">
         <v>2534</v>
       </c>
-      <c r="CG11" t="n">
+      <c r="CO11" t="n">
         <v>4324</v>
       </c>
-      <c r="CH11" t="n">
+      <c r="CP11" t="n">
         <v>0</v>
       </c>
-      <c r="CI11" t="n">
+      <c r="CQ11" t="n">
         <v>4</v>
       </c>
-      <c r="CJ11" t="n">
+      <c r="CR11" t="n">
         <v>25</v>
       </c>
-      <c r="CK11" t="n">
+      <c r="CS11" t="n">
         <v>94</v>
       </c>
-      <c r="CL11" t="inlineStr"/>
-      <c r="CM11" t="inlineStr"/>
-      <c r="CN11" t="inlineStr"/>
-      <c r="CO11" t="inlineStr"/>
-      <c r="CP11" t="inlineStr"/>
-      <c r="CQ11" t="inlineStr"/>
-      <c r="CR11" t="inlineStr"/>
-      <c r="CS11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3974,50 +4102,50 @@
         <v>33.452</v>
       </c>
       <c r="L12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
         <v>35</v>
       </c>
       <c r="N12" t="n">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="O12" t="n">
-        <v>36.4</v>
+        <v>45</v>
       </c>
       <c r="P12" t="n">
-        <v>36.494</v>
+        <v>38.487</v>
       </c>
       <c r="Q12" t="n">
-        <v>27.948</v>
+        <v>24.212</v>
       </c>
       <c r="R12" t="n">
-        <v>35.558</v>
+        <v>37.301</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.736</v>
+        <v>-1.743</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>-2.106</v>
       </c>
       <c r="U12" t="n">
-        <v>2.106</v>
+        <v>3.849</v>
       </c>
       <c r="V12" t="n">
-        <v>57.4</v>
+        <v>55</v>
       </c>
       <c r="W12" t="n">
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="X12" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.932</v>
+        <v>2.8</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -4026,53 +4154,53 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>99.553</v>
+        <v>99.72199999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>99.52</v>
+        <v>99.755</v>
       </c>
       <c r="AD12" t="n">
-        <v>99.313</v>
+        <v>99.459</v>
       </c>
       <c r="AE12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF12" t="n">
-        <v>30.948</v>
+        <v>26.364</v>
       </c>
       <c r="AG12" t="n">
-        <v>39.281</v>
+        <v>44.746</v>
       </c>
       <c r="AH12" t="n">
-        <v>24.814</v>
+        <v>13.337</v>
       </c>
       <c r="AI12" t="n">
-        <v>32.712</v>
+        <v>28.883</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32.301</v>
+        <v>35.614</v>
       </c>
       <c r="AK12" t="n">
-        <v>40.706</v>
+        <v>54.756</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.74</v>
+        <v>2.598</v>
       </c>
       <c r="AM12" t="n">
-        <v>3.578</v>
+        <v>4.13</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.812</v>
+        <v>2.681</v>
       </c>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>largest deviation HOME -3.7 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY +3.8 pp; n_eff=100; market outside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -4087,28 +4215,28 @@
         <v>-5.23</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.282</v>
+        <v>-6.318</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.948</v>
+        <v>11.548</v>
       </c>
       <c r="AW12" t="n">
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.464</v>
+        <v>1.32</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.468</v>
+        <v>1.48</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-2.385</v>
+        <v>-1.067</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.159</v>
+        <v>-1.435</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.397</v>
+        <v>2.448</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
@@ -4122,111 +4250,127 @@
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="n">
         <v>200</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.017</v>
+        <v>0.014</v>
       </c>
       <c r="BJ12" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK12" t="n">
         <v>35</v>
       </c>
       <c r="BL12" t="n">
-        <v>28.6</v>
+        <v>20</v>
       </c>
       <c r="BM12" t="n">
-        <v>36.4</v>
+        <v>45</v>
       </c>
       <c r="BN12" t="n">
-        <v>36.494</v>
+        <v>38.487</v>
       </c>
       <c r="BO12" t="n">
-        <v>27.948</v>
+        <v>24.212</v>
       </c>
       <c r="BP12" t="n">
-        <v>35.558</v>
+        <v>37.301</v>
       </c>
       <c r="BQ12" t="n">
-        <v>99.553</v>
+        <v>99.72199999999999</v>
       </c>
       <c r="BR12" t="n">
-        <v>307</v>
+        <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>40.391</v>
+        <v>46</v>
       </c>
       <c r="BT12" t="n">
-        <v>30.293</v>
+        <v>15</v>
       </c>
       <c r="BU12" t="n">
-        <v>29.316</v>
+        <v>39</v>
       </c>
       <c r="BV12" t="n">
-        <v>40.328</v>
+        <v>42.154</v>
       </c>
       <c r="BW12" t="n">
-        <v>28.725</v>
+        <v>22.545</v>
       </c>
       <c r="BX12" t="n">
-        <v>30.947</v>
+        <v>35.301</v>
       </c>
       <c r="BY12" t="n">
-        <v>97.744</v>
+        <v>97.866</v>
       </c>
       <c r="BZ12" t="n">
-        <v>28.889</v>
+        <v>100</v>
       </c>
       <c r="CA12" t="n">
-        <v>40.952</v>
+        <v>39</v>
       </c>
       <c r="CB12" t="n">
-        <v>30.159</v>
+        <v>21</v>
       </c>
       <c r="CC12" t="n">
-        <v>315</v>
+        <v>40</v>
       </c>
       <c r="CD12" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>24.545</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>35.634</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>99.51300000000001</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>24.242</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>28.788</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>66</v>
+      </c>
+      <c r="CL12" t="n">
         <v>1121</v>
       </c>
-      <c r="CE12" t="n">
+      <c r="CM12" t="n">
         <v>5189</v>
       </c>
-      <c r="CF12" t="n">
+      <c r="CN12" t="n">
         <v>13975</v>
       </c>
-      <c r="CG12" t="n">
+      <c r="CO12" t="n">
         <v>37026</v>
       </c>
-      <c r="CH12" t="n">
+      <c r="CP12" t="n">
         <v>12</v>
       </c>
-      <c r="CI12" t="n">
+      <c r="CQ12" t="n">
         <v>94</v>
       </c>
-      <c r="CJ12" t="n">
+      <c r="CR12" t="n">
         <v>310</v>
       </c>
-      <c r="CK12" t="n">
+      <c r="CS12" t="n">
         <v>1515</v>
       </c>
-      <c r="CL12" t="inlineStr"/>
-      <c r="CM12" t="inlineStr"/>
-      <c r="CN12" t="inlineStr"/>
-      <c r="CO12" t="inlineStr"/>
-      <c r="CP12" t="inlineStr"/>
-      <c r="CQ12" t="inlineStr"/>
-      <c r="CR12" t="inlineStr"/>
-      <c r="CS12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4273,105 +4417,105 @@
         <v>18.545</v>
       </c>
       <c r="L13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M13" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="N13" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="O13" t="n">
-        <v>16.2</v>
+        <v>23</v>
       </c>
       <c r="P13" t="n">
-        <v>63.241</v>
+        <v>58.23</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.889</v>
+        <v>21.74</v>
       </c>
       <c r="R13" t="n">
-        <v>16.87</v>
+        <v>20.03</v>
       </c>
       <c r="S13" t="n">
-        <v>4.397</v>
+        <v>-0.615</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.722</v>
+        <v>-0.87</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.675</v>
+        <v>1.485</v>
       </c>
       <c r="V13" t="n">
-        <v>60.2</v>
+        <v>57</v>
       </c>
       <c r="W13" t="n">
-        <v>39.8</v>
+        <v>43</v>
       </c>
       <c r="X13" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.084</v>
+        <v>3.18</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>MODERATE HISTORICAL DEVIATION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>99.57599999999999</v>
+        <v>99.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>99.55</v>
+        <v>99.738</v>
       </c>
       <c r="AD13" t="n">
-        <v>99.313</v>
+        <v>99.45</v>
       </c>
       <c r="AE13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF13" t="n">
-        <v>60.719</v>
+        <v>47.215</v>
       </c>
       <c r="AG13" t="n">
-        <v>69.05200000000001</v>
+        <v>66.267</v>
       </c>
       <c r="AH13" t="n">
-        <v>15.618</v>
+        <v>13.337</v>
       </c>
       <c r="AI13" t="n">
-        <v>22.458</v>
+        <v>28.883</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13.23</v>
+        <v>15.843</v>
       </c>
       <c r="AK13" t="n">
-        <v>19.685</v>
+        <v>32.155</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.581</v>
+        <v>1.717</v>
       </c>
       <c r="AM13" t="n">
-        <v>5.028</v>
+        <v>4.6</v>
       </c>
       <c r="AN13" t="n">
-        <v>5.928</v>
+        <v>4.993</v>
       </c>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>largest deviation HOME +4.4 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY +1.5 pp; n_eff=100; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
@@ -4383,31 +4527,31 @@
         <v>179331</v>
       </c>
       <c r="AT13" t="n">
-        <v>6.155</v>
+        <v>-1.845</v>
       </c>
       <c r="AU13" t="n">
-        <v>-3.81</v>
+        <v>-2.61</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.345</v>
+        <v>4.455</v>
       </c>
       <c r="AW13" t="n">
         <v>3</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.014</v>
+        <v>1.21</v>
       </c>
       <c r="AZ13" t="n">
-        <v>2.797</v>
+        <v>-0.375</v>
       </c>
       <c r="BA13" t="n">
-        <v>-2.037</v>
+        <v>-0.624</v>
       </c>
       <c r="BB13" t="n">
-        <v>-1.349</v>
+        <v>1.146</v>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
@@ -4421,111 +4565,127 @@
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="n">
         <v>200</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.005</v>
+        <v>0.252</v>
       </c>
       <c r="BJ13" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK13" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="BL13" t="n">
-        <v>18.8</v>
+        <v>20</v>
       </c>
       <c r="BM13" t="n">
-        <v>16.2</v>
+        <v>23</v>
       </c>
       <c r="BN13" t="n">
-        <v>63.241</v>
+        <v>58.23</v>
       </c>
       <c r="BO13" t="n">
-        <v>19.889</v>
+        <v>21.74</v>
       </c>
       <c r="BP13" t="n">
-        <v>16.87</v>
+        <v>20.03</v>
       </c>
       <c r="BQ13" t="n">
-        <v>99.57599999999999</v>
+        <v>99.73</v>
       </c>
       <c r="BR13" t="n">
-        <v>310</v>
+        <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>62.258</v>
+        <v>62</v>
       </c>
       <c r="BT13" t="n">
-        <v>21.29</v>
+        <v>20</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.452</v>
+        <v>18</v>
       </c>
       <c r="BV13" t="n">
-        <v>60.919</v>
+        <v>59.896</v>
       </c>
       <c r="BW13" t="n">
-        <v>21.808</v>
+        <v>21.74</v>
       </c>
       <c r="BX13" t="n">
-        <v>17.273</v>
+        <v>18.363</v>
       </c>
       <c r="BY13" t="n">
-        <v>98.017</v>
+        <v>98.485</v>
       </c>
       <c r="BZ13" t="n">
-        <v>51.724</v>
+        <v>100</v>
       </c>
       <c r="CA13" t="n">
-        <v>32.759</v>
+        <v>62</v>
       </c>
       <c r="CB13" t="n">
-        <v>15.517</v>
+        <v>17</v>
       </c>
       <c r="CC13" t="n">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="CD13" t="n">
+        <v>59.896</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>19.363</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>99.705</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>49.091</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>29.091</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>21.818</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>55</v>
+      </c>
+      <c r="CL13" t="n">
         <v>1201</v>
       </c>
-      <c r="CE13" t="n">
+      <c r="CM13" t="n">
         <v>4815</v>
       </c>
-      <c r="CF13" t="n">
+      <c r="CN13" t="n">
         <v>10704</v>
       </c>
-      <c r="CG13" t="n">
+      <c r="CO13" t="n">
         <v>23025</v>
       </c>
-      <c r="CH13" t="n">
+      <c r="CP13" t="n">
         <v>12</v>
       </c>
-      <c r="CI13" t="n">
+      <c r="CQ13" t="n">
         <v>59</v>
       </c>
-      <c r="CJ13" t="n">
+      <c r="CR13" t="n">
         <v>216</v>
       </c>
-      <c r="CK13" t="n">
+      <c r="CS13" t="n">
         <v>1198</v>
       </c>
-      <c r="CL13" t="inlineStr"/>
-      <c r="CM13" t="inlineStr"/>
-      <c r="CN13" t="inlineStr"/>
-      <c r="CO13" t="inlineStr"/>
-      <c r="CP13" t="inlineStr"/>
-      <c r="CQ13" t="inlineStr"/>
-      <c r="CR13" t="inlineStr"/>
-      <c r="CS13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4572,50 +4732,50 @@
         <v>14.118</v>
       </c>
       <c r="L14" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>71.2</v>
+        <v>76</v>
       </c>
       <c r="N14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O14" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>69.691</v>
+        <v>69.279</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.561</v>
+        <v>17.975</v>
       </c>
       <c r="R14" t="n">
-        <v>11.748</v>
+        <v>12.746</v>
       </c>
       <c r="S14" t="n">
-        <v>3.772</v>
+        <v>3.36</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.402</v>
+        <v>-1.987</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.37</v>
+        <v>-1.373</v>
       </c>
       <c r="V14" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="W14" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="X14" t="n">
-        <v>51.6</v>
+        <v>46</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.244</v>
+        <v>3.1</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -4624,43 +4784,43 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>99.527</v>
+        <v>99.748</v>
       </c>
       <c r="AC14" t="n">
-        <v>99.504</v>
+        <v>99.761</v>
       </c>
       <c r="AD14" t="n">
-        <v>99.199</v>
+        <v>99.441</v>
       </c>
       <c r="AE14" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF14" t="n">
-        <v>67.081</v>
+        <v>66.767</v>
       </c>
       <c r="AG14" t="n">
-        <v>74.996</v>
+        <v>83.309</v>
       </c>
       <c r="AH14" t="n">
-        <v>14.88</v>
+        <v>8.526</v>
       </c>
       <c r="AI14" t="n">
-        <v>21.608</v>
+        <v>22.137</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8.372</v>
+        <v>5.523</v>
       </c>
       <c r="AK14" t="n">
-        <v>13.826</v>
+        <v>17.437</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.435</v>
+        <v>1.443</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.388</v>
+        <v>5.563</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.512</v>
+        <v>7.846</v>
       </c>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr">
@@ -4670,7 +4830,7 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>largest deviation HOME +3.8 pp; n_eff=500; market outside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +3.4 pp; n_eff=100; market outside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
@@ -4682,31 +4842,31 @@
         <v>179331</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.281</v>
+        <v>10.081</v>
       </c>
       <c r="AU14" t="n">
-        <v>-1.962</v>
+        <v>-5.962</v>
       </c>
       <c r="AV14" t="n">
-        <v>-3.318</v>
+        <v>-4.118</v>
       </c>
       <c r="AW14" t="n">
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.358</v>
+        <v>2.38</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.886</v>
+        <v>0.72</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.491</v>
+        <v>2.127</v>
       </c>
       <c r="BA14" t="n">
-        <v>-1.098</v>
+        <v>-1.492</v>
       </c>
       <c r="BB14" t="n">
-        <v>-2.131</v>
+        <v>-1.183</v>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
@@ -4720,111 +4880,127 @@
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF14" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="n">
         <v>200</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.013</v>
+        <v>0.033</v>
       </c>
       <c r="BJ14" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK14" t="n">
-        <v>71.2</v>
+        <v>76</v>
       </c>
       <c r="BL14" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BM14" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="BN14" t="n">
-        <v>69.691</v>
+        <v>69.279</v>
       </c>
       <c r="BO14" t="n">
-        <v>18.561</v>
+        <v>17.975</v>
       </c>
       <c r="BP14" t="n">
-        <v>11.748</v>
+        <v>12.746</v>
       </c>
       <c r="BQ14" t="n">
-        <v>99.527</v>
+        <v>99.748</v>
       </c>
       <c r="BR14" t="n">
-        <v>258</v>
+        <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>63.566</v>
+        <v>71</v>
       </c>
       <c r="BT14" t="n">
-        <v>22.481</v>
+        <v>16</v>
       </c>
       <c r="BU14" t="n">
-        <v>13.953</v>
+        <v>13</v>
       </c>
       <c r="BV14" t="n">
-        <v>64.59399999999999</v>
+        <v>67.613</v>
       </c>
       <c r="BW14" t="n">
-        <v>21.381</v>
+        <v>18.642</v>
       </c>
       <c r="BX14" t="n">
-        <v>14.025</v>
+        <v>13.746</v>
       </c>
       <c r="BY14" t="n">
-        <v>98.122</v>
+        <v>98.465</v>
       </c>
       <c r="BZ14" t="n">
-        <v>51.815</v>
+        <v>100</v>
       </c>
       <c r="CA14" t="n">
-        <v>36.634</v>
+        <v>84</v>
       </c>
       <c r="CB14" t="n">
-        <v>11.551</v>
+        <v>9</v>
       </c>
       <c r="CC14" t="n">
-        <v>303</v>
+        <v>7</v>
       </c>
       <c r="CD14" t="n">
+        <v>71.946</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>16.308</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>11.746</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>99.68899999999999</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>32.609</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>6.522</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>46</v>
+      </c>
+      <c r="CL14" t="n">
         <v>961</v>
       </c>
-      <c r="CE14" t="n">
+      <c r="CM14" t="n">
         <v>3602</v>
       </c>
-      <c r="CF14" t="n">
+      <c r="CN14" t="n">
         <v>7068</v>
       </c>
-      <c r="CG14" t="n">
+      <c r="CO14" t="n">
         <v>13553</v>
       </c>
-      <c r="CH14" t="n">
+      <c r="CP14" t="n">
         <v>8</v>
       </c>
-      <c r="CI14" t="n">
+      <c r="CQ14" t="n">
         <v>30</v>
       </c>
-      <c r="CJ14" t="n">
+      <c r="CR14" t="n">
         <v>142</v>
       </c>
-      <c r="CK14" t="n">
+      <c r="CS14" t="n">
         <v>666</v>
       </c>
-      <c r="CL14" t="inlineStr"/>
-      <c r="CM14" t="inlineStr"/>
-      <c r="CN14" t="inlineStr"/>
-      <c r="CO14" t="inlineStr"/>
-      <c r="CP14" t="inlineStr"/>
-      <c r="CQ14" t="inlineStr"/>
-      <c r="CR14" t="inlineStr"/>
-      <c r="CS14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4871,50 +5047,50 @@
         <v>59.75</v>
       </c>
       <c r="L15" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M15" t="n">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="N15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O15" t="n">
-        <v>61.4</v>
+        <v>63</v>
       </c>
       <c r="P15" t="n">
-        <v>16.795</v>
+        <v>17.854</v>
       </c>
       <c r="Q15" t="n">
-        <v>22.277</v>
+        <v>21.313</v>
       </c>
       <c r="R15" t="n">
-        <v>60.929</v>
+        <v>60.833</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.487</v>
+        <v>0.573</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-1.656</v>
       </c>
       <c r="U15" t="n">
-        <v>1.179</v>
+        <v>1.083</v>
       </c>
       <c r="V15" t="n">
-        <v>55.8</v>
+        <v>55</v>
       </c>
       <c r="W15" t="n">
-        <v>44.2</v>
+        <v>45</v>
       </c>
       <c r="X15" t="n">
-        <v>52.8</v>
+        <v>50</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.834</v>
+        <v>2.69</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -4923,55 +5099,55 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>99.34</v>
+        <v>99.173</v>
       </c>
       <c r="AC15" t="n">
-        <v>99.291</v>
+        <v>99.172</v>
       </c>
       <c r="AD15" t="n">
-        <v>98.923</v>
+        <v>98.339</v>
       </c>
       <c r="AE15" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.596</v>
+        <v>12.515</v>
       </c>
       <c r="AG15" t="n">
-        <v>20.114</v>
+        <v>27.779</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.59</v>
+        <v>11.7</v>
       </c>
       <c r="AI15" t="n">
-        <v>25.837</v>
+        <v>26.668</v>
       </c>
       <c r="AJ15" t="n">
-        <v>57.061</v>
+        <v>53.22</v>
       </c>
       <c r="AK15" t="n">
-        <v>65.565</v>
+        <v>71.818</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.954</v>
+        <v>5.601</v>
       </c>
       <c r="AM15" t="n">
-        <v>4.489</v>
+        <v>4.692</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.641</v>
+        <v>1.644</v>
       </c>
       <c r="AO15" t="n">
         <v>54.545</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +1.2 pp; n_eff=500; market inside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
+          <t>largest deviation DRAW -1.7 pp; n_eff=100; market inside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
@@ -4980,34 +5156,34 @@
         </is>
       </c>
       <c r="AS15" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.681</v>
+        <v>1.719</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.969</v>
+        <v>-4.969</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.65</v>
+        <v>3.25</v>
       </c>
       <c r="AW15" t="n">
         <v>3</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.896</v>
+        <v>1.82</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0.403</v>
+        <v>0.455</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0.515</v>
+        <v>-1.181</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.752</v>
+        <v>0.663</v>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
@@ -5016,131 +5192,131 @@
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF15" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="n">
         <v>200</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.452</v>
+        <v>0.237</v>
       </c>
       <c r="BJ15" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK15" t="n">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="BL15" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BM15" t="n">
-        <v>61.4</v>
+        <v>63</v>
       </c>
       <c r="BN15" t="n">
-        <v>16.795</v>
+        <v>17.854</v>
       </c>
       <c r="BO15" t="n">
-        <v>22.277</v>
+        <v>21.313</v>
       </c>
       <c r="BP15" t="n">
-        <v>60.929</v>
+        <v>60.833</v>
       </c>
       <c r="BQ15" t="n">
-        <v>99.34</v>
+        <v>99.173</v>
       </c>
       <c r="BR15" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>14.035</v>
+        <v>15</v>
       </c>
       <c r="BT15" t="n">
-        <v>17.544</v>
+        <v>17</v>
       </c>
       <c r="BU15" t="n">
-        <v>68.42100000000001</v>
+        <v>68</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.103</v>
+        <v>16.521</v>
       </c>
       <c r="BW15" t="n">
-        <v>20.999</v>
+        <v>20.979</v>
       </c>
       <c r="BX15" t="n">
-        <v>62.898</v>
+        <v>62.5</v>
       </c>
       <c r="BY15" t="n">
-        <v>98.136</v>
+        <v>97.739</v>
       </c>
       <c r="BZ15" t="n">
-        <v>14.545</v>
+        <v>100</v>
       </c>
       <c r="CA15" t="n">
-        <v>39.394</v>
+        <v>16</v>
       </c>
       <c r="CB15" t="n">
-        <v>46.061</v>
+        <v>18</v>
       </c>
       <c r="CC15" t="n">
-        <v>330</v>
+        <v>66</v>
       </c>
       <c r="CD15" t="n">
-        <v>542</v>
+        <v>16.854</v>
       </c>
       <c r="CE15" t="n">
-        <v>1796</v>
+        <v>21.313</v>
       </c>
       <c r="CF15" t="n">
-        <v>3187</v>
+        <v>61.833</v>
       </c>
       <c r="CG15" t="n">
-        <v>5817</v>
+        <v>99.048</v>
       </c>
       <c r="CH15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="CI15" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="CJ15" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="CK15" t="n">
-        <v>411</v>
+        <v>100</v>
       </c>
       <c r="CL15" t="n">
-        <v>500</v>
+        <v>358</v>
       </c>
       <c r="CM15" t="n">
-        <v>16</v>
+        <v>1192</v>
       </c>
       <c r="CN15" t="n">
-        <v>20.4</v>
+        <v>2094</v>
       </c>
       <c r="CO15" t="n">
-        <v>63.6</v>
+        <v>3788</v>
       </c>
       <c r="CP15" t="n">
-        <v>16.366</v>
+        <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>21.134</v>
+        <v>13</v>
       </c>
       <c r="CR15" t="n">
-        <v>62.5</v>
+        <v>46</v>
       </c>
       <c r="CS15" t="n">
-        <v>98.372</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16">
@@ -5188,50 +5364,50 @@
         <v>37.126</v>
       </c>
       <c r="L16" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>35.4</v>
+        <v>27</v>
       </c>
       <c r="N16" t="n">
-        <v>25.8</v>
+        <v>29</v>
       </c>
       <c r="O16" t="n">
-        <v>38.8</v>
+        <v>44</v>
       </c>
       <c r="P16" t="n">
-        <v>35.029</v>
+        <v>31.734</v>
       </c>
       <c r="Q16" t="n">
-        <v>26.649</v>
+        <v>28.849</v>
       </c>
       <c r="R16" t="n">
-        <v>38.322</v>
+        <v>39.417</v>
       </c>
       <c r="S16" t="n">
-        <v>0.928</v>
+        <v>-2.367</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.123</v>
+        <v>0.076</v>
       </c>
       <c r="U16" t="n">
-        <v>1.196</v>
+        <v>2.291</v>
       </c>
       <c r="V16" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="W16" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="X16" t="n">
-        <v>52.8</v>
+        <v>54</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.578</v>
+        <v>2.65</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -5240,55 +5416,55 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>99.744</v>
+        <v>99.614</v>
       </c>
       <c r="AC16" t="n">
-        <v>99.729</v>
+        <v>99.628</v>
       </c>
       <c r="AD16" t="n">
-        <v>99.59699999999999</v>
+        <v>99.203</v>
       </c>
       <c r="AE16" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF16" t="n">
-        <v>31.334</v>
+        <v>19.269</v>
       </c>
       <c r="AG16" t="n">
-        <v>39.688</v>
+        <v>36.432</v>
       </c>
       <c r="AH16" t="n">
-        <v>22.16</v>
+        <v>21.015</v>
       </c>
       <c r="AI16" t="n">
-        <v>29.809</v>
+        <v>38.539</v>
       </c>
       <c r="AJ16" t="n">
-        <v>34.63</v>
+        <v>34.672</v>
       </c>
       <c r="AK16" t="n">
-        <v>43.141</v>
+        <v>53.772</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.855</v>
+        <v>3.151</v>
       </c>
       <c r="AM16" t="n">
-        <v>3.752</v>
+        <v>3.466</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.609</v>
+        <v>2.537</v>
       </c>
       <c r="AO16" t="n">
         <v>45.722</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>largest deviation DRAW -2.1 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME -2.4 pp; n_eff=100; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
@@ -5297,34 +5473,34 @@
         </is>
       </c>
       <c r="AS16" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.299</v>
+        <v>-7.101</v>
       </c>
       <c r="AU16" t="n">
-        <v>-2.973</v>
+        <v>0.227</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.674</v>
+        <v>6.874</v>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.328</v>
+        <v>1.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.613</v>
+        <v>-1.498</v>
       </c>
       <c r="BA16" t="n">
-        <v>-1.468</v>
+        <v>0.05</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.775</v>
+        <v>1.423</v>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
@@ -5333,131 +5509,131 @@
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF16" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="n">
         <v>200</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.142</v>
+        <v>0.134</v>
       </c>
       <c r="BJ16" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK16" t="n">
-        <v>35.4</v>
+        <v>27</v>
       </c>
       <c r="BL16" t="n">
-        <v>25.8</v>
+        <v>29</v>
       </c>
       <c r="BM16" t="n">
-        <v>38.8</v>
+        <v>44</v>
       </c>
       <c r="BN16" t="n">
-        <v>35.029</v>
+        <v>31.734</v>
       </c>
       <c r="BO16" t="n">
-        <v>26.649</v>
+        <v>28.849</v>
       </c>
       <c r="BP16" t="n">
-        <v>38.322</v>
+        <v>39.417</v>
       </c>
       <c r="BQ16" t="n">
-        <v>99.744</v>
+        <v>99.614</v>
       </c>
       <c r="BR16" t="n">
-        <v>351</v>
+        <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>30.769</v>
+        <v>33</v>
       </c>
       <c r="BT16" t="n">
-        <v>31.054</v>
+        <v>29</v>
       </c>
       <c r="BU16" t="n">
-        <v>38.177</v>
+        <v>38</v>
       </c>
       <c r="BV16" t="n">
-        <v>31.979</v>
+        <v>33.734</v>
       </c>
       <c r="BW16" t="n">
-        <v>30.226</v>
+        <v>28.849</v>
       </c>
       <c r="BX16" t="n">
-        <v>37.795</v>
+        <v>37.417</v>
       </c>
       <c r="BY16" t="n">
-        <v>98.06100000000001</v>
+        <v>98.43899999999999</v>
       </c>
       <c r="BZ16" t="n">
-        <v>24.501</v>
+        <v>100</v>
       </c>
       <c r="CA16" t="n">
-        <v>44.444</v>
+        <v>29</v>
       </c>
       <c r="CB16" t="n">
-        <v>31.054</v>
+        <v>33</v>
       </c>
       <c r="CC16" t="n">
-        <v>351</v>
+        <v>38</v>
       </c>
       <c r="CD16" t="n">
-        <v>2940</v>
+        <v>32.401</v>
       </c>
       <c r="CE16" t="n">
-        <v>9608</v>
+        <v>30.182</v>
       </c>
       <c r="CF16" t="n">
-        <v>17920</v>
+        <v>37.417</v>
       </c>
       <c r="CG16" t="n">
-        <v>35265</v>
+        <v>99.55200000000001</v>
       </c>
       <c r="CH16" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="CI16" t="n">
-        <v>380</v>
+        <v>41</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1349</v>
+        <v>36</v>
       </c>
       <c r="CK16" t="n">
-        <v>4783</v>
+        <v>100</v>
       </c>
       <c r="CL16" t="n">
-        <v>500</v>
+        <v>2106</v>
       </c>
       <c r="CM16" t="n">
-        <v>33.6</v>
+        <v>6629</v>
       </c>
       <c r="CN16" t="n">
-        <v>29.6</v>
+        <v>12205</v>
       </c>
       <c r="CO16" t="n">
-        <v>36.8</v>
+        <v>23666</v>
       </c>
       <c r="CP16" t="n">
-        <v>33.743</v>
+        <v>34</v>
       </c>
       <c r="CQ16" t="n">
-        <v>29.364</v>
+        <v>262</v>
       </c>
       <c r="CR16" t="n">
-        <v>36.893</v>
+        <v>936</v>
       </c>
       <c r="CS16" t="n">
-        <v>99.384</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="17">
@@ -5505,50 +5681,50 @@
         <v>15.011</v>
       </c>
       <c r="L17" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>61.6</v>
+        <v>68</v>
       </c>
       <c r="N17" t="n">
-        <v>25.2</v>
+        <v>22</v>
       </c>
       <c r="O17" t="n">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>62.115</v>
+        <v>64.935</v>
       </c>
       <c r="Q17" t="n">
-        <v>24.168</v>
+        <v>21.725</v>
       </c>
       <c r="R17" t="n">
-        <v>13.717</v>
+        <v>13.341</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.287</v>
+        <v>1.533</v>
       </c>
       <c r="T17" t="n">
-        <v>2.581</v>
+        <v>0.138</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.293</v>
+        <v>-1.67</v>
       </c>
       <c r="V17" t="n">
-        <v>57.4</v>
+        <v>54</v>
       </c>
       <c r="W17" t="n">
-        <v>42.6</v>
+        <v>46</v>
       </c>
       <c r="X17" t="n">
-        <v>56.4</v>
+        <v>49</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.004</v>
+        <v>3.02</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -5557,53 +5733,53 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>99.611</v>
+        <v>99.76600000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>99.595</v>
+        <v>99.777</v>
       </c>
       <c r="AD17" t="n">
-        <v>99.34</v>
+        <v>99.52</v>
       </c>
       <c r="AE17" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF17" t="n">
-        <v>57.264</v>
+        <v>58.337</v>
       </c>
       <c r="AG17" t="n">
-        <v>65.759</v>
+        <v>76.331</v>
       </c>
       <c r="AH17" t="n">
-        <v>21.593</v>
+        <v>15.001</v>
       </c>
       <c r="AI17" t="n">
-        <v>29.185</v>
+        <v>31.071</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10.512</v>
+        <v>5.523</v>
       </c>
       <c r="AK17" t="n">
-        <v>16.45</v>
+        <v>17.437</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AM17" t="n">
-        <v>4.138</v>
+        <v>4.603</v>
       </c>
       <c r="AN17" t="n">
-        <v>7.29</v>
+        <v>7.496</v>
       </c>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>draw</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>largest deviation DRAW +2.6 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY -1.7 pp; n_eff=100; market inside 95% CI; avg similarity 99.8%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
@@ -5615,31 +5791,31 @@
         <v>179331</v>
       </c>
       <c r="AT17" t="n">
-        <v>-1.802</v>
+        <v>4.598</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.613</v>
+        <v>0.413</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.811</v>
+        <v>-5.011</v>
       </c>
       <c r="AW17" t="n">
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.062</v>
+        <v>2.16</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.9419999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0.837</v>
+        <v>0.954</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.964</v>
+        <v>0.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>-1.134</v>
+        <v>-1.403</v>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
@@ -5653,111 +5829,127 @@
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF17" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="n">
         <v>200</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.05</v>
+        <v>0.161</v>
       </c>
       <c r="BJ17" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK17" t="n">
-        <v>61.6</v>
+        <v>68</v>
       </c>
       <c r="BL17" t="n">
-        <v>25.2</v>
+        <v>22</v>
       </c>
       <c r="BM17" t="n">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="BN17" t="n">
-        <v>62.115</v>
+        <v>64.935</v>
       </c>
       <c r="BO17" t="n">
-        <v>24.168</v>
+        <v>21.725</v>
       </c>
       <c r="BP17" t="n">
-        <v>13.717</v>
+        <v>13.341</v>
       </c>
       <c r="BQ17" t="n">
-        <v>99.611</v>
+        <v>99.76600000000001</v>
       </c>
       <c r="BR17" t="n">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>64.25700000000001</v>
+        <v>71</v>
       </c>
       <c r="BT17" t="n">
-        <v>22.49</v>
+        <v>18</v>
       </c>
       <c r="BU17" t="n">
-        <v>13.253</v>
+        <v>11</v>
       </c>
       <c r="BV17" t="n">
-        <v>63.876</v>
+        <v>65.935</v>
       </c>
       <c r="BW17" t="n">
-        <v>22.088</v>
+        <v>20.391</v>
       </c>
       <c r="BX17" t="n">
-        <v>14.036</v>
+        <v>13.674</v>
       </c>
       <c r="BY17" t="n">
-        <v>97.998</v>
+        <v>98.056</v>
       </c>
       <c r="BZ17" t="n">
-        <v>45.283</v>
+        <v>100</v>
       </c>
       <c r="CA17" t="n">
-        <v>35.535</v>
+        <v>59</v>
       </c>
       <c r="CB17" t="n">
-        <v>19.182</v>
+        <v>27</v>
       </c>
       <c r="CC17" t="n">
-        <v>318</v>
+        <v>14</v>
       </c>
       <c r="CD17" t="n">
+        <v>61.935</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>23.391</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>14.674</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>99.125</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>50</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>31.818</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>18.182</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>66</v>
+      </c>
+      <c r="CL17" t="n">
         <v>1428</v>
       </c>
-      <c r="CE17" t="n">
+      <c r="CM17" t="n">
         <v>4947</v>
       </c>
-      <c r="CF17" t="n">
+      <c r="CN17" t="n">
         <v>9022</v>
       </c>
-      <c r="CG17" t="n">
+      <c r="CO17" t="n">
         <v>16679</v>
       </c>
-      <c r="CH17" t="n">
+      <c r="CP17" t="n">
         <v>0</v>
       </c>
-      <c r="CI17" t="n">
+      <c r="CQ17" t="n">
         <v>14</v>
       </c>
-      <c r="CJ17" t="n">
+      <c r="CR17" t="n">
         <v>97</v>
       </c>
-      <c r="CK17" t="n">
+      <c r="CS17" t="n">
         <v>819</v>
       </c>
-      <c r="CL17" t="inlineStr"/>
-      <c r="CM17" t="inlineStr"/>
-      <c r="CN17" t="inlineStr"/>
-      <c r="CO17" t="inlineStr"/>
-      <c r="CP17" t="inlineStr"/>
-      <c r="CQ17" t="inlineStr"/>
-      <c r="CR17" t="inlineStr"/>
-      <c r="CS17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5804,50 +5996,50 @@
         <v>41.629</v>
       </c>
       <c r="L18" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M18" t="n">
-        <v>30.2</v>
+        <v>28</v>
       </c>
       <c r="N18" t="n">
-        <v>28.4</v>
+        <v>27</v>
       </c>
       <c r="O18" t="n">
-        <v>41.4</v>
+        <v>45</v>
       </c>
       <c r="P18" t="n">
-        <v>29.698</v>
+        <v>28.295</v>
       </c>
       <c r="Q18" t="n">
-        <v>28.837</v>
+        <v>28.953</v>
       </c>
       <c r="R18" t="n">
-        <v>41.465</v>
+        <v>42.753</v>
       </c>
       <c r="S18" t="n">
-        <v>1.256</v>
+        <v>-0.147</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.092</v>
+        <v>-0.976</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.163</v>
+        <v>1.124</v>
       </c>
       <c r="V18" t="n">
-        <v>41.2</v>
+        <v>42</v>
       </c>
       <c r="W18" t="n">
-        <v>58.8</v>
+        <v>58</v>
       </c>
       <c r="X18" t="n">
-        <v>49.4</v>
+        <v>47</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.412</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -5856,55 +6048,55 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>99.548</v>
+        <v>99.214</v>
       </c>
       <c r="AC18" t="n">
-        <v>99.53100000000001</v>
+        <v>99.20699999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>99.297</v>
+        <v>98.498</v>
       </c>
       <c r="AE18" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF18" t="n">
-        <v>26.339</v>
+        <v>20.14</v>
       </c>
       <c r="AG18" t="n">
-        <v>34.363</v>
+        <v>37.488</v>
       </c>
       <c r="AH18" t="n">
-        <v>24.624</v>
+        <v>19.269</v>
       </c>
       <c r="AI18" t="n">
-        <v>32.506</v>
+        <v>36.432</v>
       </c>
       <c r="AJ18" t="n">
-        <v>37.164</v>
+        <v>35.614</v>
       </c>
       <c r="AK18" t="n">
-        <v>45.767</v>
+        <v>54.756</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.367</v>
+        <v>3.534</v>
       </c>
       <c r="AM18" t="n">
-        <v>3.468</v>
+        <v>3.454</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.412</v>
+        <v>2.339</v>
       </c>
       <c r="AO18" t="n">
         <v>44.297</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>largest deviation HOME +1.3 pp; n_eff=500; market inside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY +1.1 pp; n_eff=100; market inside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
@@ -5913,34 +6105,34 @@
         </is>
       </c>
       <c r="AS18" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.758</v>
+        <v>-0.442</v>
       </c>
       <c r="AU18" t="n">
-        <v>-1.529</v>
+        <v>-2.929</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.229</v>
+        <v>3.371</v>
       </c>
       <c r="AW18" t="n">
         <v>2</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.084</v>
+        <v>0.99</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.328</v>
+        <v>1.41</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.871</v>
+        <v>-0.098</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0.747</v>
+        <v>-0.64</v>
       </c>
       <c r="BB18" t="n">
-        <v>-0.104</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
@@ -5949,131 +6141,131 @@
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF18" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="n">
         <v>200</v>
       </c>
       <c r="BI18" t="n">
-        <v>0.384</v>
+        <v>0.494</v>
       </c>
       <c r="BJ18" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK18" t="n">
-        <v>30.2</v>
+        <v>28</v>
       </c>
       <c r="BL18" t="n">
-        <v>28.4</v>
+        <v>27</v>
       </c>
       <c r="BM18" t="n">
-        <v>41.4</v>
+        <v>45</v>
       </c>
       <c r="BN18" t="n">
-        <v>29.698</v>
+        <v>28.295</v>
       </c>
       <c r="BO18" t="n">
-        <v>28.837</v>
+        <v>28.953</v>
       </c>
       <c r="BP18" t="n">
-        <v>41.465</v>
+        <v>42.753</v>
       </c>
       <c r="BQ18" t="n">
-        <v>99.548</v>
+        <v>99.214</v>
       </c>
       <c r="BR18" t="n">
-        <v>304</v>
+        <v>100</v>
       </c>
       <c r="BS18" t="n">
-        <v>27.303</v>
+        <v>28</v>
       </c>
       <c r="BT18" t="n">
-        <v>29.934</v>
+        <v>35</v>
       </c>
       <c r="BU18" t="n">
-        <v>42.763</v>
+        <v>37</v>
       </c>
       <c r="BV18" t="n">
-        <v>27.755</v>
+        <v>28.295</v>
       </c>
       <c r="BW18" t="n">
-        <v>29.932</v>
+        <v>31.619</v>
       </c>
       <c r="BX18" t="n">
-        <v>42.313</v>
+        <v>40.086</v>
       </c>
       <c r="BY18" t="n">
-        <v>98.18600000000001</v>
+        <v>98.373</v>
       </c>
       <c r="BZ18" t="n">
-        <v>26.263</v>
+        <v>100</v>
       </c>
       <c r="CA18" t="n">
-        <v>42.088</v>
+        <v>26</v>
       </c>
       <c r="CB18" t="n">
-        <v>31.65</v>
+        <v>31</v>
       </c>
       <c r="CC18" t="n">
-        <v>297</v>
+        <v>43</v>
       </c>
       <c r="CD18" t="n">
-        <v>1091</v>
+        <v>27.628</v>
       </c>
       <c r="CE18" t="n">
-        <v>4668</v>
+        <v>30.286</v>
       </c>
       <c r="CF18" t="n">
-        <v>10196</v>
+        <v>42.086</v>
       </c>
       <c r="CG18" t="n">
-        <v>22390</v>
+        <v>98.999</v>
       </c>
       <c r="CH18" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="CI18" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="CJ18" t="n">
-        <v>279</v>
+        <v>37</v>
       </c>
       <c r="CK18" t="n">
-        <v>1475</v>
+        <v>100</v>
       </c>
       <c r="CL18" t="n">
-        <v>500</v>
+        <v>628</v>
       </c>
       <c r="CM18" t="n">
-        <v>30</v>
+        <v>2826</v>
       </c>
       <c r="CN18" t="n">
-        <v>25.6</v>
+        <v>6376</v>
       </c>
       <c r="CO18" t="n">
-        <v>44.4</v>
+        <v>14365</v>
       </c>
       <c r="CP18" t="n">
-        <v>29.555</v>
+        <v>6</v>
       </c>
       <c r="CQ18" t="n">
-        <v>26.837</v>
+        <v>42</v>
       </c>
       <c r="CR18" t="n">
-        <v>43.608</v>
+        <v>147</v>
       </c>
       <c r="CS18" t="n">
-        <v>98.961</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19">
@@ -6121,50 +6313,50 @@
         <v>35.778</v>
       </c>
       <c r="L19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M19" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="N19" t="n">
-        <v>25.8</v>
+        <v>25</v>
       </c>
       <c r="O19" t="n">
-        <v>38.8</v>
+        <v>41</v>
       </c>
       <c r="P19" t="n">
-        <v>35.508</v>
+        <v>35.185</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.556</v>
+        <v>27.296</v>
       </c>
       <c r="R19" t="n">
-        <v>37.937</v>
+        <v>37.519</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.27</v>
+        <v>-0.593</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.889</v>
+        <v>-1.148</v>
       </c>
       <c r="U19" t="n">
-        <v>2.159</v>
+        <v>1.741</v>
       </c>
       <c r="V19" t="n">
-        <v>48.8</v>
+        <v>51</v>
       </c>
       <c r="W19" t="n">
-        <v>51.2</v>
+        <v>49</v>
       </c>
       <c r="X19" t="n">
-        <v>54.6</v>
+        <v>52</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.604</v>
+        <v>2.62</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -6173,43 +6365,43 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>99.75</v>
+        <v>99.54300000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>99.736</v>
+        <v>99.541</v>
       </c>
       <c r="AD19" t="n">
-        <v>99.605</v>
+        <v>99.188</v>
       </c>
       <c r="AE19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF19" t="n">
-        <v>31.334</v>
+        <v>25.461</v>
       </c>
       <c r="AG19" t="n">
-        <v>39.688</v>
+        <v>43.722</v>
       </c>
       <c r="AH19" t="n">
-        <v>22.16</v>
+        <v>17.545</v>
       </c>
       <c r="AI19" t="n">
-        <v>29.809</v>
+        <v>34.305</v>
       </c>
       <c r="AJ19" t="n">
-        <v>34.63</v>
+        <v>31.867</v>
       </c>
       <c r="AK19" t="n">
-        <v>43.141</v>
+        <v>50.799</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.816</v>
+        <v>2.842</v>
       </c>
       <c r="AM19" t="n">
-        <v>3.766</v>
+        <v>3.664</v>
       </c>
       <c r="AN19" t="n">
-        <v>2.636</v>
+        <v>2.665</v>
       </c>
       <c r="AO19" t="n">
         <v>48.925</v>
@@ -6221,7 +6413,7 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +2.2 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+          <t>largest deviation AWAY +1.7 pp; n_eff=100; market inside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
@@ -6230,34 +6422,34 @@
         </is>
       </c>
       <c r="AS19" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0.378</v>
+        <v>-1.778</v>
       </c>
       <c r="AU19" t="n">
-        <v>-2.644</v>
+        <v>-3.444</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.022</v>
+        <v>5.222</v>
       </c>
       <c r="AW19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.324</v>
+        <v>1.37</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0.176</v>
+        <v>-0.371</v>
       </c>
       <c r="BA19" t="n">
-        <v>-1.311</v>
+        <v>-0.763</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.41</v>
+        <v>1.089</v>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
@@ -6266,131 +6458,131 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="n">
         <v>200</v>
       </c>
       <c r="BI19" t="n">
-        <v>0.159</v>
+        <v>0.276</v>
       </c>
       <c r="BJ19" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK19" t="n">
-        <v>35.4</v>
+        <v>34</v>
       </c>
       <c r="BL19" t="n">
-        <v>25.8</v>
+        <v>25</v>
       </c>
       <c r="BM19" t="n">
-        <v>38.8</v>
+        <v>41</v>
       </c>
       <c r="BN19" t="n">
-        <v>35.508</v>
+        <v>35.185</v>
       </c>
       <c r="BO19" t="n">
-        <v>26.556</v>
+        <v>27.296</v>
       </c>
       <c r="BP19" t="n">
-        <v>37.937</v>
+        <v>37.519</v>
       </c>
       <c r="BQ19" t="n">
-        <v>99.75</v>
+        <v>99.54300000000001</v>
       </c>
       <c r="BR19" t="n">
-        <v>403</v>
+        <v>100</v>
       </c>
       <c r="BS19" t="n">
-        <v>32.754</v>
+        <v>35</v>
       </c>
       <c r="BT19" t="n">
-        <v>32.754</v>
+        <v>37</v>
       </c>
       <c r="BU19" t="n">
-        <v>34.491</v>
+        <v>28</v>
       </c>
       <c r="BV19" t="n">
-        <v>33.757</v>
+        <v>35.519</v>
       </c>
       <c r="BW19" t="n">
-        <v>31.325</v>
+        <v>31.296</v>
       </c>
       <c r="BX19" t="n">
-        <v>34.918</v>
+        <v>33.185</v>
       </c>
       <c r="BY19" t="n">
-        <v>97.81699999999999</v>
+        <v>98.11499999999999</v>
       </c>
       <c r="BZ19" t="n">
-        <v>25.137</v>
+        <v>100</v>
       </c>
       <c r="CA19" t="n">
-        <v>43.443</v>
+        <v>33</v>
       </c>
       <c r="CB19" t="n">
-        <v>31.421</v>
+        <v>27</v>
       </c>
       <c r="CC19" t="n">
-        <v>366</v>
+        <v>40</v>
       </c>
       <c r="CD19" t="n">
-        <v>3008</v>
+        <v>34.852</v>
       </c>
       <c r="CE19" t="n">
-        <v>10049</v>
+        <v>27.963</v>
       </c>
       <c r="CF19" t="n">
-        <v>19196</v>
+        <v>37.185</v>
       </c>
       <c r="CG19" t="n">
-        <v>38782</v>
+        <v>98.941</v>
       </c>
       <c r="CH19" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="CI19" t="n">
-        <v>318</v>
+        <v>44</v>
       </c>
       <c r="CJ19" t="n">
-        <v>881</v>
+        <v>35</v>
       </c>
       <c r="CK19" t="n">
-        <v>3889</v>
+        <v>100</v>
       </c>
       <c r="CL19" t="n">
-        <v>500</v>
+        <v>2181</v>
       </c>
       <c r="CM19" t="n">
-        <v>36.2</v>
+        <v>7029</v>
       </c>
       <c r="CN19" t="n">
-        <v>29.6</v>
+        <v>13277</v>
       </c>
       <c r="CO19" t="n">
-        <v>34.2</v>
+        <v>26444</v>
       </c>
       <c r="CP19" t="n">
-        <v>36.079</v>
+        <v>23</v>
       </c>
       <c r="CQ19" t="n">
-        <v>29.27</v>
+        <v>251</v>
       </c>
       <c r="CR19" t="n">
-        <v>34.651</v>
+        <v>638</v>
       </c>
       <c r="CS19" t="n">
-        <v>98.82899999999999</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="20">
@@ -6438,107 +6630,107 @@
         <v>8.456</v>
       </c>
       <c r="L20" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>82.8</v>
+        <v>73</v>
       </c>
       <c r="N20" t="n">
-        <v>12.6</v>
+        <v>23</v>
       </c>
       <c r="O20" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>80.693</v>
+        <v>74.61799999999999</v>
       </c>
       <c r="Q20" t="n">
-        <v>13.605</v>
+        <v>18.411</v>
       </c>
       <c r="R20" t="n">
-        <v>5.702</v>
+        <v>6.971</v>
       </c>
       <c r="S20" t="n">
-        <v>5.266</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-2.512</v>
+        <v>2.294</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.754</v>
+        <v>-1.485</v>
       </c>
       <c r="V20" t="n">
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="W20" t="n">
-        <v>36.8</v>
+        <v>38</v>
       </c>
       <c r="X20" t="n">
-        <v>46.8</v>
+        <v>52</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.228</v>
+        <v>3.08</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>MODERATE HISTORICAL DEVIATION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>99.508</v>
+        <v>99.337</v>
       </c>
       <c r="AC20" t="n">
-        <v>99.497</v>
+        <v>99.40900000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>99.122</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="AE20" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF20" t="n">
-        <v>79.245</v>
+        <v>63.568</v>
       </c>
       <c r="AG20" t="n">
-        <v>85.855</v>
+        <v>80.73099999999999</v>
       </c>
       <c r="AH20" t="n">
-        <v>9.973000000000001</v>
+        <v>15.843</v>
       </c>
       <c r="AI20" t="n">
-        <v>15.797</v>
+        <v>32.155</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.084</v>
+        <v>1.566</v>
       </c>
       <c r="AK20" t="n">
-        <v>6.808</v>
+        <v>9.837</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.239</v>
+        <v>1.34</v>
       </c>
       <c r="AM20" t="n">
-        <v>7.35</v>
+        <v>5.431</v>
       </c>
       <c r="AN20" t="n">
-        <v>17.539</v>
+        <v>14.346</v>
       </c>
       <c r="AO20" t="n">
         <v>61.266</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>draw</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>largest deviation HOME +5.3 pp; n_eff=500; market outside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market; downgraded to MODERATE (backtest or similarity gate)</t>
+          <t>largest deviation DRAW +2.3 pp; n_eff=100; market inside 95% CI; avg similarity 99.3%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
@@ -6547,34 +6739,34 @@
         </is>
       </c>
       <c r="AS20" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.373</v>
+        <v>-2.427</v>
       </c>
       <c r="AU20" t="n">
-        <v>-3.517</v>
+        <v>6.883</v>
       </c>
       <c r="AV20" t="n">
-        <v>-3.856</v>
+        <v>-4.456</v>
       </c>
       <c r="AW20" t="n">
         <v>3</v>
       </c>
       <c r="AX20" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.648</v>
+        <v>0.67</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.829</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="BA20" t="n">
-        <v>-2.139</v>
+        <v>1.872</v>
       </c>
       <c r="BB20" t="n">
-        <v>-3.099</v>
+        <v>-1.602</v>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
@@ -6583,131 +6775,131 @@
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF20" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="n">
         <v>200</v>
       </c>
       <c r="BI20" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="BJ20" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK20" t="n">
-        <v>82.8</v>
+        <v>73</v>
       </c>
       <c r="BL20" t="n">
-        <v>12.6</v>
+        <v>23</v>
       </c>
       <c r="BM20" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BN20" t="n">
-        <v>80.693</v>
+        <v>74.61799999999999</v>
       </c>
       <c r="BO20" t="n">
-        <v>13.605</v>
+        <v>18.411</v>
       </c>
       <c r="BP20" t="n">
-        <v>5.702</v>
+        <v>6.971</v>
       </c>
       <c r="BQ20" t="n">
-        <v>99.508</v>
+        <v>99.337</v>
       </c>
       <c r="BR20" t="n">
-        <v>262</v>
+        <v>100</v>
       </c>
       <c r="BS20" t="n">
-        <v>78.626</v>
+        <v>84</v>
       </c>
       <c r="BT20" t="n">
-        <v>13.74</v>
+        <v>8</v>
       </c>
       <c r="BU20" t="n">
-        <v>7.634</v>
+        <v>8</v>
       </c>
       <c r="BV20" t="n">
-        <v>77.241</v>
+        <v>78.285</v>
       </c>
       <c r="BW20" t="n">
-        <v>14.769</v>
+        <v>13.411</v>
       </c>
       <c r="BX20" t="n">
-        <v>7.99</v>
+        <v>8.304</v>
       </c>
       <c r="BY20" t="n">
-        <v>98.422</v>
+        <v>98.447</v>
       </c>
       <c r="BZ20" t="n">
-        <v>56.125</v>
+        <v>100</v>
       </c>
       <c r="CA20" t="n">
-        <v>34.188</v>
+        <v>78</v>
       </c>
       <c r="CB20" t="n">
-        <v>9.686999999999999</v>
+        <v>18</v>
       </c>
       <c r="CC20" t="n">
-        <v>351</v>
+        <v>4</v>
       </c>
       <c r="CD20" t="n">
-        <v>864</v>
+        <v>76.285</v>
       </c>
       <c r="CE20" t="n">
-        <v>2281</v>
+        <v>16.745</v>
       </c>
       <c r="CF20" t="n">
-        <v>3600</v>
+        <v>6.971</v>
       </c>
       <c r="CG20" t="n">
-        <v>6311</v>
+        <v>99.244</v>
       </c>
       <c r="CH20" t="n">
+        <v>56.566</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>30.303</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>13.131</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>99</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>600</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>1546</v>
+      </c>
+      <c r="CN20" t="n">
+        <v>2390</v>
+      </c>
+      <c r="CO20" t="n">
+        <v>4180</v>
+      </c>
+      <c r="CP20" t="n">
         <v>5</v>
       </c>
-      <c r="CI20" t="n">
-        <v>42</v>
-      </c>
-      <c r="CJ20" t="n">
-        <v>137</v>
-      </c>
-      <c r="CK20" t="n">
-        <v>434</v>
-      </c>
-      <c r="CL20" t="n">
-        <v>500</v>
-      </c>
-      <c r="CM20" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="CN20" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="CO20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="CP20" t="n">
-        <v>78.265</v>
-      </c>
       <c r="CQ20" t="n">
-        <v>14.176</v>
+        <v>29</v>
       </c>
       <c r="CR20" t="n">
-        <v>7.559</v>
+        <v>100</v>
       </c>
       <c r="CS20" t="n">
-        <v>99.148</v>
+        <v>302</v>
       </c>
     </row>
     <row r="21">
@@ -6755,50 +6947,50 @@
         <v>33.387</v>
       </c>
       <c r="L21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M21" t="n">
-        <v>37.8</v>
+        <v>31</v>
       </c>
       <c r="N21" t="n">
-        <v>26.4</v>
+        <v>29</v>
       </c>
       <c r="O21" t="n">
-        <v>35.8</v>
+        <v>40</v>
       </c>
       <c r="P21" t="n">
-        <v>38.263</v>
+        <v>36.613</v>
       </c>
       <c r="Q21" t="n">
-        <v>26.627</v>
+        <v>27.796</v>
       </c>
       <c r="R21" t="n">
-        <v>35.111</v>
+        <v>35.591</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.157</v>
+        <v>-2.806</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5669999999999999</v>
+        <v>0.602</v>
       </c>
       <c r="U21" t="n">
-        <v>1.723</v>
+        <v>2.204</v>
       </c>
       <c r="V21" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="W21" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="X21" t="n">
-        <v>58.4</v>
+        <v>66</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.862</v>
+        <v>2.9</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -6807,55 +6999,55 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>99.658</v>
+        <v>99.473</v>
       </c>
       <c r="AC21" t="n">
-        <v>99.637</v>
+        <v>99.476</v>
       </c>
       <c r="AD21" t="n">
-        <v>99.471</v>
+        <v>99.02800000000001</v>
       </c>
       <c r="AE21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF21" t="n">
-        <v>33.658</v>
+        <v>22.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>42.128</v>
+        <v>40.626</v>
       </c>
       <c r="AH21" t="n">
-        <v>22.727</v>
+        <v>21.015</v>
       </c>
       <c r="AI21" t="n">
-        <v>30.433</v>
+        <v>38.539</v>
       </c>
       <c r="AJ21" t="n">
-        <v>31.721</v>
+        <v>30.94</v>
       </c>
       <c r="AK21" t="n">
-        <v>40.096</v>
+        <v>49.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.614</v>
+        <v>2.731</v>
       </c>
       <c r="AM21" t="n">
-        <v>3.756</v>
+        <v>3.598</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.848</v>
+        <v>2.81</v>
       </c>
       <c r="AO21" t="n">
         <v>53.333</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>largest deviation AWAY +1.7 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME -2.8 pp; n_eff=100; market inside 95% CI; avg similarity 99.5%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
@@ -6864,34 +7056,34 @@
         </is>
       </c>
       <c r="AS21" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT21" t="n">
-        <v>-1.619</v>
+        <v>-8.419</v>
       </c>
       <c r="AU21" t="n">
-        <v>-0.794</v>
+        <v>1.806</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.413</v>
+        <v>6.613</v>
       </c>
       <c r="AW21" t="n">
         <v>3</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.516</v>
+        <v>1.42</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.346</v>
+        <v>1.48</v>
       </c>
       <c r="AZ21" t="n">
-        <v>-0.741</v>
+        <v>-1.723</v>
       </c>
       <c r="BA21" t="n">
-        <v>-0.399</v>
+        <v>0.406</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.144</v>
+        <v>1.402</v>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
@@ -6900,131 +7092,131 @@
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="n">
         <v>200</v>
       </c>
       <c r="BI21" t="n">
-        <v>0.253</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="BJ21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK21" t="n">
-        <v>37.8</v>
+        <v>31</v>
       </c>
       <c r="BL21" t="n">
-        <v>26.4</v>
+        <v>29</v>
       </c>
       <c r="BM21" t="n">
-        <v>35.8</v>
+        <v>40</v>
       </c>
       <c r="BN21" t="n">
-        <v>38.263</v>
+        <v>36.613</v>
       </c>
       <c r="BO21" t="n">
-        <v>26.627</v>
+        <v>27.796</v>
       </c>
       <c r="BP21" t="n">
-        <v>35.111</v>
+        <v>35.591</v>
       </c>
       <c r="BQ21" t="n">
-        <v>99.658</v>
+        <v>99.473</v>
       </c>
       <c r="BR21" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BS21" t="n">
-        <v>37.8</v>
+        <v>41</v>
       </c>
       <c r="BT21" t="n">
-        <v>32.6</v>
+        <v>28</v>
       </c>
       <c r="BU21" t="n">
-        <v>29.6</v>
+        <v>31</v>
       </c>
       <c r="BV21" t="n">
-        <v>38.263</v>
+        <v>39.946</v>
       </c>
       <c r="BW21" t="n">
-        <v>31.055</v>
+        <v>27.462</v>
       </c>
       <c r="BX21" t="n">
-        <v>30.682</v>
+        <v>32.591</v>
       </c>
       <c r="BY21" t="n">
-        <v>98.08499999999999</v>
+        <v>98.431</v>
       </c>
       <c r="BZ21" t="n">
-        <v>31.624</v>
+        <v>100</v>
       </c>
       <c r="CA21" t="n">
-        <v>41.311</v>
+        <v>33</v>
       </c>
       <c r="CB21" t="n">
-        <v>27.066</v>
+        <v>25</v>
       </c>
       <c r="CC21" t="n">
-        <v>351</v>
+        <v>42</v>
       </c>
       <c r="CD21" t="n">
-        <v>2005</v>
+        <v>37.28</v>
       </c>
       <c r="CE21" t="n">
-        <v>8952</v>
+        <v>26.462</v>
       </c>
       <c r="CF21" t="n">
-        <v>18575</v>
+        <v>36.258</v>
       </c>
       <c r="CG21" t="n">
-        <v>41421</v>
+        <v>99.306</v>
       </c>
       <c r="CH21" t="n">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="CI21" t="n">
-        <v>349</v>
+        <v>53</v>
       </c>
       <c r="CJ21" t="n">
-        <v>1213</v>
+        <v>23</v>
       </c>
       <c r="CK21" t="n">
-        <v>4652</v>
+        <v>100</v>
       </c>
       <c r="CL21" t="n">
-        <v>500</v>
+        <v>1409</v>
       </c>
       <c r="CM21" t="n">
-        <v>36.6</v>
+        <v>6377</v>
       </c>
       <c r="CN21" t="n">
-        <v>28.6</v>
+        <v>12984</v>
       </c>
       <c r="CO21" t="n">
-        <v>34.8</v>
+        <v>28329</v>
       </c>
       <c r="CP21" t="n">
-        <v>37.406</v>
+        <v>33</v>
       </c>
       <c r="CQ21" t="n">
-        <v>28.198</v>
+        <v>200</v>
       </c>
       <c r="CR21" t="n">
-        <v>34.396</v>
+        <v>729</v>
       </c>
       <c r="CS21" t="n">
-        <v>99.199</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="22">
@@ -7072,107 +7264,107 @@
         <v>25.769</v>
       </c>
       <c r="L22" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M22" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="N22" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P22" t="n">
-        <v>53.462</v>
+        <v>52.746</v>
       </c>
       <c r="Q22" t="n">
-        <v>25.604</v>
+        <v>21.742</v>
       </c>
       <c r="R22" t="n">
-        <v>20.934</v>
+        <v>25.512</v>
       </c>
       <c r="S22" t="n">
-        <v>3.844</v>
+        <v>3.127</v>
       </c>
       <c r="T22" t="n">
-        <v>0.991</v>
+        <v>-2.871</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.835</v>
+        <v>-0.256</v>
       </c>
       <c r="V22" t="n">
-        <v>61.2</v>
+        <v>65</v>
       </c>
       <c r="W22" t="n">
-        <v>38.8</v>
+        <v>35</v>
       </c>
       <c r="X22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.092</v>
+        <v>3.19</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>MODERATE HISTORICAL DEVIATION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>99.413</v>
+        <v>99.161</v>
       </c>
       <c r="AC22" t="n">
-        <v>99.369</v>
+        <v>99.148</v>
       </c>
       <c r="AD22" t="n">
-        <v>99.089</v>
+        <v>98.488</v>
       </c>
       <c r="AE22" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF22" t="n">
-        <v>50.618</v>
+        <v>49.201</v>
       </c>
       <c r="AG22" t="n">
-        <v>59.306</v>
+        <v>68.133</v>
       </c>
       <c r="AH22" t="n">
-        <v>22.349</v>
+        <v>10.095</v>
       </c>
       <c r="AI22" t="n">
-        <v>30.017</v>
+        <v>24.42</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15.803</v>
+        <v>17.545</v>
       </c>
       <c r="AK22" t="n">
-        <v>22.67</v>
+        <v>34.305</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.87</v>
+        <v>1.896</v>
       </c>
       <c r="AM22" t="n">
-        <v>3.906</v>
+        <v>4.599</v>
       </c>
       <c r="AN22" t="n">
-        <v>4.777</v>
+        <v>3.92</v>
       </c>
       <c r="AO22" t="n">
         <v>60.513</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>largest deviation AWAY -4.8 pp; n_eff=500; market outside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +3.1 pp; n_eff=100; market inside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
@@ -7181,34 +7373,34 @@
         </is>
       </c>
       <c r="AS22" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT22" t="n">
-        <v>5.382</v>
+        <v>9.382</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.387</v>
+        <v>-8.613</v>
       </c>
       <c r="AV22" t="n">
-        <v>-6.769</v>
+        <v>-0.769</v>
       </c>
       <c r="AW22" t="n">
         <v>3</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.934</v>
+        <v>2.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.158</v>
+        <v>1.16</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.407</v>
+        <v>1.876</v>
       </c>
       <c r="BA22" t="n">
-        <v>0.72</v>
+        <v>-1.999</v>
       </c>
       <c r="BB22" t="n">
-        <v>-3.461</v>
+        <v>-0.176</v>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
@@ -7217,131 +7409,131 @@
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF22" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG22" t="inlineStr"/>
       <c r="BH22" t="n">
         <v>200</v>
       </c>
       <c r="BI22" t="n">
-        <v>0.001</v>
+        <v>0.046</v>
       </c>
       <c r="BJ22" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK22" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="BL22" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="BM22" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="BN22" t="n">
-        <v>53.462</v>
+        <v>52.746</v>
       </c>
       <c r="BO22" t="n">
-        <v>25.604</v>
+        <v>21.742</v>
       </c>
       <c r="BP22" t="n">
-        <v>20.934</v>
+        <v>25.512</v>
       </c>
       <c r="BQ22" t="n">
-        <v>99.413</v>
+        <v>99.161</v>
       </c>
       <c r="BR22" t="n">
-        <v>187</v>
+        <v>100</v>
       </c>
       <c r="BS22" t="n">
-        <v>52.941</v>
+        <v>48</v>
       </c>
       <c r="BT22" t="n">
-        <v>24.064</v>
+        <v>25</v>
       </c>
       <c r="BU22" t="n">
-        <v>22.995</v>
+        <v>27</v>
       </c>
       <c r="BV22" t="n">
-        <v>51.224</v>
+        <v>49.079</v>
       </c>
       <c r="BW22" t="n">
-        <v>24.348</v>
+        <v>24.742</v>
       </c>
       <c r="BX22" t="n">
-        <v>24.428</v>
+        <v>26.179</v>
       </c>
       <c r="BY22" t="n">
-        <v>97.721</v>
+        <v>96.61</v>
       </c>
       <c r="BZ22" t="n">
-        <v>47.222</v>
+        <v>100</v>
       </c>
       <c r="CA22" t="n">
-        <v>32.54</v>
+        <v>57</v>
       </c>
       <c r="CB22" t="n">
-        <v>20.238</v>
+        <v>20</v>
       </c>
       <c r="CC22" t="n">
-        <v>252</v>
+        <v>23</v>
       </c>
       <c r="CD22" t="n">
-        <v>750</v>
+        <v>52.079</v>
       </c>
       <c r="CE22" t="n">
-        <v>3641</v>
+        <v>23.075</v>
       </c>
       <c r="CF22" t="n">
-        <v>10591</v>
+        <v>24.846</v>
       </c>
       <c r="CG22" t="n">
-        <v>32590</v>
+        <v>99.05500000000001</v>
       </c>
       <c r="CH22" t="n">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="CI22" t="n">
-        <v>87</v>
+        <v>28</v>
       </c>
       <c r="CJ22" t="n">
-        <v>321</v>
+        <v>25</v>
       </c>
       <c r="CK22" t="n">
-        <v>1415</v>
+        <v>100</v>
       </c>
       <c r="CL22" t="n">
-        <v>500</v>
+        <v>382</v>
       </c>
       <c r="CM22" t="n">
-        <v>50.2</v>
+        <v>2166</v>
       </c>
       <c r="CN22" t="n">
-        <v>25.8</v>
+        <v>6730</v>
       </c>
       <c r="CO22" t="n">
-        <v>24</v>
+        <v>21344</v>
       </c>
       <c r="CP22" t="n">
-        <v>50.034</v>
+        <v>0</v>
       </c>
       <c r="CQ22" t="n">
-        <v>25.461</v>
+        <v>28</v>
       </c>
       <c r="CR22" t="n">
-        <v>24.505</v>
+        <v>135</v>
       </c>
       <c r="CS22" t="n">
-        <v>98.66500000000001</v>
+        <v>722</v>
       </c>
     </row>
     <row r="23">
@@ -7389,50 +7581,50 @@
         <v>32.02</v>
       </c>
       <c r="L23" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M23" t="n">
-        <v>39.8</v>
+        <v>46</v>
       </c>
       <c r="N23" t="n">
-        <v>28.8</v>
+        <v>26</v>
       </c>
       <c r="O23" t="n">
-        <v>31.4</v>
+        <v>28</v>
       </c>
       <c r="P23" t="n">
-        <v>39.407</v>
+        <v>40.949</v>
       </c>
       <c r="Q23" t="n">
-        <v>29.016</v>
+        <v>28.371</v>
       </c>
       <c r="R23" t="n">
-        <v>31.577</v>
+        <v>30.68</v>
       </c>
       <c r="S23" t="n">
-        <v>0.983</v>
+        <v>2.525</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.54</v>
+        <v>-1.186</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.443</v>
+        <v>-1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>44.2</v>
+        <v>34</v>
       </c>
       <c r="W23" t="n">
-        <v>55.8</v>
+        <v>66</v>
       </c>
       <c r="X23" t="n">
-        <v>48.4</v>
+        <v>39</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.38</v>
+        <v>2.06</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -7441,43 +7633,43 @@
         </is>
       </c>
       <c r="AB23" t="n">
-        <v>99.742</v>
+        <v>99.596</v>
       </c>
       <c r="AC23" t="n">
-        <v>99.736</v>
+        <v>99.593</v>
       </c>
       <c r="AD23" t="n">
-        <v>99.586</v>
+        <v>99.249</v>
       </c>
       <c r="AE23" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF23" t="n">
-        <v>35.603</v>
+        <v>36.561</v>
       </c>
       <c r="AG23" t="n">
-        <v>44.153</v>
+        <v>55.735</v>
       </c>
       <c r="AH23" t="n">
-        <v>25.004</v>
+        <v>18.405</v>
       </c>
       <c r="AI23" t="n">
-        <v>32.919</v>
+        <v>35.371</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27.487</v>
+        <v>20.14</v>
       </c>
       <c r="AK23" t="n">
-        <v>35.597</v>
+        <v>37.488</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.538</v>
+        <v>2.442</v>
       </c>
       <c r="AM23" t="n">
-        <v>3.446</v>
+        <v>3.525</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.167</v>
+        <v>3.259</v>
       </c>
       <c r="AO23" t="n">
         <v>41.995</v>
@@ -7489,7 +7681,7 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>largest deviation HOME +1.0 pp; n_eff=500; market inside 95% CI; avg similarity 99.7%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +2.5 pp; n_eff=100; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
@@ -7498,34 +7690,34 @@
         </is>
       </c>
       <c r="AS23" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.376</v>
+        <v>7.576</v>
       </c>
       <c r="AU23" t="n">
-        <v>-0.757</v>
+        <v>-3.557</v>
       </c>
       <c r="AV23" t="n">
-        <v>-0.62</v>
+        <v>-4.02</v>
       </c>
       <c r="AW23" t="n">
         <v>2</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.294</v>
+        <v>1.22</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.086</v>
+        <v>0.84</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.633</v>
+        <v>1.558</v>
       </c>
       <c r="BA23" t="n">
-        <v>-0.371</v>
+        <v>-0.779</v>
       </c>
       <c r="BB23" t="n">
-        <v>-0.297</v>
+        <v>-0.862</v>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
@@ -7534,131 +7726,131 @@
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF23" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="n">
         <v>200</v>
       </c>
       <c r="BI23" t="n">
-        <v>0.527</v>
+        <v>0.119</v>
       </c>
       <c r="BJ23" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK23" t="n">
-        <v>39.8</v>
+        <v>46</v>
       </c>
       <c r="BL23" t="n">
-        <v>28.8</v>
+        <v>26</v>
       </c>
       <c r="BM23" t="n">
-        <v>31.4</v>
+        <v>28</v>
       </c>
       <c r="BN23" t="n">
-        <v>39.407</v>
+        <v>40.949</v>
       </c>
       <c r="BO23" t="n">
-        <v>29.016</v>
+        <v>28.371</v>
       </c>
       <c r="BP23" t="n">
-        <v>31.577</v>
+        <v>30.68</v>
       </c>
       <c r="BQ23" t="n">
-        <v>99.742</v>
+        <v>99.596</v>
       </c>
       <c r="BR23" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BS23" t="n">
-        <v>38.4</v>
+        <v>46</v>
       </c>
       <c r="BT23" t="n">
-        <v>29.4</v>
+        <v>26</v>
       </c>
       <c r="BU23" t="n">
-        <v>32.2</v>
+        <v>28</v>
       </c>
       <c r="BV23" t="n">
-        <v>38.407</v>
+        <v>40.949</v>
       </c>
       <c r="BW23" t="n">
-        <v>29.445</v>
+        <v>28.371</v>
       </c>
       <c r="BX23" t="n">
-        <v>32.148</v>
+        <v>30.68</v>
       </c>
       <c r="BY23" t="n">
-        <v>98.669</v>
+        <v>98.988</v>
       </c>
       <c r="BZ23" t="n">
-        <v>30.211</v>
+        <v>100</v>
       </c>
       <c r="CA23" t="n">
-        <v>46.828</v>
+        <v>41</v>
       </c>
       <c r="CB23" t="n">
-        <v>22.961</v>
+        <v>33</v>
       </c>
       <c r="CC23" t="n">
-        <v>331</v>
+        <v>26</v>
       </c>
       <c r="CD23" t="n">
-        <v>3572</v>
+        <v>39.282</v>
       </c>
       <c r="CE23" t="n">
-        <v>12739</v>
+        <v>30.704</v>
       </c>
       <c r="CF23" t="n">
-        <v>23767</v>
+        <v>30.013</v>
       </c>
       <c r="CG23" t="n">
-        <v>45114</v>
+        <v>99.453</v>
       </c>
       <c r="CH23" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="CI23" t="n">
-        <v>404</v>
+        <v>40</v>
       </c>
       <c r="CJ23" t="n">
-        <v>1604</v>
+        <v>23</v>
       </c>
       <c r="CK23" t="n">
-        <v>6291</v>
+        <v>100</v>
       </c>
       <c r="CL23" t="n">
-        <v>500</v>
+        <v>2522</v>
       </c>
       <c r="CM23" t="n">
-        <v>40.4</v>
+        <v>9057</v>
       </c>
       <c r="CN23" t="n">
-        <v>30</v>
+        <v>16579</v>
       </c>
       <c r="CO23" t="n">
-        <v>29.6</v>
+        <v>30661</v>
       </c>
       <c r="CP23" t="n">
-        <v>39.835</v>
+        <v>25</v>
       </c>
       <c r="CQ23" t="n">
-        <v>29.873</v>
+        <v>229</v>
       </c>
       <c r="CR23" t="n">
-        <v>30.291</v>
+        <v>974</v>
       </c>
       <c r="CS23" t="n">
-        <v>99.518</v>
+        <v>4324</v>
       </c>
     </row>
     <row r="24">
@@ -7706,50 +7898,50 @@
         <v>14.405</v>
       </c>
       <c r="L24" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M24" t="n">
-        <v>64.8</v>
+        <v>60</v>
       </c>
       <c r="N24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O24" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="P24" t="n">
-        <v>64.60599999999999</v>
+        <v>62.748</v>
       </c>
       <c r="Q24" t="n">
-        <v>21.85</v>
+        <v>22.316</v>
       </c>
       <c r="R24" t="n">
-        <v>13.544</v>
+        <v>14.937</v>
       </c>
       <c r="S24" t="n">
-        <v>0.484</v>
+        <v>-1.374</v>
       </c>
       <c r="T24" t="n">
-        <v>0.376</v>
+        <v>0.842</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.861</v>
+        <v>0.532</v>
       </c>
       <c r="V24" t="n">
-        <v>54.4</v>
+        <v>50</v>
       </c>
       <c r="W24" t="n">
-        <v>45.6</v>
+        <v>50</v>
       </c>
       <c r="X24" t="n">
-        <v>53.8</v>
+        <v>52</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.982</v>
+        <v>2.9</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -7758,55 +7950,55 @@
         </is>
       </c>
       <c r="AB24" t="n">
-        <v>99.617</v>
+        <v>99.372</v>
       </c>
       <c r="AC24" t="n">
-        <v>99.602</v>
+        <v>99.34699999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>99.36799999999999</v>
+        <v>98.90300000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF24" t="n">
-        <v>60.515</v>
+        <v>50.2</v>
       </c>
       <c r="AG24" t="n">
-        <v>68.85899999999999</v>
+        <v>69.06</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.59</v>
+        <v>16.691</v>
       </c>
       <c r="AI24" t="n">
-        <v>25.837</v>
+        <v>33.233</v>
       </c>
       <c r="AJ24" t="n">
-        <v>10.512</v>
+        <v>10.095</v>
       </c>
       <c r="AK24" t="n">
-        <v>16.45</v>
+        <v>24.42</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.548</v>
+        <v>1.594</v>
       </c>
       <c r="AM24" t="n">
-        <v>4.577</v>
+        <v>4.481</v>
       </c>
       <c r="AN24" t="n">
-        <v>7.383</v>
+        <v>6.695</v>
       </c>
       <c r="AO24" t="n">
         <v>55.585</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>largest deviation AWAY -0.9 pp; n_eff=500; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME -1.4 pp; n_eff=100; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
@@ -7815,34 +8007,34 @@
         </is>
       </c>
       <c r="AS24" t="n">
-        <v>179331</v>
+        <v>116272</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.678</v>
+        <v>-4.122</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.527</v>
+        <v>2.527</v>
       </c>
       <c r="AV24" t="n">
-        <v>-1.205</v>
+        <v>1.595</v>
       </c>
       <c r="AW24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
-        <v>2.086</v>
+        <v>1.9</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.896</v>
+        <v>1</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.316</v>
+        <v>-0.859</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.287</v>
+        <v>0.615</v>
       </c>
       <c r="BB24" t="n">
-        <v>-0.767</v>
+        <v>0.454</v>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
@@ -7851,131 +8043,131 @@
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>1x2</t>
+          <t>1x2_ou</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF24" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="n">
         <v>200</v>
       </c>
       <c r="BI24" t="n">
-        <v>0.443</v>
+        <v>0.39</v>
       </c>
       <c r="BJ24" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK24" t="n">
-        <v>64.8</v>
+        <v>60</v>
       </c>
       <c r="BL24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BM24" t="n">
-        <v>13.2</v>
+        <v>16</v>
       </c>
       <c r="BN24" t="n">
-        <v>64.60599999999999</v>
+        <v>62.748</v>
       </c>
       <c r="BO24" t="n">
-        <v>21.85</v>
+        <v>22.316</v>
       </c>
       <c r="BP24" t="n">
-        <v>13.544</v>
+        <v>14.937</v>
       </c>
       <c r="BQ24" t="n">
-        <v>99.617</v>
+        <v>99.372</v>
       </c>
       <c r="BR24" t="n">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="BS24" t="n">
-        <v>61.074</v>
+        <v>69</v>
       </c>
       <c r="BT24" t="n">
-        <v>26.846</v>
+        <v>23</v>
       </c>
       <c r="BU24" t="n">
-        <v>12.081</v>
+        <v>8</v>
       </c>
       <c r="BV24" t="n">
-        <v>62.82</v>
+        <v>65.748</v>
       </c>
       <c r="BW24" t="n">
-        <v>23.767</v>
+        <v>21.982</v>
       </c>
       <c r="BX24" t="n">
-        <v>13.413</v>
+        <v>12.27</v>
       </c>
       <c r="BY24" t="n">
-        <v>98.098</v>
+        <v>97.381</v>
       </c>
       <c r="BZ24" t="n">
-        <v>49.375</v>
+        <v>100</v>
       </c>
       <c r="CA24" t="n">
-        <v>31.562</v>
+        <v>63</v>
       </c>
       <c r="CB24" t="n">
-        <v>19.062</v>
+        <v>20</v>
       </c>
       <c r="CC24" t="n">
-        <v>320</v>
+        <v>17</v>
       </c>
       <c r="CD24" t="n">
-        <v>1469</v>
+        <v>63.748</v>
       </c>
       <c r="CE24" t="n">
-        <v>4979</v>
+        <v>20.982</v>
       </c>
       <c r="CF24" t="n">
-        <v>8706</v>
+        <v>15.27</v>
       </c>
       <c r="CG24" t="n">
-        <v>15761</v>
+        <v>99.133</v>
       </c>
       <c r="CH24" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="CI24" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="CJ24" t="n">
-        <v>368</v>
+        <v>17</v>
       </c>
       <c r="CK24" t="n">
-        <v>1451</v>
+        <v>100</v>
       </c>
       <c r="CL24" t="n">
-        <v>500</v>
+        <v>888</v>
       </c>
       <c r="CM24" t="n">
-        <v>65.8</v>
+        <v>2936</v>
       </c>
       <c r="CN24" t="n">
-        <v>22.6</v>
+        <v>5048</v>
       </c>
       <c r="CO24" t="n">
-        <v>11.6</v>
+        <v>9078</v>
       </c>
       <c r="CP24" t="n">
-        <v>65.321</v>
+        <v>9</v>
       </c>
       <c r="CQ24" t="n">
-        <v>22.278</v>
+        <v>50</v>
       </c>
       <c r="CR24" t="n">
-        <v>12.401</v>
+        <v>203</v>
       </c>
       <c r="CS24" t="n">
-        <v>99.036</v>
+        <v>845</v>
       </c>
     </row>
     <row r="25">
@@ -8023,50 +8215,50 @@
         <v>27.931</v>
       </c>
       <c r="L25" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M25" t="n">
-        <v>42.6</v>
+        <v>44</v>
       </c>
       <c r="N25" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="O25" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="P25" t="n">
-        <v>41.78</v>
+        <v>41.153</v>
       </c>
       <c r="Q25" t="n">
-        <v>32.669</v>
+        <v>32.227</v>
       </c>
       <c r="R25" t="n">
-        <v>25.552</v>
+        <v>26.62</v>
       </c>
       <c r="S25" t="n">
-        <v>2.051</v>
+        <v>1.424</v>
       </c>
       <c r="T25" t="n">
-        <v>0.328</v>
+        <v>-0.114</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.379</v>
+        <v>-1.31</v>
       </c>
       <c r="V25" t="n">
-        <v>33.8</v>
+        <v>31</v>
       </c>
       <c r="W25" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="X25" t="n">
-        <v>43.6</v>
+        <v>41</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -8075,53 +8267,53 @@
         </is>
       </c>
       <c r="AB25" t="n">
-        <v>99.40000000000001</v>
+        <v>99.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>99.366</v>
+        <v>99.642</v>
       </c>
       <c r="AD25" t="n">
-        <v>99.086</v>
+        <v>99.193</v>
       </c>
       <c r="AE25" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF25" t="n">
-        <v>38.338</v>
+        <v>34.672</v>
       </c>
       <c r="AG25" t="n">
-        <v>46.975</v>
+        <v>53.772</v>
       </c>
       <c r="AH25" t="n">
-        <v>28.83</v>
+        <v>23.669</v>
       </c>
       <c r="AI25" t="n">
-        <v>37.033</v>
+        <v>41.663</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21.028</v>
+        <v>16.691</v>
       </c>
       <c r="AK25" t="n">
-        <v>28.559</v>
+        <v>33.233</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.394</v>
+        <v>2.43</v>
       </c>
       <c r="AM25" t="n">
-        <v>3.061</v>
+        <v>3.103</v>
       </c>
       <c r="AN25" t="n">
-        <v>3.914</v>
+        <v>3.757</v>
       </c>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>largest deviation AWAY -2.4 pp; n_eff=500; market inside 95% CI; avg similarity 99.4%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +1.4 pp; n_eff=100; market inside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
@@ -8133,31 +8325,31 @@
         <v>179331</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.871</v>
+        <v>4.271</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.459</v>
+        <v>-0.341</v>
       </c>
       <c r="AV25" t="n">
-        <v>-3.331</v>
+        <v>-3.931</v>
       </c>
       <c r="AW25" t="n">
         <v>2</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.156</v>
+        <v>1.14</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.894</v>
+        <v>0.82</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.312</v>
+        <v>0.873</v>
       </c>
       <c r="BA25" t="n">
-        <v>0.22</v>
+        <v>-0.073</v>
       </c>
       <c r="BB25" t="n">
-        <v>-1.66</v>
+        <v>-0.876</v>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
@@ -8171,111 +8363,127 @@
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF25" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="n">
         <v>200</v>
       </c>
       <c r="BI25" t="n">
-        <v>0.097</v>
+        <v>0.381</v>
       </c>
       <c r="BJ25" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK25" t="n">
-        <v>42.6</v>
+        <v>44</v>
       </c>
       <c r="BL25" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="BM25" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="BN25" t="n">
-        <v>41.78</v>
+        <v>41.153</v>
       </c>
       <c r="BO25" t="n">
-        <v>32.669</v>
+        <v>32.227</v>
       </c>
       <c r="BP25" t="n">
-        <v>25.552</v>
+        <v>26.62</v>
       </c>
       <c r="BQ25" t="n">
-        <v>99.40000000000001</v>
+        <v>99.61</v>
       </c>
       <c r="BR25" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BS25" t="n">
-        <v>40.8</v>
+        <v>42</v>
       </c>
       <c r="BT25" t="n">
-        <v>30.6</v>
+        <v>34</v>
       </c>
       <c r="BU25" t="n">
-        <v>28.6</v>
+        <v>24</v>
       </c>
       <c r="BV25" t="n">
-        <v>40.494</v>
+        <v>40.486</v>
       </c>
       <c r="BW25" t="n">
-        <v>31.097</v>
+        <v>32.894</v>
       </c>
       <c r="BX25" t="n">
-        <v>28.409</v>
+        <v>26.62</v>
       </c>
       <c r="BY25" t="n">
-        <v>98.742</v>
+        <v>99.286</v>
       </c>
       <c r="BZ25" t="n">
-        <v>31.095</v>
+        <v>100</v>
       </c>
       <c r="CA25" t="n">
-        <v>44.876</v>
+        <v>42</v>
       </c>
       <c r="CB25" t="n">
-        <v>24.028</v>
+        <v>32</v>
       </c>
       <c r="CC25" t="n">
-        <v>283</v>
+        <v>26</v>
       </c>
       <c r="CD25" t="n">
+        <v>40.486</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>32.227</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>27.287</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>99.584</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>30.909</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>49.091</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>20</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>55</v>
+      </c>
+      <c r="CL25" t="n">
         <v>693</v>
       </c>
-      <c r="CE25" t="n">
+      <c r="CM25" t="n">
         <v>3306</v>
       </c>
-      <c r="CF25" t="n">
+      <c r="CN25" t="n">
         <v>8971</v>
       </c>
-      <c r="CG25" t="n">
+      <c r="CO25" t="n">
         <v>32565</v>
       </c>
-      <c r="CH25" t="n">
+      <c r="CP25" t="n">
         <v>9</v>
       </c>
-      <c r="CI25" t="n">
+      <c r="CQ25" t="n">
         <v>74</v>
       </c>
-      <c r="CJ25" t="n">
+      <c r="CR25" t="n">
         <v>261</v>
       </c>
-      <c r="CK25" t="n">
+      <c r="CS25" t="n">
         <v>1435</v>
       </c>
-      <c r="CL25" t="inlineStr"/>
-      <c r="CM25" t="inlineStr"/>
-      <c r="CN25" t="inlineStr"/>
-      <c r="CO25" t="inlineStr"/>
-      <c r="CP25" t="inlineStr"/>
-      <c r="CQ25" t="inlineStr"/>
-      <c r="CR25" t="inlineStr"/>
-      <c r="CS25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -8322,50 +8530,50 @@
         <v>33.983</v>
       </c>
       <c r="L26" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>30.8</v>
+        <v>32</v>
       </c>
       <c r="N26" t="n">
-        <v>38.4</v>
+        <v>34</v>
       </c>
       <c r="O26" t="n">
-        <v>30.8</v>
+        <v>34</v>
       </c>
       <c r="P26" t="n">
-        <v>31.044</v>
+        <v>31.77</v>
       </c>
       <c r="Q26" t="n">
-        <v>37.246</v>
+        <v>34.241</v>
       </c>
       <c r="R26" t="n">
-        <v>31.709</v>
+        <v>33.989</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.611</v>
+        <v>0.115</v>
       </c>
       <c r="T26" t="n">
-        <v>2.884</v>
+        <v>-0.121</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.273</v>
+        <v>0.006</v>
       </c>
       <c r="V26" t="n">
-        <v>35.4</v>
+        <v>29</v>
       </c>
       <c r="W26" t="n">
-        <v>64.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="X26" t="n">
-        <v>46.6</v>
+        <v>39</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.036</v>
+        <v>1.91</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -8374,43 +8582,43 @@
         </is>
       </c>
       <c r="AB26" t="n">
-        <v>98.58</v>
+        <v>99.121</v>
       </c>
       <c r="AC26" t="n">
-        <v>98.462</v>
+        <v>99.29000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>97.873</v>
+        <v>97.95</v>
       </c>
       <c r="AE26" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF26" t="n">
-        <v>26.913</v>
+        <v>23.669</v>
       </c>
       <c r="AG26" t="n">
-        <v>34.98</v>
+        <v>41.663</v>
       </c>
       <c r="AH26" t="n">
-        <v>34.241</v>
+        <v>25.461</v>
       </c>
       <c r="AI26" t="n">
-        <v>42.736</v>
+        <v>43.722</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26.913</v>
+        <v>25.461</v>
       </c>
       <c r="AK26" t="n">
-        <v>34.98</v>
+        <v>43.722</v>
       </c>
       <c r="AL26" t="n">
-        <v>3.221</v>
+        <v>3.148</v>
       </c>
       <c r="AM26" t="n">
-        <v>2.685</v>
+        <v>2.92</v>
       </c>
       <c r="AN26" t="n">
-        <v>3.154</v>
+        <v>2.942</v>
       </c>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr">
@@ -8420,7 +8628,7 @@
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>largest deviation DRAW +2.9 pp; n_eff=500; market inside 95% CI; avg similarity 98.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation DRAW -0.1 pp; n_eff=100; market inside 95% CI; avg similarity 99.1%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
@@ -8432,31 +8640,31 @@
         <v>179331</v>
       </c>
       <c r="AT26" t="n">
-        <v>-0.855</v>
+        <v>0.345</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.038</v>
+        <v>-0.362</v>
       </c>
       <c r="AV26" t="n">
-        <v>-3.183</v>
+        <v>0.017</v>
       </c>
       <c r="AW26" t="n">
         <v>2</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.006</v>
+        <v>0.89</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ26" t="n">
-        <v>-0.411</v>
+        <v>0.074</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.901</v>
+        <v>-0.076</v>
       </c>
       <c r="BB26" t="n">
-        <v>-1.503</v>
+        <v>0.004</v>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
@@ -8470,111 +8678,127 @@
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF26" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="n">
         <v>200</v>
       </c>
       <c r="BI26" t="n">
-        <v>0.057</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="BJ26" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK26" t="n">
-        <v>30.8</v>
+        <v>32</v>
       </c>
       <c r="BL26" t="n">
-        <v>38.4</v>
+        <v>34</v>
       </c>
       <c r="BM26" t="n">
-        <v>30.8</v>
+        <v>34</v>
       </c>
       <c r="BN26" t="n">
-        <v>31.044</v>
+        <v>31.77</v>
       </c>
       <c r="BO26" t="n">
-        <v>37.246</v>
+        <v>34.241</v>
       </c>
       <c r="BP26" t="n">
-        <v>31.709</v>
+        <v>33.989</v>
       </c>
       <c r="BQ26" t="n">
-        <v>98.58</v>
+        <v>99.121</v>
       </c>
       <c r="BR26" t="n">
-        <v>411</v>
+        <v>100</v>
       </c>
       <c r="BS26" t="n">
-        <v>33.577</v>
+        <v>33</v>
       </c>
       <c r="BT26" t="n">
-        <v>35.523</v>
+        <v>35</v>
       </c>
       <c r="BU26" t="n">
-        <v>30.9</v>
+        <v>32</v>
       </c>
       <c r="BV26" t="n">
-        <v>32.948</v>
+        <v>32.104</v>
       </c>
       <c r="BW26" t="n">
-        <v>35.143</v>
+        <v>34.575</v>
       </c>
       <c r="BX26" t="n">
-        <v>31.909</v>
+        <v>33.322</v>
       </c>
       <c r="BY26" t="n">
-        <v>97.857</v>
+        <v>98.44799999999999</v>
       </c>
       <c r="BZ26" t="n">
-        <v>29.63</v>
+        <v>100</v>
       </c>
       <c r="CA26" t="n">
-        <v>49.537</v>
+        <v>28</v>
       </c>
       <c r="CB26" t="n">
-        <v>20.833</v>
+        <v>34</v>
       </c>
       <c r="CC26" t="n">
-        <v>216</v>
+        <v>38</v>
       </c>
       <c r="CD26" t="n">
+        <v>30.437</v>
+      </c>
+      <c r="CE26" t="n">
+        <v>34.241</v>
+      </c>
+      <c r="CF26" t="n">
+        <v>35.322</v>
+      </c>
+      <c r="CG26" t="n">
+        <v>99.003</v>
+      </c>
+      <c r="CH26" t="n">
+        <v>23.529</v>
+      </c>
+      <c r="CI26" t="n">
+        <v>47.059</v>
+      </c>
+      <c r="CJ26" t="n">
+        <v>29.412</v>
+      </c>
+      <c r="CK26" t="n">
+        <v>34</v>
+      </c>
+      <c r="CL26" t="n">
         <v>105</v>
       </c>
-      <c r="CE26" t="n">
+      <c r="CM26" t="n">
         <v>482</v>
       </c>
-      <c r="CF26" t="n">
+      <c r="CN26" t="n">
         <v>1802</v>
       </c>
-      <c r="CG26" t="n">
+      <c r="CO26" t="n">
         <v>10558</v>
       </c>
-      <c r="CH26" t="n">
+      <c r="CP26" t="n">
         <v>0</v>
       </c>
-      <c r="CI26" t="n">
+      <c r="CQ26" t="n">
         <v>16</v>
       </c>
-      <c r="CJ26" t="n">
+      <c r="CR26" t="n">
         <v>52</v>
       </c>
-      <c r="CK26" t="n">
+      <c r="CS26" t="n">
         <v>218</v>
       </c>
-      <c r="CL26" t="inlineStr"/>
-      <c r="CM26" t="inlineStr"/>
-      <c r="CN26" t="inlineStr"/>
-      <c r="CO26" t="inlineStr"/>
-      <c r="CP26" t="inlineStr"/>
-      <c r="CQ26" t="inlineStr"/>
-      <c r="CR26" t="inlineStr"/>
-      <c r="CS26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -8621,95 +8845,95 @@
         <v>13.876</v>
       </c>
       <c r="L27" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="N27" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="O27" t="n">
-        <v>10.2</v>
+        <v>12</v>
       </c>
       <c r="P27" t="n">
-        <v>69.441</v>
+        <v>66.69499999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>19.309</v>
+        <v>20.055</v>
       </c>
       <c r="R27" t="n">
-        <v>11.25</v>
+        <v>13.251</v>
       </c>
       <c r="S27" t="n">
-        <v>3.899</v>
+        <v>1.153</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.273</v>
+        <v>-0.527</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.626</v>
+        <v>-0.625</v>
       </c>
       <c r="V27" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="W27" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="X27" t="n">
-        <v>50.8</v>
+        <v>53</v>
       </c>
       <c r="Y27" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>MODERATE HISTORICAL DEVIATION</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="AB27" t="n">
-        <v>99.587</v>
+        <v>99.76000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>99.565</v>
+        <v>99.78400000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>99.303</v>
+        <v>99.47499999999999</v>
       </c>
       <c r="AE27" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF27" t="n">
-        <v>66.874</v>
+        <v>59.374</v>
       </c>
       <c r="AG27" t="n">
-        <v>74.80500000000001</v>
+        <v>77.22</v>
       </c>
       <c r="AH27" t="n">
-        <v>15.618</v>
+        <v>12.515</v>
       </c>
       <c r="AI27" t="n">
-        <v>22.458</v>
+        <v>27.779</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7.843</v>
+        <v>6.999</v>
       </c>
       <c r="AK27" t="n">
-        <v>13.164</v>
+        <v>19.812</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.44</v>
+        <v>1.499</v>
       </c>
       <c r="AM27" t="n">
-        <v>5.179</v>
+        <v>4.986</v>
       </c>
       <c r="AN27" t="n">
-        <v>8.888999999999999</v>
+        <v>7.547</v>
       </c>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr">
@@ -8719,7 +8943,7 @@
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>largest deviation HOME +3.9 pp; n_eff=500; market outside 95% CI; avg similarity 99.6%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +1.2 pp; n_eff=100; market inside 95% CI; avg similarity 99.8%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
@@ -8731,31 +8955,31 @@
         <v>179331</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.458</v>
+        <v>3.458</v>
       </c>
       <c r="AU27" t="n">
-        <v>-1.782</v>
+        <v>-1.582</v>
       </c>
       <c r="AV27" t="n">
-        <v>-3.676</v>
+        <v>-1.876</v>
       </c>
       <c r="AW27" t="n">
         <v>3</v>
       </c>
       <c r="AX27" t="n">
-        <v>2.286</v>
+        <v>2.08</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.844</v>
+        <v>0.92</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.568</v>
+        <v>0.728</v>
       </c>
       <c r="BA27" t="n">
-        <v>-0.986</v>
+        <v>-0.391</v>
       </c>
       <c r="BB27" t="n">
-        <v>-2.378</v>
+        <v>-0.543</v>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
@@ -8769,111 +8993,127 @@
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF27" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="n">
         <v>200</v>
       </c>
       <c r="BI27" t="n">
-        <v>0.01</v>
+        <v>0.467</v>
       </c>
       <c r="BJ27" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK27" t="n">
+        <v>69</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>12</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>66.69499999999999</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>20.055</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>13.251</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>99.76000000000001</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>100</v>
+      </c>
+      <c r="BS27" t="n">
         <v>71</v>
       </c>
-      <c r="BL27" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="BM27" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BN27" t="n">
-        <v>69.441</v>
-      </c>
-      <c r="BO27" t="n">
-        <v>19.309</v>
-      </c>
-      <c r="BP27" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="BQ27" t="n">
-        <v>99.587</v>
-      </c>
-      <c r="BR27" t="n">
-        <v>362</v>
-      </c>
-      <c r="BS27" t="n">
-        <v>67.68000000000001</v>
-      </c>
       <c r="BT27" t="n">
-        <v>18.508</v>
+        <v>15</v>
       </c>
       <c r="BU27" t="n">
-        <v>13.812</v>
+        <v>14</v>
       </c>
       <c r="BV27" t="n">
-        <v>66.919</v>
+        <v>67.361</v>
       </c>
       <c r="BW27" t="n">
-        <v>19.246</v>
+        <v>18.721</v>
       </c>
       <c r="BX27" t="n">
-        <v>13.835</v>
+        <v>13.917</v>
       </c>
       <c r="BY27" t="n">
-        <v>97.947</v>
+        <v>98.129</v>
       </c>
       <c r="BZ27" t="n">
-        <v>49.53</v>
+        <v>100</v>
       </c>
       <c r="CA27" t="n">
-        <v>37.304</v>
+        <v>72</v>
       </c>
       <c r="CB27" t="n">
-        <v>13.166</v>
+        <v>20</v>
       </c>
       <c r="CC27" t="n">
-        <v>319</v>
+        <v>8</v>
       </c>
       <c r="CD27" t="n">
+        <v>67.69499999999999</v>
+      </c>
+      <c r="CE27" t="n">
+        <v>20.388</v>
+      </c>
+      <c r="CF27" t="n">
+        <v>11.917</v>
+      </c>
+      <c r="CG27" t="n">
+        <v>99.149</v>
+      </c>
+      <c r="CH27" t="n">
+        <v>35.616</v>
+      </c>
+      <c r="CI27" t="n">
+        <v>49.315</v>
+      </c>
+      <c r="CJ27" t="n">
+        <v>15.068</v>
+      </c>
+      <c r="CK27" t="n">
+        <v>73</v>
+      </c>
+      <c r="CL27" t="n">
         <v>1295</v>
       </c>
-      <c r="CE27" t="n">
+      <c r="CM27" t="n">
         <v>4346</v>
       </c>
-      <c r="CF27" t="n">
+      <c r="CN27" t="n">
         <v>7782</v>
       </c>
-      <c r="CG27" t="n">
+      <c r="CO27" t="n">
         <v>14041</v>
       </c>
-      <c r="CH27" t="n">
+      <c r="CP27" t="n">
         <v>11</v>
       </c>
-      <c r="CI27" t="n">
+      <c r="CQ27" t="n">
         <v>82</v>
       </c>
-      <c r="CJ27" t="n">
+      <c r="CR27" t="n">
         <v>325</v>
       </c>
-      <c r="CK27" t="n">
+      <c r="CS27" t="n">
         <v>1207</v>
       </c>
-      <c r="CL27" t="inlineStr"/>
-      <c r="CM27" t="inlineStr"/>
-      <c r="CN27" t="inlineStr"/>
-      <c r="CO27" t="inlineStr"/>
-      <c r="CP27" t="inlineStr"/>
-      <c r="CQ27" t="inlineStr"/>
-      <c r="CR27" t="inlineStr"/>
-      <c r="CS27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -8920,95 +9160,95 @@
         <v>10.855</v>
       </c>
       <c r="L28" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="M28" t="n">
-        <v>67.8</v>
+        <v>78</v>
       </c>
       <c r="N28" t="n">
-        <v>21.6</v>
+        <v>14</v>
       </c>
       <c r="O28" t="n">
-        <v>10.6</v>
+        <v>8</v>
       </c>
       <c r="P28" t="n">
-        <v>67.258</v>
+        <v>69.93600000000001</v>
       </c>
       <c r="Q28" t="n">
-        <v>22.069</v>
+        <v>20.161</v>
       </c>
       <c r="R28" t="n">
-        <v>10.673</v>
+        <v>9.903</v>
       </c>
       <c r="S28" t="n">
-        <v>1.354</v>
+        <v>4.032</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.172</v>
+        <v>-3.08</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.182</v>
+        <v>-0.952</v>
       </c>
       <c r="V28" t="n">
-        <v>46.8</v>
+        <v>50</v>
       </c>
       <c r="W28" t="n">
-        <v>53.2</v>
+        <v>50</v>
       </c>
       <c r="X28" t="n">
-        <v>43.2</v>
+        <v>41</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.548</v>
+        <v>2.55</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>MODERATE HISTORICAL DEVIATION</t>
         </is>
       </c>
       <c r="AB28" t="n">
-        <v>98.884</v>
+        <v>99.157</v>
       </c>
       <c r="AC28" t="n">
-        <v>98.797</v>
+        <v>99.14400000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>98.29900000000001</v>
+        <v>98.434</v>
       </c>
       <c r="AE28" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AF28" t="n">
-        <v>63.582</v>
+        <v>68.929</v>
       </c>
       <c r="AG28" t="n">
-        <v>71.746</v>
+        <v>84.999</v>
       </c>
       <c r="AH28" t="n">
-        <v>18.217</v>
+        <v>8.526</v>
       </c>
       <c r="AI28" t="n">
-        <v>25.416</v>
+        <v>22.137</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8.196</v>
+        <v>4.109</v>
       </c>
       <c r="AK28" t="n">
-        <v>13.605</v>
+        <v>14.998</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.487</v>
+        <v>1.43</v>
       </c>
       <c r="AM28" t="n">
-        <v>4.531</v>
+        <v>4.96</v>
       </c>
       <c r="AN28" t="n">
-        <v>9.369999999999999</v>
+        <v>10.098</v>
       </c>
       <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr">
@@ -9018,7 +9258,7 @@
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>largest deviation HOME +1.4 pp; n_eff=500; market inside 95% CI; avg similarity 98.9%; backtest: no significant improvement over market</t>
+          <t>largest deviation HOME +4.0 pp; n_eff=100; market outside 95% CI; avg similarity 99.2%; backtest: no significant improvement over market</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
@@ -9030,31 +9270,31 @@
         <v>179331</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.896</v>
+        <v>12.096</v>
       </c>
       <c r="AU28" t="n">
-        <v>-1.641</v>
+        <v>-9.241</v>
       </c>
       <c r="AV28" t="n">
-        <v>-0.255</v>
+        <v>-2.855</v>
       </c>
       <c r="AW28" t="n">
         <v>2</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.854</v>
+        <v>1.96</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.694</v>
+        <v>0.59</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.894</v>
+        <v>2.552</v>
       </c>
       <c r="BA28" t="n">
-        <v>-0.869</v>
+        <v>-2.188</v>
       </c>
       <c r="BB28" t="n">
-        <v>-0.183</v>
+        <v>-0.918</v>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
@@ -9068,111 +9308,127 @@
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>cosine</t>
+          <t>mahalanobis</t>
         </is>
       </c>
       <c r="BF28" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BG28" t="inlineStr"/>
       <c r="BH28" t="n">
         <v>200</v>
       </c>
       <c r="BI28" t="n">
-        <v>0.371</v>
+        <v>0.011</v>
       </c>
       <c r="BJ28" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="BK28" t="n">
-        <v>67.8</v>
+        <v>78</v>
       </c>
       <c r="BL28" t="n">
-        <v>21.6</v>
+        <v>14</v>
       </c>
       <c r="BM28" t="n">
-        <v>10.6</v>
+        <v>8</v>
       </c>
       <c r="BN28" t="n">
-        <v>67.258</v>
+        <v>69.93600000000001</v>
       </c>
       <c r="BO28" t="n">
-        <v>22.069</v>
+        <v>20.161</v>
       </c>
       <c r="BP28" t="n">
-        <v>10.673</v>
+        <v>9.903</v>
       </c>
       <c r="BQ28" t="n">
-        <v>98.884</v>
+        <v>99.157</v>
       </c>
       <c r="BR28" t="n">
-        <v>167</v>
+        <v>100</v>
       </c>
       <c r="BS28" t="n">
-        <v>64.67100000000001</v>
+        <v>65</v>
       </c>
       <c r="BT28" t="n">
-        <v>20.359</v>
+        <v>24</v>
       </c>
       <c r="BU28" t="n">
-        <v>14.97</v>
+        <v>11</v>
       </c>
       <c r="BV28" t="n">
-        <v>65.343</v>
+        <v>65.60299999999999</v>
       </c>
       <c r="BW28" t="n">
-        <v>21.93</v>
+        <v>23.494</v>
       </c>
       <c r="BX28" t="n">
-        <v>12.727</v>
+        <v>10.903</v>
       </c>
       <c r="BY28" t="n">
-        <v>98.127</v>
+        <v>97.988</v>
       </c>
       <c r="BZ28" t="n">
-        <v>47.143</v>
+        <v>100</v>
       </c>
       <c r="CA28" t="n">
-        <v>40.714</v>
+        <v>73</v>
       </c>
       <c r="CB28" t="n">
-        <v>12.143</v>
+        <v>19</v>
       </c>
       <c r="CC28" t="n">
-        <v>280</v>
+        <v>8</v>
       </c>
       <c r="CD28" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="CE28" t="n">
+        <v>21.827</v>
+      </c>
+      <c r="CF28" t="n">
+        <v>9.903</v>
+      </c>
+      <c r="CG28" t="n">
+        <v>98.98699999999999</v>
+      </c>
+      <c r="CH28" t="n">
+        <v>59.016</v>
+      </c>
+      <c r="CI28" t="n">
+        <v>31.148</v>
+      </c>
+      <c r="CJ28" t="n">
+        <v>9.836</v>
+      </c>
+      <c r="CK28" t="n">
+        <v>61</v>
+      </c>
+      <c r="CL28" t="n">
         <v>168</v>
       </c>
-      <c r="CE28" t="n">
+      <c r="CM28" t="n">
         <v>1266</v>
       </c>
-      <c r="CF28" t="n">
+      <c r="CN28" t="n">
         <v>3918</v>
       </c>
-      <c r="CG28" t="n">
+      <c r="CO28" t="n">
         <v>11703</v>
       </c>
-      <c r="CH28" t="n">
+      <c r="CP28" t="n">
         <v>4</v>
       </c>
-      <c r="CI28" t="n">
+      <c r="CQ28" t="n">
         <v>6</v>
       </c>
-      <c r="CJ28" t="n">
+      <c r="CR28" t="n">
         <v>26</v>
       </c>
-      <c r="CK28" t="n">
+      <c r="CS28" t="n">
         <v>105</v>
       </c>
-      <c r="CL28" t="inlineStr"/>
-      <c r="CM28" t="inlineStr"/>
-      <c r="CN28" t="inlineStr"/>
-      <c r="CO28" t="inlineStr"/>
-      <c r="CP28" t="inlineStr"/>
-      <c r="CQ28" t="inlineStr"/>
-      <c r="CR28" t="inlineStr"/>
-      <c r="CS28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
